--- a/data/Cost declines by tech.xlsx
+++ b/data/Cost declines by tech.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9a072a59b81ab8f9/Documents/Work/Clients ^0 prospects/EpochAI/inference-cost/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1141" documentId="8_{237EF59B-240D-4B45-BBDB-12EDD86E70D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84804678-1A27-4079-8D64-B1C7EC584673}"/>
+  <xr:revisionPtr revIDLastSave="1237" documentId="8_{237EF59B-240D-4B45-BBDB-12EDD86E70D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D5CFCC3-0D9C-47D3-9E82-7716AAE62D33}"/>
   <bookViews>
-    <workbookView xWindow="-78" yWindow="0" windowWidth="18318" windowHeight="14478" xr2:uid="{55FDA7DF-2265-4D1B-B569-857BE3FE3144}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" xr2:uid="{55FDA7DF-2265-4D1B-B569-857BE3FE3144}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="4" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="228">
   <si>
     <t>World</t>
   </si>
@@ -2220,13 +2220,7 @@
     <t>1800–2023</t>
   </si>
   <si>
-    <t>2001–25</t>
-  </si>
-  <si>
     <t>2023–26</t>
-  </si>
-  <si>
-    <t>Price drops expressed as compounded quarterly rates, after inflation adjustment. The fastest drop for residential electricity price is especially uncertain as it is based on rough figures for 1902 and 1907.</t>
   </si>
   <si>
     <t>t</t>
@@ -2274,13 +2268,19 @@
     <t>Hersh (1999)</t>
   </si>
   <si>
-    <t>Real (9182-84 $)</t>
-  </si>
-  <si>
     <t>Combined</t>
   </si>
   <si>
     <t>1940–2001</t>
+  </si>
+  <si>
+    <t>Chart source data (index, first observation = 100)</t>
+  </si>
+  <si>
+    <t>2001–22</t>
+  </si>
+  <si>
+    <t>Price drops expressed as compounded quarterly rates, after inflation adjustment.</t>
   </si>
 </sst>
 </file>
@@ -2295,7 +2295,7 @@
     <numFmt numFmtId="168" formatCode="0.000000"/>
     <numFmt numFmtId="169" formatCode="0.0000"/>
     <numFmt numFmtId="170" formatCode="0.0%"/>
-    <numFmt numFmtId="173" formatCode="0.00&quot;x/year&quot;"/>
+    <numFmt numFmtId="171" formatCode="0.00&quot;x/year&quot;"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -2495,7 +2495,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2640,18 +2640,23 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2827,9 +2832,9 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="7.0861400192108848E-2"/>
-          <c:y val="4.1051005502140296E-2"/>
-          <c:w val="0.8870302051404414"/>
+          <c:x val="9.4016404945968773E-2"/>
+          <c:y val="6.0274498584973017E-2"/>
+          <c:w val="0.86806932836467099"/>
           <c:h val="0.84656994233186922"/>
         </c:manualLayout>
       </c:layout>
@@ -2845,7 +2850,9 @@
           <c:spPr>
             <a:ln w="12700" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2856,9 +2863,9 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Table!$B$12:$B$13</c:f>
+              <c:f>Table!$AD$5:$AD$6</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>1.6163586584530094</c:v>
@@ -2871,9 +2878,9 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Table!$C$12:$C$13</c:f>
+              <c:f>Table!$AE$5:$AE$6</c:f>
               <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>1.6493911422653169</c:v>
@@ -2900,7 +2907,7 @@
           <c:spPr>
             <a:ln w="12700" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent4"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2911,7 +2918,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Compute!$M$22:$M$76</c:f>
+              <c:f>Table!$Z$4:$Z$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="55"/>
@@ -3085,7 +3092,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Compute!$Q$22:$Q$76</c:f>
+              <c:f>Table!$AA$4:$AA$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="55"/>
@@ -3284,7 +3291,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Lithium batteries'!$D$4:$D$37</c:f>
+              <c:f>Table!$X$4:$X$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="34"/>
@@ -3395,7 +3402,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Lithium batteries'!$F$4:$F$37</c:f>
+              <c:f>Table!$Y$4:$Y$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="34"/>
@@ -3520,10 +3527,7 @@
           <c:spPr>
             <a:ln w="12700" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="40000"/>
-                  <a:lumOff val="60000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3534,10 +3538,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'DNA sequencing'!$C$6:$C$84</c:f>
+              <c:f>Table!$AB$4:$AB$81</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="79"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="78"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3771,19 +3775,16 @@
                 </c:pt>
                 <c:pt idx="77">
                   <c:v>20.665297741273207</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>23.750855578371102</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'DNA sequencing'!$J$6:$J$84</c:f>
+              <c:f>Table!$AC$4:$AC$81</c:f>
               <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="79"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="78"/>
                 <c:pt idx="0">
                   <c:v>100</c:v>
                 </c:pt>
@@ -4039,7 +4040,6 @@
               <a:solidFill>
                 <a:schemeClr val="accent5"/>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -4049,9 +4049,9 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Table!$B$11:$B$12</c:f>
+              <c:f>Table!$AD$4:$AD$5</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -4064,11 +4064,11 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Table!$C$11:$C$12</c:f>
+              <c:f>Table!$AE$4:$AE$5</c:f>
               <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
-                <c:pt idx="0" formatCode="0">
+                <c:pt idx="0">
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -4093,7 +4093,7 @@
           <c:spPr>
             <a:ln w="12700" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="00B0F0"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4104,7 +4104,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Electricity!$K$4:$K$58</c:f>
+              <c:f>Table!$V$4:$V$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="55"/>
@@ -4278,7 +4278,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Electricity!$L$4:$L$58</c:f>
+              <c:f>Table!$W$4:$W$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="55"/>
@@ -4586,7 +4586,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
@@ -6341,15 +6341,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>194310</xdr:rowOff>
+      <xdr:rowOff>354330</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>483870</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:colOff>487680</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>73660</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6383,12 +6383,12 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.65714</cdr:x>
-      <cdr:y>0.79582</cdr:y>
+      <cdr:x>0.67193</cdr:x>
+      <cdr:y>0.81426</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.79881</cdr:x>
-      <cdr:y>0.90817</cdr:y>
+      <cdr:x>0.8136</cdr:x>
+      <cdr:y>0.92661</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -6403,8 +6403,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4247929" y="3149322"/>
-          <a:ext cx="915798" cy="444605"/>
+          <a:off x="4500571" y="3196437"/>
+          <a:ext cx="948902" cy="441038"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -6458,12 +6458,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.37278</cdr:x>
-      <cdr:y>0.18049</cdr:y>
+      <cdr:x>0.387</cdr:x>
+      <cdr:y>0.1999</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.51446</cdr:x>
-      <cdr:y>0.25149</cdr:y>
+      <cdr:x>0.52868</cdr:x>
+      <cdr:y>0.2709</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -6478,8 +6478,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="2437233" y="709212"/>
-          <a:ext cx="926298" cy="278986"/>
+          <a:off x="2592123" y="784726"/>
+          <a:ext cx="948970" cy="278716"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -6610,12 +6610,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.24011</cdr:x>
-      <cdr:y>0.41158</cdr:y>
+      <cdr:x>0.26343</cdr:x>
+      <cdr:y>0.42808</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.38179</cdr:x>
-      <cdr:y>0.57549</cdr:y>
+      <cdr:x>0.40511</cdr:x>
+      <cdr:y>0.59199</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -6630,8 +6630,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1569824" y="1617260"/>
-          <a:ext cx="926298" cy="644065"/>
+          <a:off x="1764462" y="1680456"/>
+          <a:ext cx="948970" cy="643440"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -6675,7 +6675,7 @@
               <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>2001–25</a:t>
+            <a:t>2001–22</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100" kern="1200">
             <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -6687,12 +6687,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.11351</cdr:x>
-      <cdr:y>0.4121</cdr:y>
+      <cdr:x>0.13456</cdr:x>
+      <cdr:y>0.42957</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.17077</cdr:x>
-      <cdr:y>0.54032</cdr:y>
+      <cdr:x>0.19182</cdr:x>
+      <cdr:y>0.55779</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -6707,8 +6707,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="742146" y="1619300"/>
-          <a:ext cx="374364" cy="503825"/>
+          <a:off x="901258" y="1686307"/>
+          <a:ext cx="383526" cy="503337"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -6762,12 +6762,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.85865</cdr:x>
-      <cdr:y>0.10641</cdr:y>
+      <cdr:x>0.8706</cdr:x>
+      <cdr:y>0.12194</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>1</cdr:x>
-      <cdr:y>0.23067</cdr:y>
+      <cdr:x>0.99374</cdr:x>
+      <cdr:y>0.2462</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -6782,8 +6782,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5613819" y="418125"/>
-          <a:ext cx="924141" cy="488265"/>
+          <a:off x="5831231" y="478680"/>
+          <a:ext cx="824839" cy="487791"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -6820,12 +6820,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.00641</cdr:x>
-      <cdr:y>0.00776</cdr:y>
+      <cdr:x>0.00796</cdr:x>
+      <cdr:y>0</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.07284</cdr:x>
-      <cdr:y>0.0863</cdr:y>
+      <cdr:x>0.08745</cdr:x>
+      <cdr:y>0.099</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -6840,8 +6840,66 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="41910" y="30480"/>
-          <a:ext cx="434340" cy="308610"/>
+          <a:off x="53340" y="0"/>
+          <a:ext cx="532378" cy="388620"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>Starting</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>price</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.04601</cdr:x>
+      <cdr:y>0.1028</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.09846</cdr:x>
+      <cdr:y>0.17358</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="8" name="TextBox 7">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8660BA5-7038-65A7-9FF1-0F500B788276}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="308164" y="403555"/>
+          <a:ext cx="351309" cy="277852"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -6857,7 +6915,7 @@
               <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
               <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
             </a:rPr>
-            <a:t>Start</a:t>
+            <a:t>10x fall</a:t>
           </a:r>
         </a:p>
       </cdr:txBody>
@@ -6865,57 +6923,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.02098</cdr:x>
-      <cdr:y>0.08242</cdr:y>
+      <cdr:x>0.02446</cdr:x>
+      <cdr:y>0.17746</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.07343</cdr:x>
-      <cdr:y>0.1532</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="8" name="TextBox 7">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8660BA5-7038-65A7-9FF1-0F500B788276}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="137160" y="323850"/>
-          <a:ext cx="342900" cy="278130"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>10x</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0</cdr:x>
-      <cdr:y>0.15902</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.0711</cdr:x>
-      <cdr:y>0.23368</cdr:y>
+      <cdr:x>0.09556</cdr:x>
+      <cdr:y>0.25212</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -6930,8 +6943,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="624840"/>
-          <a:ext cx="464820" cy="293370"/>
+          <a:off x="163830" y="696634"/>
+          <a:ext cx="476227" cy="293083"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -7012,12 +7025,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.03089</cdr:x>
-      <cdr:y>0.2298</cdr:y>
+      <cdr:x>0.0599</cdr:x>
+      <cdr:y>0.40353</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.06469</cdr:x>
-      <cdr:y>0.3161</cdr:y>
+      <cdr:x>0.0937</cdr:x>
+      <cdr:y>0.48983</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -7032,8 +7045,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="201930" y="902970"/>
-          <a:ext cx="220980" cy="339090"/>
+          <a:off x="401211" y="1584086"/>
+          <a:ext cx="226391" cy="338777"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -7056,12 +7069,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.02991</cdr:x>
-      <cdr:y>0.30295</cdr:y>
+      <cdr:x>0.06063</cdr:x>
+      <cdr:y>0.24666</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.06371</cdr:x>
-      <cdr:y>0.36189</cdr:y>
+      <cdr:x>0.09443</cdr:x>
+      <cdr:y>0.3056</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -7076,8 +7089,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="195568" y="1190409"/>
-          <a:ext cx="220983" cy="231597"/>
+          <a:off x="406077" y="968271"/>
+          <a:ext cx="226391" cy="231374"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -7164,12 +7177,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.0305</cdr:x>
-      <cdr:y>0.38429</cdr:y>
+      <cdr:x>0.05951</cdr:x>
+      <cdr:y>0.32509</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.0643</cdr:x>
-      <cdr:y>0.44323</cdr:y>
+      <cdr:x>0.09331</cdr:x>
+      <cdr:y>0.38403</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -7184,8 +7197,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="199390" y="1510026"/>
-          <a:ext cx="220983" cy="231598"/>
+          <a:off x="398598" y="1276147"/>
+          <a:ext cx="226392" cy="231373"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -7375,10 +7388,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7748,9 +7757,31 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="582" row="5">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{E6D776B9-D753-4D5F-9CEE-19A46C7FA9D5}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;92ebab2c-2bca-4762-ba12-4cf0652975e0&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937B7894-4F69-400D-85CE-13DD92AA35D6}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:AE81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16.41796875" customWidth="1"/>
@@ -7762,9 +7793,10 @@
     <col min="7" max="7" width="14.26171875" customWidth="1"/>
     <col min="8" max="8" width="6" customWidth="1"/>
     <col min="9" max="9" width="10.9453125" customWidth="1"/>
+    <col min="22" max="31" width="10.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:31" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="49" t="s">
         <v>10</v>
       </c>
@@ -7775,19 +7807,22 @@
         <v>191</v>
       </c>
       <c r="D1" s="50" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E1" s="50" t="s">
         <v>201</v>
       </c>
       <c r="F1" s="51"/>
       <c r="G1" s="58" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H1" s="58"/>
       <c r="I1" s="58"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="V1" s="11" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4" t="s">
         <v>197</v>
       </c>
@@ -7811,12 +7846,32 @@
         <f t="shared" ref="H2:H6" si="0">$G$7/G2</f>
         <v>53.955240180849124</v>
       </c>
-      <c r="I2" s="63">
+      <c r="I2" s="61">
         <f t="shared" ref="I2:I6" si="1">(1-D2)^-4</f>
         <v>1.0481922705785034</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="V2" s="65" t="s">
+        <v>197</v>
+      </c>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA2" s="65"/>
+      <c r="AB2" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC2" s="65"/>
+      <c r="AD2" s="65" t="s">
+        <v>200</v>
+      </c>
+      <c r="AE2" s="65"/>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>195</v>
       </c>
@@ -7843,12 +7898,42 @@
         <f t="shared" si="0"/>
         <v>17.563946037544497</v>
       </c>
-      <c r="I3" s="63">
+      <c r="I3" s="61">
         <f t="shared" si="1"/>
         <v>1.155561883967176</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="V3" s="64" t="s">
+        <v>216</v>
+      </c>
+      <c r="W3" s="64" t="s">
+        <v>203</v>
+      </c>
+      <c r="X3" s="64" t="s">
+        <v>216</v>
+      </c>
+      <c r="Y3" s="64" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z3" s="64" t="s">
+        <v>216</v>
+      </c>
+      <c r="AA3" s="64" t="s">
+        <v>203</v>
+      </c>
+      <c r="AB3" s="64" t="s">
+        <v>216</v>
+      </c>
+      <c r="AC3" s="64" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD3" s="64" t="s">
+        <v>216</v>
+      </c>
+      <c r="AE3" s="64" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4" t="s">
         <v>192</v>
       </c>
@@ -7864,7 +7949,7 @@
       </c>
       <c r="E4" s="47">
         <f>Illumination!E1</f>
-        <v>6.6782094039954276E-2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="47"/>
       <c r="G4" s="57">
@@ -7875,18 +7960,58 @@
         <f t="shared" si="0"/>
         <v>68.371379189749248</v>
       </c>
-      <c r="I4" s="63">
+      <c r="I4" s="61">
         <f t="shared" si="1"/>
         <v>1.0378413449321391</v>
       </c>
       <c r="J4" s="4"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="V4">
+        <f>Electricity!K4</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="66">
+        <f>Electricity!L4</f>
+        <v>100</v>
+      </c>
+      <c r="X4">
+        <f>'Lithium batteries'!D4</f>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="66">
+        <f>'Lithium batteries'!F4</f>
+        <v>100</v>
+      </c>
+      <c r="Z4">
+        <f>Compute!M22</f>
+        <v>0</v>
+      </c>
+      <c r="AA4" s="66">
+        <f>Compute!Q22</f>
+        <v>100</v>
+      </c>
+      <c r="AB4">
+        <f>'DNA sequencing'!C6</f>
+        <v>0</v>
+      </c>
+      <c r="AC4" s="66">
+        <f>'DNA sequencing'!J6</f>
+        <v>100</v>
+      </c>
+      <c r="AD4">
+        <f>$B11</f>
+        <v>0</v>
+      </c>
+      <c r="AE4" s="66">
+        <f>$C11</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>202</v>
       </c>
       <c r="B5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C5" t="s">
         <v>193</v>
@@ -7895,10 +8020,7 @@
         <f>1-(Compute!P76/Compute!P22)^(1/(Compute!N76-Compute!N22)/4)</f>
         <v>9.8502965405815934E-2</v>
       </c>
-      <c r="E5" s="47">
-        <f>Compute!P5</f>
-        <v>0.25071175800559653</v>
-      </c>
+      <c r="E5" s="47"/>
       <c r="F5" s="47"/>
       <c r="G5" s="57">
         <f t="shared" si="2"/>
@@ -7908,23 +8030,63 @@
         <f t="shared" si="0"/>
         <v>6.1223461741650125</v>
       </c>
-      <c r="I5" s="63">
+      <c r="I5" s="61">
         <f t="shared" si="1"/>
         <v>1.5140589684406742</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="V5">
+        <f>Electricity!K5</f>
+        <v>5</v>
+      </c>
+      <c r="W5" s="66">
+        <f>Electricity!L5</f>
+        <v>98.103137396321642</v>
+      </c>
+      <c r="X5">
+        <f>'Lithium batteries'!D5</f>
+        <v>1</v>
+      </c>
+      <c r="Y5" s="66">
+        <f>'Lithium batteries'!F5</f>
+        <v>80.216650398524251</v>
+      </c>
+      <c r="Z5">
+        <f>Compute!M23</f>
+        <v>1</v>
+      </c>
+      <c r="AA5" s="66">
+        <f>Compute!Q23</f>
+        <v>100</v>
+      </c>
+      <c r="AB5">
+        <f>'DNA sequencing'!C7</f>
+        <v>0.49828884325802392</v>
+      </c>
+      <c r="AC5" s="66">
+        <f>'DNA sequencing'!J7</f>
+        <v>72.966450166975193</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD6" si="3">$B12</f>
+        <v>1.6163586584530094</v>
+      </c>
+      <c r="AE5" s="66">
+        <f t="shared" ref="AE5:AE6" si="4">$C12</f>
+        <v>1.6493911422653169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>198</v>
       </c>
       <c r="D6" s="52">
-        <f>1-('DNA sequencing'!G83/Table1[[#This Row],[Cost deflated]])^(1/('DNA sequencing'!A83-Table1[[#This Row],[Date]])*365.25/4)</f>
+        <f>1-('DNA sequencing'!G83/'DNA sequencing'!G6)^(1/('DNA sequencing'!A83-'DNA sequencing'!A6)*365.25/4)</f>
         <v>0.14155466236548164</v>
       </c>
       <c r="E6" s="52">
@@ -7940,17 +8102,57 @@
         <f t="shared" si="0"/>
         <v>4.1595283982091802</v>
       </c>
-      <c r="I6" s="63">
+      <c r="I6" s="61">
         <f t="shared" si="1"/>
         <v>1.8414054111435121</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="V6">
+        <f>Electricity!K6</f>
+        <v>10</v>
+      </c>
+      <c r="W6" s="66">
+        <f>Electricity!L6</f>
+        <v>77.924442228328303</v>
+      </c>
+      <c r="X6">
+        <f>'Lithium batteries'!D6</f>
+        <v>2</v>
+      </c>
+      <c r="Y6" s="66">
+        <f>'Lithium batteries'!F6</f>
+        <v>63.861393255108737</v>
+      </c>
+      <c r="Z6">
+        <f>Compute!M24</f>
+        <v>2</v>
+      </c>
+      <c r="AA6" s="66">
+        <f>Compute!Q24</f>
+        <v>35.11547603886779</v>
+      </c>
+      <c r="AB6">
+        <f>'DNA sequencing'!C8</f>
+        <v>0.99931553730334599</v>
+      </c>
+      <c r="AC6" s="66">
+        <f>'DNA sequencing'!J8</f>
+        <v>63.222391132945198</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="3"/>
+        <v>4.7829586584530261</v>
+      </c>
+      <c r="AE6" s="66">
+        <f t="shared" si="4"/>
+        <v>5.3075186958275811E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="48" t="s">
         <v>200</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C7" s="48" t="s">
         <v>199</v>
@@ -7971,36 +8173,166 @@
         <f>$G$7/G7</f>
         <v>1</v>
       </c>
-      <c r="I7" s="63">
+      <c r="I7" s="61">
         <f>(1-D7)^-4</f>
         <v>12.673498611808327</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="43.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="60" t="s">
-        <v>217</v>
-      </c>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
+      <c r="V7">
+        <f>Electricity!K7</f>
+        <v>15</v>
+      </c>
+      <c r="W7" s="66">
+        <f>Electricity!L7</f>
+        <v>46.036688553442083</v>
+      </c>
+      <c r="X7">
+        <f>'Lithium batteries'!D7</f>
+        <v>3</v>
+      </c>
+      <c r="Y7" s="66">
+        <f>'Lithium batteries'!F7</f>
+        <v>72.902084964219142</v>
+      </c>
+      <c r="Z7">
+        <f>Compute!M25</f>
+        <v>3</v>
+      </c>
+      <c r="AA7" s="66">
+        <f>Compute!Q25</f>
+        <v>7.8033172753900661</v>
+      </c>
+      <c r="AB7">
+        <f>'DNA sequencing'!C9</f>
+        <v>1.4976043805613699</v>
+      </c>
+      <c r="AC7" s="66">
+        <f>'DNA sequencing'!J9</f>
+        <v>54.699705192006995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="62" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" s="62"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="V8">
+        <f>Electricity!K8</f>
+        <v>20</v>
+      </c>
+      <c r="W8" s="66">
+        <f>Electricity!L8</f>
+        <v>38.533537553467681</v>
+      </c>
+      <c r="X8">
+        <f>'Lithium batteries'!D8</f>
+        <v>4</v>
+      </c>
+      <c r="Y8" s="66">
+        <f>'Lithium batteries'!F8</f>
+        <v>68.422648511492127</v>
+      </c>
+      <c r="Z8">
+        <f>Compute!M26</f>
+        <v>4</v>
+      </c>
+      <c r="AA8" s="66">
+        <f>Compute!Q26</f>
+        <v>7.8033172753900661</v>
+      </c>
+      <c r="AB8">
+        <f>'DNA sequencing'!C10</f>
+        <v>2.0835044490077053</v>
+      </c>
+      <c r="AC8" s="66">
+        <f>'DNA sequencing'!J10</f>
+        <v>40.468201668292465</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="V9">
+        <f>Electricity!K9</f>
+        <v>25</v>
+      </c>
+      <c r="W9" s="66">
+        <f>Electricity!L9</f>
+        <v>24.21568181818181</v>
+      </c>
+      <c r="X9">
+        <f>'Lithium batteries'!D9</f>
+        <v>5</v>
+      </c>
+      <c r="Y9" s="66">
+        <f>'Lithium batteries'!F9</f>
+        <v>57.629766031901482</v>
+      </c>
+      <c r="Z9">
+        <f>Compute!M27</f>
+        <v>5</v>
+      </c>
+      <c r="AA9" s="66">
+        <f>Compute!Q27</f>
+        <v>7.8033172753900661</v>
+      </c>
+      <c r="AB9">
+        <f>'DNA sequencing'!C11</f>
+        <v>2.3353867214236743</v>
+      </c>
+      <c r="AC9" s="66">
+        <f>'DNA sequencing'!J11</f>
+        <v>28.73892560087431</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C10" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="V10">
+        <f>Electricity!K10</f>
+        <v>30</v>
+      </c>
+      <c r="W10" s="66">
+        <f>Electricity!L10</f>
+        <v>18.106558441558441</v>
+      </c>
+      <c r="X10">
+        <f>'Lithium batteries'!D10</f>
+        <v>6</v>
+      </c>
+      <c r="Y10" s="66">
+        <f>'Lithium batteries'!F10</f>
+        <v>49.3504776753675</v>
+      </c>
+      <c r="Z10">
+        <f>Compute!M28</f>
+        <v>6</v>
+      </c>
+      <c r="AA10" s="66">
+        <f>Compute!Q28</f>
+        <v>4.6382056926548554</v>
+      </c>
+      <c r="AB10">
+        <f>'DNA sequencing'!C12</f>
+        <v>2.5817932922657292</v>
+      </c>
+      <c r="AC10" s="66">
+        <f>'DNA sequencing'!J12</f>
+        <v>20.250436288913715</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="6">
         <f>DATEVALUE("2021-11-18")/365.25+1900</f>
         <v>2021.883641341547</v>
@@ -8012,8 +8344,40 @@
       <c r="C11" s="55">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="V11">
+        <f>Electricity!K11</f>
+        <v>34</v>
+      </c>
+      <c r="W11" s="66">
+        <f>Electricity!L11</f>
+        <v>16.300975860297893</v>
+      </c>
+      <c r="X11">
+        <f>'Lithium batteries'!D11</f>
+        <v>7</v>
+      </c>
+      <c r="Y11" s="66">
+        <f>'Lithium batteries'!F11</f>
+        <v>39.704364603272666</v>
+      </c>
+      <c r="Z11">
+        <f>Compute!M29</f>
+        <v>7</v>
+      </c>
+      <c r="AA11" s="66">
+        <f>Compute!Q29</f>
+        <v>4.6382056926548554</v>
+      </c>
+      <c r="AB11">
+        <f>'DNA sequencing'!C13</f>
+        <v>2.8336755646816982</v>
+      </c>
+      <c r="AC11" s="66">
+        <f>'DNA sequencing'!J13</f>
+        <v>19.64261179806801</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="6">
         <v>2023.5</v>
       </c>
@@ -8022,11 +8386,43 @@
         <v>1.6163586584530094</v>
       </c>
       <c r="C12" s="5">
-        <f>$C$11*(1-47%)^(4*(A12-$A$11))</f>
+        <f>$C$11*(1-$D$7)^(4*(A12-$A$11))</f>
         <v>1.6493911422653169</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="V12">
+        <f>Electricity!K12</f>
+        <v>35</v>
+      </c>
+      <c r="W12" s="66">
+        <f>Electricity!L12</f>
+        <v>16.155632183908043</v>
+      </c>
+      <c r="X12">
+        <f>'Lithium batteries'!D12</f>
+        <v>8</v>
+      </c>
+      <c r="Y12" s="66">
+        <f>'Lithium batteries'!F12</f>
+        <v>30.073870033647371</v>
+      </c>
+      <c r="Z12">
+        <f>Compute!M30</f>
+        <v>8</v>
+      </c>
+      <c r="AA12" s="66">
+        <f>Compute!Q30</f>
+        <v>4.6382056926548554</v>
+      </c>
+      <c r="AB12">
+        <f>'DNA sequencing'!C14</f>
+        <v>3.0855578370978947</v>
+      </c>
+      <c r="AC12" s="66">
+        <f>'DNA sequencing'!J14</f>
+        <v>18.010307127461044</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="6">
         <v>2026.6666</v>
       </c>
@@ -8035,8 +8431,1632 @@
         <v>4.7829586584530261</v>
       </c>
       <c r="C13" s="5">
-        <f>$C$11*(1-47%)^(4*(A13-$A$11))</f>
+        <f>$C$11*(1-$D$7)^(4*(A13-$A$11))</f>
         <v>5.3075186958275811E-4</v>
+      </c>
+      <c r="V13">
+        <f>Electricity!K13</f>
+        <v>36</v>
+      </c>
+      <c r="W13" s="66">
+        <f>Electricity!L13</f>
+        <v>15.98108452950558</v>
+      </c>
+      <c r="X13">
+        <f>'Lithium batteries'!D13</f>
+        <v>9</v>
+      </c>
+      <c r="Y13" s="66">
+        <f>'Lithium batteries'!F13</f>
+        <v>29.213463724575828</v>
+      </c>
+      <c r="Z13">
+        <f>Compute!M31</f>
+        <v>9</v>
+      </c>
+      <c r="AA13" s="66">
+        <f>Compute!Q31</f>
+        <v>0.57840715825846489</v>
+      </c>
+      <c r="AB13">
+        <f>'DNA sequencing'!C15</f>
+        <v>3.3374401095140911</v>
+      </c>
+      <c r="AC13" s="66">
+        <f>'DNA sequencing'!J15</f>
+        <v>16.990976065198431</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="V14">
+        <f>Electricity!K14</f>
+        <v>37</v>
+      </c>
+      <c r="W14" s="66">
+        <f>Electricity!L14</f>
+        <v>15.257958532695373</v>
+      </c>
+      <c r="X14">
+        <f>'Lithium batteries'!D14</f>
+        <v>10</v>
+      </c>
+      <c r="Y14" s="66">
+        <f>'Lithium batteries'!F14</f>
+        <v>20.390688397575303</v>
+      </c>
+      <c r="Z14">
+        <f>Compute!M32</f>
+        <v>10</v>
+      </c>
+      <c r="AA14" s="66">
+        <f>Compute!Q32</f>
+        <v>0.57840715825846489</v>
+      </c>
+      <c r="AB14">
+        <f>'DNA sequencing'!C16</f>
+        <v>3.5811088295688478</v>
+      </c>
+      <c r="AC14" s="66">
+        <f>'DNA sequencing'!J16</f>
+        <v>15.56131540651009</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="V15">
+        <f>Electricity!K15</f>
+        <v>38</v>
+      </c>
+      <c r="W15" s="66">
+        <f>Electricity!L15</f>
+        <v>14.882972237343495</v>
+      </c>
+      <c r="X15">
+        <f>'Lithium batteries'!D15</f>
+        <v>11</v>
+      </c>
+      <c r="Y15" s="66">
+        <f>'Lithium batteries'!F15</f>
+        <v>14.609075994844863</v>
+      </c>
+      <c r="Z15">
+        <f>Compute!M33</f>
+        <v>11</v>
+      </c>
+      <c r="AA15" s="66">
+        <f>Compute!Q33</f>
+        <v>0.57840715825846489</v>
+      </c>
+      <c r="AB15">
+        <f>'DNA sequencing'!C17</f>
+        <v>3.8329911019850442</v>
+      </c>
+      <c r="AC15" s="66">
+        <f>'DNA sequencing'!J17</f>
+        <v>15.382443136010684</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="V16">
+        <f>Electricity!K16</f>
+        <v>39</v>
+      </c>
+      <c r="W16" s="66">
+        <f>Electricity!L16</f>
+        <v>15.673755980861243</v>
+      </c>
+      <c r="X16">
+        <f>'Lithium batteries'!D16</f>
+        <v>12</v>
+      </c>
+      <c r="Y16" s="66">
+        <f>'Lithium batteries'!F16</f>
+        <v>11.295786315868334</v>
+      </c>
+      <c r="Z16">
+        <f>Compute!M34</f>
+        <v>12</v>
+      </c>
+      <c r="AA16" s="66">
+        <f>Compute!Q34</f>
+        <v>0.57840715825846489</v>
+      </c>
+      <c r="AB16">
+        <f>'DNA sequencing'!C18</f>
+        <v>4.0848733744012407</v>
+      </c>
+      <c r="AC16" s="66">
+        <f>'DNA sequencing'!J18</f>
+        <v>12.988182068984196</v>
+      </c>
+    </row>
+    <row r="17" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V17">
+        <f>Electricity!K17</f>
+        <v>40</v>
+      </c>
+      <c r="W17" s="66">
+        <f>Electricity!L17</f>
+        <v>16.878394160583941</v>
+      </c>
+      <c r="X17">
+        <f>'Lithium batteries'!D17</f>
+        <v>13</v>
+      </c>
+      <c r="Y17" s="66">
+        <f>'Lithium batteries'!F17</f>
+        <v>10.107282119990488</v>
+      </c>
+      <c r="Z17">
+        <f>Compute!M35</f>
+        <v>13</v>
+      </c>
+      <c r="AA17" s="66">
+        <f>Compute!Q35</f>
+        <v>0.11894462989462484</v>
+      </c>
+      <c r="AB17">
+        <f>'DNA sequencing'!C19</f>
+        <v>4.3367556468174371</v>
+      </c>
+      <c r="AC17" s="66">
+        <f>'DNA sequencing'!J19</f>
+        <v>11.76709291497095</v>
+      </c>
+    </row>
+    <row r="18" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V18">
+        <f>Electricity!K18</f>
+        <v>41</v>
+      </c>
+      <c r="W18" s="66">
+        <f>Electricity!L18</f>
+        <v>17.501874125874121</v>
+      </c>
+      <c r="X18">
+        <f>'Lithium batteries'!D18</f>
+        <v>14</v>
+      </c>
+      <c r="Y18" s="66">
+        <f>'Lithium batteries'!F18</f>
+        <v>8.7135380983971089</v>
+      </c>
+      <c r="Z18">
+        <f>Compute!M36</f>
+        <v>14</v>
+      </c>
+      <c r="AA18" s="66">
+        <f>Compute!Q36</f>
+        <v>0.11894462989462484</v>
+      </c>
+      <c r="AB18">
+        <f>'DNA sequencing'!C20</f>
+        <v>4.5804243668721938</v>
+      </c>
+      <c r="AC18" s="66">
+        <f>'DNA sequencing'!J20</f>
+        <v>10.865918549877641</v>
+      </c>
+    </row>
+    <row r="19" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V19">
+        <f>Electricity!K19</f>
+        <v>42</v>
+      </c>
+      <c r="W19" s="66">
+        <f>Electricity!L19</f>
+        <v>16.394993215739483</v>
+      </c>
+      <c r="X19">
+        <f>'Lithium batteries'!D19</f>
+        <v>15</v>
+      </c>
+      <c r="Y19" s="66">
+        <f>'Lithium batteries'!F19</f>
+        <v>7.4623091931471857</v>
+      </c>
+      <c r="Z19">
+        <f>Compute!M37</f>
+        <v>15</v>
+      </c>
+      <c r="AA19" s="66">
+        <f>Compute!Q37</f>
+        <v>3.9869035438097035E-2</v>
+      </c>
+      <c r="AB19">
+        <f>'DNA sequencing'!C21</f>
+        <v>4.8323066392881628</v>
+      </c>
+      <c r="AC19" s="66">
+        <f>'DNA sequencing'!J21</f>
+        <v>10.479033872157595</v>
+      </c>
+    </row>
+    <row r="20" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V20">
+        <f>Electricity!K20</f>
+        <v>43</v>
+      </c>
+      <c r="W20" s="66">
+        <f>Electricity!L20</f>
+        <v>15.073218314532181</v>
+      </c>
+      <c r="X20">
+        <f>'Lithium batteries'!D20</f>
+        <v>16</v>
+      </c>
+      <c r="Y20" s="66">
+        <f>'Lithium batteries'!F20</f>
+        <v>7.1207342270497049</v>
+      </c>
+      <c r="Z20">
+        <f>Compute!M38</f>
+        <v>18</v>
+      </c>
+      <c r="AA20" s="66">
+        <f>Compute!Q38</f>
+        <v>3.9869035438097035E-2</v>
+      </c>
+      <c r="AB20">
+        <f>'DNA sequencing'!C22</f>
+        <v>5.0841889117043593</v>
+      </c>
+      <c r="AC20" s="66">
+        <f>'DNA sequencing'!J22</f>
+        <v>9.6672432806743718</v>
+      </c>
+    </row>
+    <row r="21" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V21">
+        <f>Electricity!K21</f>
+        <v>44</v>
+      </c>
+      <c r="W21" s="66">
+        <f>Electricity!L21</f>
+        <v>13.848122956180505</v>
+      </c>
+      <c r="X21">
+        <f>'Lithium batteries'!D21</f>
+        <v>17</v>
+      </c>
+      <c r="Y21" s="66">
+        <f>'Lithium batteries'!F21</f>
+        <v>7.4662293992658171</v>
+      </c>
+      <c r="Z21">
+        <f>Compute!M39</f>
+        <v>19</v>
+      </c>
+      <c r="AA21" s="66">
+        <f>Compute!Q39</f>
+        <v>3.9869035438097035E-2</v>
+      </c>
+      <c r="AB21">
+        <f>'DNA sequencing'!C23</f>
+        <v>5.3360711841205557</v>
+      </c>
+      <c r="AC21" s="66">
+        <f>'DNA sequencing'!J23</f>
+        <v>8.5889241079984053</v>
+      </c>
+    </row>
+    <row r="22" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V22">
+        <f>Electricity!K22</f>
+        <v>45</v>
+      </c>
+      <c r="W22" s="66">
+        <f>Electricity!L22</f>
+        <v>12.279583333333331</v>
+      </c>
+      <c r="X22">
+        <f>'Lithium batteries'!D22</f>
+        <v>18</v>
+      </c>
+      <c r="Y22" s="66">
+        <f>'Lithium batteries'!F22</f>
+        <v>6.6510416135101948</v>
+      </c>
+      <c r="Z22">
+        <f>Compute!M40</f>
+        <v>20</v>
+      </c>
+      <c r="AA22" s="66">
+        <f>Compute!Q40</f>
+        <v>1.4230696120937077E-2</v>
+      </c>
+      <c r="AB22">
+        <f>'DNA sequencing'!C24</f>
+        <v>5.5797399041753124</v>
+      </c>
+      <c r="AC22" s="66">
+        <f>'DNA sequencing'!J24</f>
+        <v>8.1576880020311346</v>
+      </c>
+    </row>
+    <row r="23" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V23">
+        <f>Electricity!K23</f>
+        <v>46</v>
+      </c>
+      <c r="W23" s="66">
+        <f>Electricity!L23</f>
+        <v>12.102359767891679</v>
+      </c>
+      <c r="X23">
+        <f>'Lithium batteries'!D23</f>
+        <v>19</v>
+      </c>
+      <c r="Y23" s="66">
+        <f>'Lithium batteries'!F23</f>
+        <v>5.9794450301458273</v>
+      </c>
+      <c r="Z23">
+        <f>Compute!M41</f>
+        <v>21</v>
+      </c>
+      <c r="AA23" s="66">
+        <f>Compute!Q41</f>
+        <v>1.3078890527653684E-2</v>
+      </c>
+      <c r="AB23">
+        <f>'DNA sequencing'!C25</f>
+        <v>5.8316221765915088</v>
+      </c>
+      <c r="AC23" s="66">
+        <f>'DNA sequencing'!J25</f>
+        <v>8.0144379342313012</v>
+      </c>
+    </row>
+    <row r="24" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V24">
+        <f>Electricity!K24</f>
+        <v>47</v>
+      </c>
+      <c r="W24" s="66">
+        <f>Electricity!L24</f>
+        <v>11.861347285807716</v>
+      </c>
+      <c r="X24">
+        <f>'Lithium batteries'!D24</f>
+        <v>20</v>
+      </c>
+      <c r="Y24" s="66">
+        <f>'Lithium batteries'!F24</f>
+        <v>5.6958182368952777</v>
+      </c>
+      <c r="Z24">
+        <f>Compute!M42</f>
+        <v>22</v>
+      </c>
+      <c r="AA24" s="66">
+        <f>Compute!Q42</f>
+        <v>1.3078890527653684E-2</v>
+      </c>
+      <c r="AB24">
+        <f>'DNA sequencing'!C26</f>
+        <v>6.0835044490077053</v>
+      </c>
+      <c r="AC24" s="66">
+        <f>'DNA sequencing'!J26</f>
+        <v>6.3202787487277767</v>
+      </c>
+    </row>
+    <row r="25" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V25">
+        <f>Electricity!K25</f>
+        <v>48</v>
+      </c>
+      <c r="W25" s="66">
+        <f>Electricity!L25</f>
+        <v>11.305558441558441</v>
+      </c>
+      <c r="X25">
+        <f>'Lithium batteries'!D25</f>
+        <v>21</v>
+      </c>
+      <c r="Y25" s="66">
+        <f>'Lithium batteries'!F25</f>
+        <v>5.8597070865765568</v>
+      </c>
+      <c r="Z25">
+        <f>Compute!M43</f>
+        <v>23</v>
+      </c>
+      <c r="AA25" s="66">
+        <f>Compute!Q43</f>
+        <v>1.3078890527653684E-2</v>
+      </c>
+      <c r="AB25">
+        <f>'DNA sequencing'!C27</f>
+        <v>6.3353867214236743</v>
+      </c>
+      <c r="AC25" s="66">
+        <f>'DNA sequencing'!J27</f>
+        <v>2.6855959871058328</v>
+      </c>
+    </row>
+    <row r="26" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V26">
+        <f>Electricity!K26</f>
+        <v>49</v>
+      </c>
+      <c r="W26" s="66">
+        <f>Electricity!L26</f>
+        <v>10.458763141620283</v>
+      </c>
+      <c r="X26">
+        <f>'Lithium batteries'!D26</f>
+        <v>22</v>
+      </c>
+      <c r="Y26" s="66">
+        <f>'Lithium batteries'!F26</f>
+        <v>5.3298723267497126</v>
+      </c>
+      <c r="Z26">
+        <f>Compute!M44</f>
+        <v>24</v>
+      </c>
+      <c r="AA26" s="66">
+        <f>Compute!Q44</f>
+        <v>4.4641876916147174E-3</v>
+      </c>
+      <c r="AB26">
+        <f>'DNA sequencing'!C28</f>
+        <v>6.5817932922657292</v>
+      </c>
+      <c r="AC26" s="66">
+        <f>'DNA sequencing'!J28</f>
+        <v>1.1720659796107069</v>
+      </c>
+    </row>
+    <row r="27" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V27">
+        <f>Electricity!K27</f>
+        <v>50</v>
+      </c>
+      <c r="W27" s="66">
+        <f>Electricity!L27</f>
+        <v>9.3056999442275501</v>
+      </c>
+      <c r="X27">
+        <f>'Lithium batteries'!D27</f>
+        <v>23</v>
+      </c>
+      <c r="Y27" s="66">
+        <f>'Lithium batteries'!F27</f>
+        <v>4.715082033782001</v>
+      </c>
+      <c r="Z27">
+        <f>Compute!M45</f>
+        <v>25</v>
+      </c>
+      <c r="AA27" s="66">
+        <f>Compute!Q45</f>
+        <v>4.4641876916147174E-3</v>
+      </c>
+      <c r="AB27">
+        <f>'DNA sequencing'!C29</f>
+        <v>6.8336755646816982</v>
+      </c>
+      <c r="AC27" s="66">
+        <f>'DNA sequencing'!J29</f>
+        <v>0.64114083441616443</v>
+      </c>
+    </row>
+    <row r="28" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V28">
+        <f>Electricity!K28</f>
+        <v>51</v>
+      </c>
+      <c r="W28" s="66">
+        <f>Electricity!L28</f>
+        <v>8.5771939043615344</v>
+      </c>
+      <c r="X28">
+        <f>'Lithium batteries'!D28</f>
+        <v>24</v>
+      </c>
+      <c r="Y28" s="66">
+        <f>'Lithium batteries'!F28</f>
+        <v>3.6040658050884722</v>
+      </c>
+      <c r="Z28">
+        <f>Compute!M46</f>
+        <v>26</v>
+      </c>
+      <c r="AA28" s="66">
+        <f>Compute!Q46</f>
+        <v>4.4641876916147174E-3</v>
+      </c>
+      <c r="AB28">
+        <f>'DNA sequencing'!C30</f>
+        <v>7.0855578370978947</v>
+      </c>
+      <c r="AC28" s="66">
+        <f>'DNA sequencing'!J30</f>
+        <v>0.29956434297798684</v>
+      </c>
+    </row>
+    <row r="29" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V29">
+        <f>Electricity!K29</f>
+        <v>52</v>
+      </c>
+      <c r="W29" s="66">
+        <f>Electricity!L29</f>
+        <v>8.2202169421487579</v>
+      </c>
+      <c r="X29">
+        <f>'Lithium batteries'!D29</f>
+        <v>25</v>
+      </c>
+      <c r="Y29" s="66">
+        <f>'Lithium batteries'!F29</f>
+        <v>2.8120904689676589</v>
+      </c>
+      <c r="Z29">
+        <f>Compute!M47</f>
+        <v>27</v>
+      </c>
+      <c r="AA29" s="66">
+        <f>Compute!Q47</f>
+        <v>4.4641876916147174E-3</v>
+      </c>
+      <c r="AB29">
+        <f>'DNA sequencing'!C31</f>
+        <v>7.3374401095140911</v>
+      </c>
+      <c r="AC29" s="66">
+        <f>'DNA sequencing'!J31</f>
+        <v>0.20398733178367293</v>
+      </c>
+    </row>
+    <row r="30" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V30">
+        <f>Electricity!K30</f>
+        <v>53</v>
+      </c>
+      <c r="W30" s="66">
+        <f>Electricity!L30</f>
+        <v>7.8085555555555537</v>
+      </c>
+      <c r="X30">
+        <f>'Lithium batteries'!D30</f>
+        <v>26</v>
+      </c>
+      <c r="Y30" s="66">
+        <f>'Lithium batteries'!F30</f>
+        <v>2.0303510335789658</v>
+      </c>
+      <c r="Z30">
+        <f>Compute!M48</f>
+        <v>29</v>
+      </c>
+      <c r="AA30" s="66">
+        <f>Compute!Q48</f>
+        <v>2.3236862295869746E-3</v>
+      </c>
+      <c r="AB30">
+        <f>'DNA sequencing'!C32</f>
+        <v>7.5811088295688478</v>
+      </c>
+      <c r="AC30" s="66">
+        <f>'DNA sequencing'!J32</f>
+        <v>0.13540116803166066</v>
+      </c>
+    </row>
+    <row r="31" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V31">
+        <f>Electricity!K31</f>
+        <v>54</v>
+      </c>
+      <c r="W31" s="66">
+        <f>Electricity!L31</f>
+        <v>6.8062843822843817</v>
+      </c>
+      <c r="X31">
+        <f>'Lithium batteries'!D31</f>
+        <v>27</v>
+      </c>
+      <c r="Y31" s="66">
+        <f>'Lithium batteries'!F31</f>
+        <v>1.7046262688336773</v>
+      </c>
+      <c r="Z31">
+        <f>Compute!M49</f>
+        <v>30</v>
+      </c>
+      <c r="AA31" s="66">
+        <f>Compute!Q49</f>
+        <v>2.3236862295869746E-3</v>
+      </c>
+      <c r="AB31">
+        <f>'DNA sequencing'!C33</f>
+        <v>7.8329911019850442</v>
+      </c>
+      <c r="AC31" s="66">
+        <f>'DNA sequencing'!J33</f>
+        <v>9.351205005827852E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V32">
+        <f>Electricity!K32</f>
+        <v>55</v>
+      </c>
+      <c r="W32" s="66">
+        <f>Electricity!L32</f>
+        <v>5.7113982878108427</v>
+      </c>
+      <c r="X32">
+        <f>'Lithium batteries'!D32</f>
+        <v>28</v>
+      </c>
+      <c r="Y32" s="66">
+        <f>'Lithium batteries'!F32</f>
+        <v>1.4331889648792702</v>
+      </c>
+      <c r="Z32">
+        <f>Compute!M50</f>
+        <v>31</v>
+      </c>
+      <c r="AA32" s="66">
+        <f>Compute!Q50</f>
+        <v>2.3236862295869746E-3</v>
+      </c>
+      <c r="AB32">
+        <f>'DNA sequencing'!C34</f>
+        <v>8.0848733744012407</v>
+      </c>
+      <c r="AC32" s="66">
+        <f>'DNA sequencing'!J34</f>
+        <v>6.0360355326899352E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V33">
+        <f>Electricity!K33</f>
+        <v>56</v>
+      </c>
+      <c r="W33" s="66">
+        <f>Electricity!L33</f>
+        <v>5.1479969822708398</v>
+      </c>
+      <c r="X33">
+        <f>'Lithium batteries'!D33</f>
+        <v>29</v>
+      </c>
+      <c r="Y33" s="66">
+        <f>'Lithium batteries'!F33</f>
+        <v>1.3354715354556836</v>
+      </c>
+      <c r="Z33">
+        <f>Compute!M51</f>
+        <v>32</v>
+      </c>
+      <c r="AA33" s="66">
+        <f>Compute!Q51</f>
+        <v>2.3236862295869746E-3</v>
+      </c>
+      <c r="AB33">
+        <f>'DNA sequencing'!C35</f>
+        <v>8.3367556468174371</v>
+      </c>
+      <c r="AC33" s="66">
+        <f>'DNA sequencing'!J35</f>
+        <v>4.0133189210794687E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V34">
+        <f>Electricity!K34</f>
+        <v>57</v>
+      </c>
+      <c r="W34" s="66">
+        <f>Electricity!L34</f>
+        <v>5.1089763177998471</v>
+      </c>
+      <c r="X34">
+        <f>'Lithium batteries'!D34</f>
+        <v>30</v>
+      </c>
+      <c r="Y34" s="66">
+        <f>'Lithium batteries'!F34</f>
+        <v>1.2920415668229785</v>
+      </c>
+      <c r="Z34">
+        <f>Compute!M52</f>
+        <v>33</v>
+      </c>
+      <c r="AA34" s="66">
+        <f>Compute!Q52</f>
+        <v>2.3236862295869746E-3</v>
+      </c>
+      <c r="AB34">
+        <f>'DNA sequencing'!C36</f>
+        <v>8.5804243668721938</v>
+      </c>
+      <c r="AC34" s="66">
+        <f>'DNA sequencing'!J36</f>
+        <v>2.7036791526076815E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V35">
+        <f>Electricity!K35</f>
+        <v>58</v>
+      </c>
+      <c r="W35" s="66">
+        <f>Electricity!L35</f>
+        <v>4.925658242172763</v>
+      </c>
+      <c r="X35">
+        <f>'Lithium batteries'!D35</f>
+        <v>31</v>
+      </c>
+      <c r="Y35" s="66">
+        <f>'Lithium batteries'!F35</f>
+        <v>1.4331889648792702</v>
+      </c>
+      <c r="Z35">
+        <f>Compute!M53</f>
+        <v>35</v>
+      </c>
+      <c r="AA35" s="66">
+        <f>Compute!Q53</f>
+        <v>2.3236862295869746E-3</v>
+      </c>
+      <c r="AB35">
+        <f>'DNA sequencing'!C37</f>
+        <v>8.8323066392881628</v>
+      </c>
+      <c r="AC35" s="66">
+        <f>'DNA sequencing'!J37</f>
+        <v>2.662711554270181E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V36">
+        <f>Electricity!K36</f>
+        <v>59</v>
+      </c>
+      <c r="W36" s="66">
+        <f>Electricity!L36</f>
+        <v>4.454734265734265</v>
+      </c>
+      <c r="X36">
+        <f>'Lithium batteries'!D36</f>
+        <v>32</v>
+      </c>
+      <c r="Y36" s="66">
+        <f>'Lithium batteries'!F36</f>
+        <v>1.2051816295575681</v>
+      </c>
+      <c r="Z36">
+        <f>Compute!M54</f>
+        <v>36</v>
+      </c>
+      <c r="AA36" s="66">
+        <f>Compute!Q54</f>
+        <v>3.161819275679901E-4</v>
+      </c>
+      <c r="AB36">
+        <f>'DNA sequencing'!C38</f>
+        <v>9.0841889117043593</v>
+      </c>
+      <c r="AC36" s="66">
+        <f>'DNA sequencing'!J38</f>
+        <v>2.4698775629687982E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V37">
+        <f>Electricity!K37</f>
+        <v>60</v>
+      </c>
+      <c r="W37" s="66">
+        <f>Electricity!L37</f>
+        <v>4.3084665523156085</v>
+      </c>
+      <c r="X37">
+        <f>'Lithium batteries'!D37</f>
+        <v>33</v>
+      </c>
+      <c r="Y37" s="66">
+        <f>'Lithium batteries'!F37</f>
+        <v>0.84688438833775048</v>
+      </c>
+      <c r="Z37">
+        <f>Compute!M55</f>
+        <v>37</v>
+      </c>
+      <c r="AA37" s="66">
+        <f>Compute!Q55</f>
+        <v>7.2772030948188199E-5</v>
+      </c>
+      <c r="AB37">
+        <f>'DNA sequencing'!C39</f>
+        <v>9.3360711841205557</v>
+      </c>
+      <c r="AC37" s="66">
+        <f>'DNA sequencing'!J39</f>
+        <v>1.7612212416533383E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V38">
+        <f>Electricity!K38</f>
+        <v>61</v>
+      </c>
+      <c r="W38" s="66">
+        <f>Electricity!L38</f>
+        <v>4.2298808307797069</v>
+      </c>
+      <c r="Z38">
+        <f>Compute!M56</f>
+        <v>38</v>
+      </c>
+      <c r="AA38" s="66">
+        <f>Compute!Q56</f>
+        <v>7.2772030948188199E-5</v>
+      </c>
+      <c r="AB38">
+        <f>'DNA sequencing'!C40</f>
+        <v>9.5797399041753124</v>
+      </c>
+      <c r="AC38" s="66">
+        <f>'DNA sequencing'!J40</f>
+        <v>1.3859234684711133E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V39">
+        <f>Electricity!K39</f>
+        <v>62</v>
+      </c>
+      <c r="W39" s="66">
+        <f>Electricity!L39</f>
+        <v>4.1218181818181812</v>
+      </c>
+      <c r="Z39">
+        <f>Compute!M57</f>
+        <v>40</v>
+      </c>
+      <c r="AA39" s="66">
+        <f>Compute!Q57</f>
+        <v>7.2772030948188199E-5</v>
+      </c>
+      <c r="AB39">
+        <f>'DNA sequencing'!C41</f>
+        <v>9.8316221765915088</v>
+      </c>
+      <c r="AC39" s="66">
+        <f>'DNA sequencing'!J41</f>
+        <v>8.6550335982576426E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V40">
+        <f>Electricity!K40</f>
+        <v>63</v>
+      </c>
+      <c r="W40" s="66">
+        <f>Electricity!L40</f>
+        <v>4.0602985074626865</v>
+      </c>
+      <c r="Z40">
+        <f>Compute!M58</f>
+        <v>42</v>
+      </c>
+      <c r="AA40" s="66">
+        <f>Compute!Q58</f>
+        <v>1.2546901887618654E-5</v>
+      </c>
+      <c r="AB40">
+        <f>'DNA sequencing'!C42</f>
+        <v>10.080766598220407</v>
+      </c>
+      <c r="AC40" s="66">
+        <f>'DNA sequencing'!J42</f>
+        <v>6.3548184017738268E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V41">
+        <f>Electricity!K41</f>
+        <v>64</v>
+      </c>
+      <c r="W41" s="66">
+        <f>Electricity!L41</f>
+        <v>3.9399732620320855</v>
+      </c>
+      <c r="Z41">
+        <f>Compute!M59</f>
+        <v>43</v>
+      </c>
+      <c r="AA41" s="66">
+        <f>Compute!Q59</f>
+        <v>1.2546901887618654E-5</v>
+      </c>
+      <c r="AB41">
+        <f>'DNA sequencing'!C43</f>
+        <v>10.335386721423674</v>
+      </c>
+      <c r="AC41" s="66">
+        <f>'DNA sequencing'!J43</f>
+        <v>6.259483926466778E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V42">
+        <f>Electricity!K42</f>
+        <v>65</v>
+      </c>
+      <c r="W42" s="66">
+        <f>Electricity!L42</f>
+        <v>3.7551083791653181</v>
+      </c>
+      <c r="Z42">
+        <f>Compute!M60</f>
+        <v>44</v>
+      </c>
+      <c r="AA42" s="66">
+        <f>Compute!Q60</f>
+        <v>1.2546901887618654E-5</v>
+      </c>
+      <c r="AB42">
+        <f>'DNA sequencing'!C44</f>
+        <v>10.581793292265729</v>
+      </c>
+      <c r="AC42" s="66">
+        <f>'DNA sequencing'!J44</f>
+        <v>4.8103278850098871E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V43">
+        <f>Electricity!K43</f>
+        <v>66</v>
+      </c>
+      <c r="W43" s="66">
+        <f>Electricity!L43</f>
+        <v>3.6083737024221443</v>
+      </c>
+      <c r="Z43">
+        <f>Compute!M61</f>
+        <v>45</v>
+      </c>
+      <c r="AA43" s="66">
+        <f>Compute!Q61</f>
+        <v>1.2546901887618654E-5</v>
+      </c>
+      <c r="AB43">
+        <f>'DNA sequencing'!C45</f>
+        <v>10.833675564681698</v>
+      </c>
+      <c r="AC43" s="66">
+        <f>'DNA sequencing'!J45</f>
+        <v>4.85276588713253E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V44">
+        <f>Electricity!K44</f>
+        <v>67</v>
+      </c>
+      <c r="W44" s="66">
+        <f>Electricity!L44</f>
+        <v>3.541080912214932</v>
+      </c>
+      <c r="Z44">
+        <f>Compute!M62</f>
+        <v>46</v>
+      </c>
+      <c r="AA44" s="66">
+        <f>Compute!Q62</f>
+        <v>2.509380377523731E-6</v>
+      </c>
+      <c r="AB44">
+        <f>'DNA sequencing'!C46</f>
+        <v>11.085557837097895</v>
+      </c>
+      <c r="AC44" s="66">
+        <f>'DNA sequencing'!J46</f>
+        <v>5.3356606328380223E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V45">
+        <f>Electricity!K45</f>
+        <v>68</v>
+      </c>
+      <c r="W45" s="66">
+        <f>Electricity!L45</f>
+        <v>3.4394901719901712</v>
+      </c>
+      <c r="Z45">
+        <f>Compute!M63</f>
+        <v>47</v>
+      </c>
+      <c r="AA45" s="66">
+        <f>Compute!Q63</f>
+        <v>2.509380377523731E-6</v>
+      </c>
+      <c r="AB45">
+        <f>'DNA sequencing'!C47</f>
+        <v>11.337440109514091</v>
+      </c>
+      <c r="AC45" s="66">
+        <f>'DNA sequencing'!J47</f>
+        <v>4.5390613351393473E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V46">
+        <f>Electricity!K46</f>
+        <v>69</v>
+      </c>
+      <c r="W46" s="66">
+        <f>Electricity!L46</f>
+        <v>3.3774095469747647</v>
+      </c>
+      <c r="Z46">
+        <f>Compute!M64</f>
+        <v>48</v>
+      </c>
+      <c r="AA46" s="66">
+        <f>Compute!Q64</f>
+        <v>4.7678227172950892E-7</v>
+      </c>
+      <c r="AB46">
+        <f>'DNA sequencing'!C48</f>
+        <v>11.581108829568848</v>
+      </c>
+      <c r="AC46" s="66">
+        <f>'DNA sequencing'!J48</f>
+        <v>4.4621528929781468E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V47">
+        <f>Electricity!K47</f>
+        <v>70</v>
+      </c>
+      <c r="W47" s="66">
+        <f>Electricity!L47</f>
+        <v>3.2892655027092115</v>
+      </c>
+      <c r="Z47">
+        <f>Compute!M65</f>
+        <v>50</v>
+      </c>
+      <c r="AA47" s="66">
+        <f>Compute!Q65</f>
+        <v>4.7678227172950892E-7</v>
+      </c>
+      <c r="AB47">
+        <f>'DNA sequencing'!C49</f>
+        <v>11.832991101985044</v>
+      </c>
+      <c r="AC47" s="66">
+        <f>'DNA sequencing'!J49</f>
+        <v>4.432278548469012E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V48">
+        <f>Electricity!K48</f>
+        <v>71</v>
+      </c>
+      <c r="W48" s="66">
+        <f>Electricity!L48</f>
+        <v>3.1923885918003561</v>
+      </c>
+      <c r="Z48">
+        <f>Compute!M66</f>
+        <v>51</v>
+      </c>
+      <c r="AA48" s="66">
+        <f>Compute!Q66</f>
+        <v>1.5056282265142386E-7</v>
+      </c>
+      <c r="AB48">
+        <f>'DNA sequencing'!C50</f>
+        <v>12.084873374401241</v>
+      </c>
+      <c r="AC48" s="66">
+        <f>'DNA sequencing'!J50</f>
+        <v>4.0583822454023444E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V49">
+        <f>Electricity!K49</f>
+        <v>72</v>
+      </c>
+      <c r="W49" s="66">
+        <f>Electricity!L49</f>
+        <v>3.0714193548387092</v>
+      </c>
+      <c r="Z49">
+        <f>Compute!M67</f>
+        <v>52</v>
+      </c>
+      <c r="AA49" s="66">
+        <f>Compute!Q67</f>
+        <v>1.5056282265142386E-7</v>
+      </c>
+      <c r="AB49">
+        <f>'DNA sequencing'!C51</f>
+        <v>12.336755646817437</v>
+      </c>
+      <c r="AC49" s="66">
+        <f>'DNA sequencing'!J51</f>
+        <v>3.1723427881520981E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V50">
+        <f>Electricity!K50</f>
+        <v>73</v>
+      </c>
+      <c r="W50" s="66">
+        <f>Electricity!L50</f>
+        <v>2.9441558441558433</v>
+      </c>
+      <c r="Z50">
+        <f>Compute!M68</f>
+        <v>53</v>
+      </c>
+      <c r="AA50" s="66">
+        <f>Compute!Q68</f>
+        <v>5.0187607550474612E-8</v>
+      </c>
+      <c r="AB50">
+        <f>'DNA sequencing'!C52</f>
+        <v>12.580424366872194</v>
+      </c>
+      <c r="AC50" s="66">
+        <f>'DNA sequencing'!J52</f>
+        <v>3.8719458844008944E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V51">
+        <f>Electricity!K51</f>
+        <v>74</v>
+      </c>
+      <c r="W51" s="66">
+        <f>Electricity!L51</f>
+        <v>2.7987654320987652</v>
+      </c>
+      <c r="Z51">
+        <f>Compute!M69</f>
+        <v>54</v>
+      </c>
+      <c r="AA51" s="66">
+        <f>Compute!Q69</f>
+        <v>2.5093803775237306E-8</v>
+      </c>
+      <c r="AB51">
+        <f>'DNA sequencing'!C53</f>
+        <v>12.832306639288163</v>
+      </c>
+      <c r="AC51" s="66">
+        <f>'DNA sequencing'!J53</f>
+        <v>3.8508215680075619E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V52">
+        <f>Electricity!K52</f>
+        <v>75</v>
+      </c>
+      <c r="W52" s="66">
+        <f>Electricity!L52</f>
+        <v>2.6779477408818719</v>
+      </c>
+      <c r="Z52">
+        <f>Compute!M70</f>
+        <v>55</v>
+      </c>
+      <c r="AA52" s="66">
+        <f>Compute!Q70</f>
+        <v>2.5093803775237306E-8</v>
+      </c>
+      <c r="AB52">
+        <f>'DNA sequencing'!C54</f>
+        <v>13.084188911704359</v>
+      </c>
+      <c r="AC52" s="66">
+        <f>'DNA sequencing'!J54</f>
+        <v>4.5084089040370572E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V53">
+        <f>Electricity!K53</f>
+        <v>76</v>
+      </c>
+      <c r="W53" s="66">
+        <f>Electricity!L53</f>
+        <v>2.5109926854754439</v>
+      </c>
+      <c r="Z53">
+        <f>Compute!M71</f>
+        <v>56</v>
+      </c>
+      <c r="AA53" s="66">
+        <f>Compute!Q71</f>
+        <v>2.5093803775237306E-8</v>
+      </c>
+      <c r="AB53">
+        <f>'DNA sequencing'!C55</f>
+        <v>13.336071184120556</v>
+      </c>
+      <c r="AC53" s="66">
+        <f>'DNA sequencing'!J55</f>
+        <v>3.1447903655264526E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V54">
+        <f>Electricity!K54</f>
+        <v>77</v>
+      </c>
+      <c r="W54" s="66">
+        <f>Electricity!L54</f>
+        <v>2.3473024523160757</v>
+      </c>
+      <c r="Z54">
+        <f>Compute!M72</f>
+        <v>57</v>
+      </c>
+      <c r="AA54" s="66">
+        <f>Compute!Q72</f>
+        <v>2.5093803775237306E-8</v>
+      </c>
+      <c r="AB54">
+        <f>'DNA sequencing'!C56</f>
+        <v>13.579739904175312</v>
+      </c>
+      <c r="AC54" s="66">
+        <f>'DNA sequencing'!J56</f>
+        <v>3.3123140454630736E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V55">
+        <f>Electricity!K55</f>
+        <v>78</v>
+      </c>
+      <c r="W55" s="66">
+        <f>Electricity!L55</f>
+        <v>2.2308809746954079</v>
+      </c>
+      <c r="Z55">
+        <f>Compute!M73</f>
+        <v>58</v>
+      </c>
+      <c r="AA55" s="66">
+        <f>Compute!Q73</f>
+        <v>5.972325298506479E-9</v>
+      </c>
+      <c r="AB55">
+        <f>'DNA sequencing'!C57</f>
+        <v>13.831622176591509</v>
+      </c>
+      <c r="AC55" s="66">
+        <f>'DNA sequencing'!J57</f>
+        <v>1.067710707139257E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V56">
+        <f>Electricity!K56</f>
+        <v>79</v>
+      </c>
+      <c r="W56" s="66">
+        <f>Electricity!L56</f>
+        <v>2.2288350168350166</v>
+      </c>
+      <c r="Z56">
+        <f>Compute!M74</f>
+        <v>59</v>
+      </c>
+      <c r="AA56" s="66">
+        <f>Compute!Q74</f>
+        <v>3.7389767625103586E-9</v>
+      </c>
+      <c r="AB56">
+        <f>'DNA sequencing'!C58</f>
+        <v>14.083504449007705</v>
+      </c>
+      <c r="AC56" s="66">
+        <f>'DNA sequencing'!J58</f>
+        <v>9.7541058846892562E-4</v>
+      </c>
+    </row>
+    <row r="57" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V57">
+        <f>Electricity!K57</f>
+        <v>80</v>
+      </c>
+      <c r="W57" s="66">
+        <f>Electricity!L57</f>
+        <v>2.2581252718573293</v>
+      </c>
+      <c r="Z57">
+        <f>Compute!M75</f>
+        <v>60</v>
+      </c>
+      <c r="AA57" s="66">
+        <f>Compute!Q75</f>
+        <v>3.7389767625103586E-9</v>
+      </c>
+      <c r="AB57">
+        <f>'DNA sequencing'!C59</f>
+        <v>14.666666666666742</v>
+      </c>
+      <c r="AC57" s="66">
+        <f>'DNA sequencing'!J59</f>
+        <v>9.12469670315097E-4</v>
+      </c>
+    </row>
+    <row r="58" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="V58">
+        <f>Electricity!K58</f>
+        <v>81</v>
+      </c>
+      <c r="W58" s="66">
+        <f>Electricity!L58</f>
+        <v>2.209443079443079</v>
+      </c>
+      <c r="Z58">
+        <f>Compute!M76</f>
+        <v>61</v>
+      </c>
+      <c r="AA58" s="66">
+        <f>Compute!Q76</f>
+        <v>1.0263365744072059E-9</v>
+      </c>
+      <c r="AB58">
+        <f>'DNA sequencing'!C60</f>
+        <v>14.918548939082939</v>
+      </c>
+      <c r="AC58" s="66">
+        <f>'DNA sequencing'!J60</f>
+        <v>1.1655187674886646E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB59">
+        <f>'DNA sequencing'!C61</f>
+        <v>15.167693360711837</v>
+      </c>
+      <c r="AC59" s="66">
+        <f>'DNA sequencing'!J61</f>
+        <v>1.0417268640705677E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB60">
+        <f>'DNA sequencing'!C62</f>
+        <v>15.414099931553892</v>
+      </c>
+      <c r="AC60" s="66">
+        <f>'DNA sequencing'!J62</f>
+        <v>7.7616015133699081E-4</v>
+      </c>
+    </row>
+    <row r="61" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB61">
+        <f>'DNA sequencing'!C63</f>
+        <v>15.665982203969861</v>
+      </c>
+      <c r="AC61" s="66">
+        <f>'DNA sequencing'!J63</f>
+        <v>1.0181197746957041E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB62">
+        <f>'DNA sequencing'!C64</f>
+        <v>15.917864476386058</v>
+      </c>
+      <c r="AC62" s="66">
+        <f>'DNA sequencing'!J64</f>
+        <v>8.5785382607503542E-4</v>
+      </c>
+    </row>
+    <row r="63" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB63">
+        <f>'DNA sequencing'!C65</f>
+        <v>16.167008898015183</v>
+      </c>
+      <c r="AC63" s="66">
+        <f>'DNA sequencing'!J65</f>
+        <v>1.3873546008372642E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="22:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB64">
+        <f>'DNA sequencing'!C66</f>
+        <v>16.413415468857011</v>
+      </c>
+      <c r="AC64" s="66">
+        <f>'DNA sequencing'!J66</f>
+        <v>9.2049523124533008E-4</v>
+      </c>
+    </row>
+    <row r="65" spans="28:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB65">
+        <f>'DNA sequencing'!C67</f>
+        <v>16.665297741273207</v>
+      </c>
+      <c r="AC65" s="66">
+        <f>'DNA sequencing'!J67</f>
+        <v>1.0866685918468429E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="28:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB66">
+        <f>'DNA sequencing'!C68</f>
+        <v>16.917180013689403</v>
+      </c>
+      <c r="AC66" s="66">
+        <f>'DNA sequencing'!J68</f>
+        <v>1.0847204116506927E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="28:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB67">
+        <f>'DNA sequencing'!C69</f>
+        <v>17.166324435318302</v>
+      </c>
+      <c r="AC67" s="66">
+        <f>'DNA sequencing'!J69</f>
+        <v>1.0264509761350724E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="28:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB68">
+        <f>'DNA sequencing'!C70</f>
+        <v>17.412731006160357</v>
+      </c>
+      <c r="AC68" s="66">
+        <f>'DNA sequencing'!J70</f>
+        <v>7.2814851439087123E-4</v>
+      </c>
+    </row>
+    <row r="69" spans="28:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB69">
+        <f>'DNA sequencing'!C71</f>
+        <v>17.582477754962383</v>
+      </c>
+      <c r="AC69" s="66">
+        <f>'DNA sequencing'!J71</f>
+        <v>4.4276553363266954E-4</v>
+      </c>
+    </row>
+    <row r="70" spans="28:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB70">
+        <f>'DNA sequencing'!C72</f>
+        <v>17.83436002737858</v>
+      </c>
+      <c r="AC70" s="66">
+        <f>'DNA sequencing'!J72</f>
+        <v>6.8601844627310087E-4</v>
+      </c>
+    </row>
+    <row r="71" spans="28:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB71">
+        <f>'DNA sequencing'!C73</f>
+        <v>18.165639972621648</v>
+      </c>
+      <c r="AC71" s="66">
+        <f>'DNA sequencing'!J73</f>
+        <v>5.012544478800742E-4</v>
+      </c>
+    </row>
+    <row r="72" spans="28:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB72">
+        <f>'DNA sequencing'!C74</f>
+        <v>18.412046543463475</v>
+      </c>
+      <c r="AC72" s="66">
+        <f>'DNA sequencing'!J74</f>
+        <v>4.6566339492538819E-4</v>
+      </c>
+    </row>
+    <row r="73" spans="28:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB73">
+        <f>'DNA sequencing'!C75</f>
+        <v>18.666666666666742</v>
+      </c>
+      <c r="AC73" s="66">
+        <f>'DNA sequencing'!J75</f>
+        <v>5.0883900051850264E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="28:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB74">
+        <f>'DNA sequencing'!C76</f>
+        <v>18.918548939082939</v>
+      </c>
+      <c r="AC74" s="66">
+        <f>'DNA sequencing'!J76</f>
+        <v>4.9373666442219515E-4</v>
+      </c>
+    </row>
+    <row r="75" spans="28:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB75">
+        <f>'DNA sequencing'!C77</f>
+        <v>19.167693360711837</v>
+      </c>
+      <c r="AC75" s="66">
+        <f>'DNA sequencing'!J77</f>
+        <v>3.6423861203251415E-4</v>
+      </c>
+    </row>
+    <row r="76" spans="28:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB76">
+        <f>'DNA sequencing'!C78</f>
+        <v>19.414099931553892</v>
+      </c>
+      <c r="AC76" s="66">
+        <f>'DNA sequencing'!J78</f>
+        <v>5.9866651559596358E-4</v>
+      </c>
+    </row>
+    <row r="77" spans="28:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB77">
+        <f>'DNA sequencing'!C79</f>
+        <v>19.665982203969861</v>
+      </c>
+      <c r="AC77" s="66">
+        <f>'DNA sequencing'!J79</f>
+        <v>3.1275476067508102E-4</v>
+      </c>
+    </row>
+    <row r="78" spans="28:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB78">
+        <f>'DNA sequencing'!C80</f>
+        <v>19.917864476386058</v>
+      </c>
+      <c r="AC78" s="66">
+        <f>'DNA sequencing'!J80</f>
+        <v>3.826328938425051E-4</v>
+      </c>
+    </row>
+    <row r="79" spans="28:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB79">
+        <f>'DNA sequencing'!C81</f>
+        <v>20.167008898015183</v>
+      </c>
+      <c r="AC79" s="66">
+        <f>'DNA sequencing'!J81</f>
+        <v>3.6656030166835174E-4</v>
+      </c>
+    </row>
+    <row r="80" spans="28:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB80">
+        <f>'DNA sequencing'!C82</f>
+        <v>20.413415468857011</v>
+      </c>
+      <c r="AC80" s="66">
+        <f>'DNA sequencing'!J82</f>
+        <v>3.3999026951282637E-4</v>
+      </c>
+    </row>
+    <row r="81" spans="28:29" x14ac:dyDescent="0.55000000000000004">
+      <c r="AB81">
+        <f>'DNA sequencing'!C83</f>
+        <v>20.665297741273207</v>
+      </c>
+      <c r="AC81" s="66">
+        <f>'DNA sequencing'!J83</f>
+        <v>3.3159531996810655E-4</v>
       </c>
     </row>
   </sheetData>
@@ -8044,7 +10064,8 @@
     <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -8060,20 +10081,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="62" t="s">
-        <v>224</v>
-      </c>
-      <c r="C2" s="62"/>
-      <c r="E2" s="62" t="s">
+      <c r="B2" s="63" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" s="63"/>
+      <c r="E2" s="63" t="s">
+        <v>221</v>
+      </c>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="63" t="s">
         <v>223</v>
       </c>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="62" t="s">
-        <v>226</v>
-      </c>
-      <c r="J2" s="62"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:12" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
@@ -8100,7 +10121,7 @@
         <v>22</v>
       </c>
       <c r="J3" s="51" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="K3" s="51"/>
       <c r="L3" t="s">
@@ -8157,7 +10178,7 @@
         <v>5</v>
       </c>
       <c r="L5">
-        <f t="shared" ref="L5:L68" si="2">J5/$J$4*100</f>
+        <f t="shared" ref="L5:L58" si="2">J5/$J$4*100</f>
         <v>98.103137396321642</v>
       </c>
     </row>
@@ -10428,10 +12449,7 @@
       <c r="D1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="47" cm="1">
-        <f t="array" ref="E1">1-EXP(LN(MIN(D7:D727/D4:D724))/12)</f>
-        <v>6.6782094039954276E-2</v>
-      </c>
+      <c r="E1" s="47"/>
       <c r="F1" s="10" t="s">
         <v>16</v>
       </c>
@@ -17352,7 +19370,7 @@
         <v>10014.107</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A497" t="s">
         <v>27</v>
       </c>
@@ -17366,7 +19384,7 @@
         <v>9656.0820000000003</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A498" t="s">
         <v>27</v>
       </c>
@@ -17380,7 +19398,7 @@
         <v>9568.52</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A499" t="s">
         <v>27</v>
       </c>
@@ -17394,7 +19412,7 @@
         <v>9484.5769999999993</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A500" t="s">
         <v>27</v>
       </c>
@@ -17408,7 +19426,7 @@
         <v>9308.357</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A501" t="s">
         <v>27</v>
       </c>
@@ -17422,7 +19440,7 @@
         <v>9247.8539999999994</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A502" t="s">
         <v>27</v>
       </c>
@@ -17436,7 +19454,7 @@
         <v>9329.8250000000007</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A503" t="s">
         <v>27</v>
       </c>
@@ -17450,7 +19468,7 @@
         <v>8989.2829999999994</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A504" t="s">
         <v>27</v>
       </c>
@@ -17463,12 +19481,8 @@
       <c r="D504">
         <v>8497.482</v>
       </c>
-      <c r="E504">
-        <f>1-(D505/D504)^(1/3)</f>
-        <v>1.0079344982575011E-2</v>
-      </c>
-    </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A505" t="s">
         <v>27</v>
       </c>
@@ -17481,12 +19495,8 @@
       <c r="D505">
         <v>8243.116</v>
       </c>
-      <c r="E505">
-        <f t="shared" ref="E505:E568" si="0">1-(D506/D505)^(1/3)</f>
-        <v>6.6106897136974929E-4</v>
-      </c>
-    </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="506" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A506" t="s">
         <v>27</v>
       </c>
@@ -17499,12 +19509,8 @@
       <c r="D506">
         <v>8226.7790000000005</v>
       </c>
-      <c r="E506">
-        <f t="shared" si="0"/>
-        <v>2.1600422300164235E-3</v>
-      </c>
-    </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="507" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A507" t="s">
         <v>27</v>
       </c>
@@ -17517,12 +19523,8 @@
       <c r="D507">
         <v>8173.5834999999997</v>
       </c>
-      <c r="E507">
-        <f t="shared" si="0"/>
-        <v>-3.9362580786894696E-4</v>
-      </c>
-    </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="508" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A508" t="s">
         <v>27</v>
       </c>
@@ -17535,12 +19537,8 @@
       <c r="D508">
         <v>8183.2393000000002</v>
       </c>
-      <c r="E508">
-        <f t="shared" si="0"/>
-        <v>-5.4642726719495993E-3</v>
-      </c>
-    </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="509" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A509" t="s">
         <v>27</v>
       </c>
@@ -17553,12 +19551,8 @@
       <c r="D509">
         <v>8318.1200000000008</v>
       </c>
-      <c r="E509">
-        <f t="shared" si="0"/>
-        <v>1.9711864206861662E-4</v>
-      </c>
-    </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A510" t="s">
         <v>27</v>
       </c>
@@ -17571,12 +19565,8 @@
       <c r="D510">
         <v>8313.2019999999993</v>
       </c>
-      <c r="E510">
-        <f t="shared" si="0"/>
-        <v>6.644285341191547E-3</v>
-      </c>
-    </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="511" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A511" t="s">
         <v>27</v>
       </c>
@@ -17589,12 +19579,8 @@
       <c r="D511">
         <v>8148.5946999999996</v>
       </c>
-      <c r="E511">
-        <f t="shared" si="0"/>
-        <v>-9.800368003388682E-3</v>
-      </c>
-    </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="512" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A512" t="s">
         <v>27</v>
       </c>
@@ -17607,12 +19593,8 @@
       <c r="D512">
         <v>8390.5280000000002</v>
       </c>
-      <c r="E512">
-        <f t="shared" si="0"/>
-        <v>3.9936274441947361E-3</v>
-      </c>
-    </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="513" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A513" t="s">
         <v>27</v>
       </c>
@@ -17625,12 +19607,8 @@
       <c r="D513">
         <v>8290.4030000000002</v>
       </c>
-      <c r="E513">
-        <f t="shared" si="0"/>
-        <v>-4.2259938465893931E-4</v>
-      </c>
-    </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="514" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A514" t="s">
         <v>27</v>
       </c>
@@ -17643,12 +19621,8 @@
       <c r="D514">
         <v>8300.9179999999997</v>
       </c>
-      <c r="E514">
-        <f t="shared" si="0"/>
-        <v>-5.8163013787009277E-3</v>
-      </c>
-    </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A515" t="s">
         <v>27</v>
       </c>
@@ -17661,12 +19635,8 @@
       <c r="D515">
         <v>8446.6039999999994</v>
       </c>
-      <c r="E515">
-        <f t="shared" si="0"/>
-        <v>7.4757713703020867E-3</v>
-      </c>
-    </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A516" t="s">
         <v>27</v>
       </c>
@@ -17679,12 +19649,8 @@
       <c r="D516">
         <v>8258.5820000000003</v>
       </c>
-      <c r="E516">
-        <f t="shared" si="0"/>
-        <v>2.6607967947166911E-2</v>
-      </c>
-    </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A517" t="s">
         <v>27</v>
       </c>
@@ -17697,12 +19663,8 @@
       <c r="D517">
         <v>7616.7349999999997</v>
       </c>
-      <c r="E517">
-        <f t="shared" si="0"/>
-        <v>1.2379153487399375E-2</v>
-      </c>
-    </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A518" t="s">
         <v>27</v>
       </c>
@@ -17715,12 +19677,8 @@
       <c r="D518">
         <v>7337.3559999999998</v>
       </c>
-      <c r="E518">
-        <f t="shared" si="0"/>
-        <v>1.5851427430322196E-2</v>
-      </c>
-    </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A519" t="s">
         <v>27</v>
       </c>
@@ -17733,12 +19691,8 @@
       <c r="D519">
         <v>6993.9350000000004</v>
       </c>
-      <c r="E519">
-        <f t="shared" si="0"/>
-        <v>2.6048505200692129E-2</v>
-      </c>
-    </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A520" t="s">
         <v>27</v>
       </c>
@@ -17751,12 +19705,8 @@
       <c r="D520">
         <v>6461.5033999999996</v>
       </c>
-      <c r="E520">
-        <f t="shared" si="0"/>
-        <v>8.8957382211077851E-3</v>
-      </c>
-    </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A521" t="s">
         <v>27</v>
       </c>
@@ -17769,12 +19719,8 @@
       <c r="D521">
         <v>6290.5933000000005</v>
       </c>
-      <c r="E521">
-        <f t="shared" si="0"/>
-        <v>2.0942329265250303E-2</v>
-      </c>
-    </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A522" t="s">
         <v>27</v>
       </c>
@@ -17787,12 +19733,8 @@
       <c r="D522">
         <v>5903.5933000000005</v>
       </c>
-      <c r="E522">
-        <f t="shared" si="0"/>
-        <v>1.927328287786445E-2</v>
-      </c>
-    </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A523" t="s">
         <v>27</v>
       </c>
@@ -17805,12 +19747,8 @@
       <c r="D523">
         <v>5568.7849999999999</v>
       </c>
-      <c r="E523">
-        <f t="shared" si="0"/>
-        <v>1.5203868823600919E-2</v>
-      </c>
-    </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A524" t="s">
         <v>27</v>
       </c>
@@ -17823,12 +19761,8 @@
       <c r="D524">
         <v>5318.6260000000002</v>
       </c>
-      <c r="E524">
-        <f t="shared" si="0"/>
-        <v>1.6702268754859473E-2</v>
-      </c>
-    </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A525" t="s">
         <v>27</v>
       </c>
@@ -17841,12 +19775,8 @@
       <c r="D525">
         <v>5056.5529999999999</v>
       </c>
-      <c r="E525">
-        <f t="shared" si="0"/>
-        <v>3.4611780836439454E-2</v>
-      </c>
-    </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A526" t="s">
         <v>27</v>
       </c>
@@ -17859,12 +19789,8 @@
       <c r="D526">
         <v>4549.4673000000003</v>
       </c>
-      <c r="E526">
-        <f t="shared" si="0"/>
-        <v>2.934202290222232E-2</v>
-      </c>
-    </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A527" t="s">
         <v>27</v>
       </c>
@@ -17877,12 +19803,8 @@
       <c r="D527">
         <v>4160.6313</v>
       </c>
-      <c r="E527">
-        <f t="shared" si="0"/>
-        <v>2.4852295029400784E-2</v>
-      </c>
-    </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A528" t="s">
         <v>27</v>
       </c>
@@ -17895,12 +19817,8 @@
       <c r="D528">
         <v>3858.0729999999999</v>
       </c>
-      <c r="E528">
-        <f t="shared" si="0"/>
-        <v>2.2175815310383151E-2</v>
-      </c>
-    </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A529" t="s">
         <v>27</v>
       </c>
@@ -17913,12 +19831,8 @@
       <c r="D529">
         <v>3607.0549999999998</v>
       </c>
-      <c r="E529">
-        <f t="shared" si="0"/>
-        <v>1.5800435157237169E-2</v>
-      </c>
-    </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="530" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A530" t="s">
         <v>27</v>
       </c>
@@ -17931,12 +19845,8 @@
       <c r="D530">
         <v>3438.7631999999999</v>
       </c>
-      <c r="E530">
-        <f t="shared" si="0"/>
-        <v>1.5210064747600893E-2</v>
-      </c>
-    </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A531" t="s">
         <v>27</v>
       </c>
@@ -17949,12 +19859,8 @@
       <c r="D531">
         <v>3284.2262999999998</v>
       </c>
-      <c r="E531">
-        <f t="shared" si="0"/>
-        <v>3.9055766313118578E-3</v>
-      </c>
-    </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A532" t="s">
         <v>27</v>
       </c>
@@ -17967,12 +19873,8 @@
       <c r="D532">
         <v>3245.8960000000002</v>
       </c>
-      <c r="E532">
-        <f t="shared" si="0"/>
-        <v>3.165894900707622E-3</v>
-      </c>
-    </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A533" t="s">
         <v>27</v>
       </c>
@@ -17985,12 +19887,8 @@
       <c r="D533">
         <v>3215.165</v>
       </c>
-      <c r="E533">
-        <f t="shared" si="0"/>
-        <v>-6.2178269786883344E-3</v>
-      </c>
-    </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A534" t="s">
         <v>27</v>
       </c>
@@ -18003,12 +19901,8 @@
       <c r="D534">
         <v>3275.5127000000002</v>
       </c>
-      <c r="E534">
-        <f t="shared" si="0"/>
-        <v>-2.6898120285014926E-3</v>
-      </c>
-    </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A535" t="s">
         <v>27</v>
       </c>
@@ -18021,12 +19915,8 @@
       <c r="D535">
         <v>3302.0154000000002</v>
       </c>
-      <c r="E535">
-        <f t="shared" si="0"/>
-        <v>-1.9147154709566738E-3</v>
-      </c>
-    </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A536" t="s">
         <v>27</v>
       </c>
@@ -18039,12 +19929,8 @@
       <c r="D536">
         <v>3321.0189999999998</v>
       </c>
-      <c r="E536">
-        <f t="shared" si="0"/>
-        <v>-5.0952338931209429E-3</v>
-      </c>
-    </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="537" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A537" t="s">
         <v>27</v>
       </c>
@@ -18057,12 +19943,8 @@
       <c r="D537">
         <v>3372.0421999999999</v>
       </c>
-      <c r="E537">
-        <f t="shared" si="0"/>
-        <v>-5.1413490023375363E-3</v>
-      </c>
-    </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A538" t="s">
         <v>27</v>
       </c>
@@ -18075,12 +19957,8 @@
       <c r="D538">
         <v>3424.3206</v>
       </c>
-      <c r="E538">
-        <f t="shared" si="0"/>
-        <v>-4.3448622646136137E-4</v>
-      </c>
-    </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A539" t="s">
         <v>27</v>
       </c>
@@ -18093,12 +19971,8 @@
       <c r="D539">
         <v>3428.7860000000001</v>
       </c>
-      <c r="E539">
-        <f t="shared" si="0"/>
-        <v>4.2965466919382411E-3</v>
-      </c>
-    </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A540" t="s">
         <v>27</v>
       </c>
@@ -18111,12 +19985,8 @@
       <c r="D540">
         <v>3384.7797999999998</v>
       </c>
-      <c r="E540">
-        <f t="shared" si="0"/>
-        <v>8.869735273384749E-3</v>
-      </c>
-    </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A541" t="s">
         <v>27</v>
       </c>
@@ -18129,12 +19999,8 @@
       <c r="D541">
         <v>3295.51</v>
       </c>
-      <c r="E541">
-        <f t="shared" si="0"/>
-        <v>1.3329696200710006E-2</v>
-      </c>
-    </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A542" t="s">
         <v>27</v>
       </c>
@@ -18147,12 +20013,8 @@
       <c r="D542">
         <v>3165.4744000000001</v>
       </c>
-      <c r="E542">
-        <f t="shared" si="0"/>
-        <v>1.7288242377500374E-2</v>
-      </c>
-    </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="543" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A543" t="s">
         <v>27</v>
       </c>
@@ -18165,12 +20027,8 @@
       <c r="D543">
         <v>3004.1199000000001</v>
       </c>
-      <c r="E543">
-        <f t="shared" si="0"/>
-        <v>2.2641704804096885E-2</v>
-      </c>
-    </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="544" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A544" t="s">
         <v>27</v>
       </c>
@@ -18183,12 +20041,8 @@
       <c r="D544">
         <v>2804.65</v>
       </c>
-      <c r="E544">
-        <f t="shared" si="0"/>
-        <v>1.6257256398612197E-2</v>
-      </c>
-    </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="545" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A545" t="s">
         <v>27</v>
       </c>
@@ -18201,12 +20055,8 @@
       <c r="D545">
         <v>2670.0740000000001</v>
       </c>
-      <c r="E545">
-        <f t="shared" si="0"/>
-        <v>1.1294440030524378E-2</v>
-      </c>
-    </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="546" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A546" t="s">
         <v>27</v>
       </c>
@@ -18219,12 +20069,8 @@
       <c r="D546">
         <v>2580.6210000000001</v>
       </c>
-      <c r="E546">
-        <f t="shared" si="0"/>
-        <v>3.9894601630936499E-3</v>
-      </c>
-    </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="547" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A547" t="s">
         <v>27</v>
       </c>
@@ -18237,12 +20083,8 @@
       <c r="D547">
         <v>2549.8582000000001</v>
       </c>
-      <c r="E547">
-        <f t="shared" si="0"/>
-        <v>2.7418853389846731E-3</v>
-      </c>
-    </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="548" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A548" t="s">
         <v>27</v>
       </c>
@@ -18255,12 +20097,8 @@
       <c r="D548">
         <v>2528.9414000000002</v>
       </c>
-      <c r="E548">
-        <f t="shared" si="0"/>
-        <v>-3.5060660477093109E-6</v>
-      </c>
-    </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="549" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A549" t="s">
         <v>27</v>
       </c>
@@ -18273,12 +20111,8 @@
       <c r="D549">
         <v>2528.9679999999998</v>
       </c>
-      <c r="E549">
-        <f t="shared" si="0"/>
-        <v>5.7820231995111548E-3</v>
-      </c>
-    </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="550" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A550" t="s">
         <v>27</v>
       </c>
@@ -18291,12 +20125,8 @@
       <c r="D550">
         <v>2485.3535000000002</v>
       </c>
-      <c r="E550">
-        <f t="shared" si="0"/>
-        <v>1.0860255581131129E-2</v>
-      </c>
-    </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="551" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A551" t="s">
         <v>27</v>
       </c>
@@ -18309,12 +20139,8 @@
       <c r="D551">
         <v>2405.2550000000001</v>
       </c>
-      <c r="E551">
-        <f t="shared" si="0"/>
-        <v>8.3102684722251574E-3</v>
-      </c>
-    </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="552" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A552" t="s">
         <v>27</v>
       </c>
@@ -18327,12 +20153,8 @@
       <c r="D552">
         <v>2345.7869999999998</v>
       </c>
-      <c r="E552">
-        <f t="shared" si="0"/>
-        <v>1.0973247982679624E-3</v>
-      </c>
-    </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="553" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A553" t="s">
         <v>27</v>
       </c>
@@ -18345,12 +20167,8 @@
       <c r="D553">
         <v>2338.0731999999998</v>
       </c>
-      <c r="E553">
-        <f t="shared" si="0"/>
-        <v>-6.0134459467131585E-4</v>
-      </c>
-    </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="554" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A554" t="s">
         <v>27</v>
       </c>
@@ -18363,12 +20181,8 @@
       <c r="D554">
         <v>2342.2937000000002</v>
       </c>
-      <c r="E554">
-        <f t="shared" si="0"/>
-        <v>-6.4536461258175581E-3</v>
-      </c>
-    </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="555" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A555" t="s">
         <v>27</v>
       </c>
@@ -18381,12 +20195,8 @@
       <c r="D555">
         <v>2387.9360000000001</v>
       </c>
-      <c r="E555">
-        <f t="shared" si="0"/>
-        <v>-3.7392003696332665E-3</v>
-      </c>
-    </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="556" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A556" t="s">
         <v>27</v>
       </c>
@@ -18399,12 +20209,8 @@
       <c r="D556">
         <v>2414.8231999999998</v>
       </c>
-      <c r="E556">
-        <f t="shared" si="0"/>
-        <v>1.1565016388873084E-2</v>
-      </c>
-    </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="557" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A557" t="s">
         <v>27</v>
       </c>
@@ -18417,12 +20223,8 @@
       <c r="D557">
         <v>2332.0059999999999</v>
       </c>
-      <c r="E557">
-        <f t="shared" si="0"/>
-        <v>3.0321822656213193E-2</v>
-      </c>
-    </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="558" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A558" t="s">
         <v>27</v>
       </c>
@@ -18435,12 +20237,8 @@
       <c r="D558">
         <v>2126.2411999999999</v>
       </c>
-      <c r="E558">
-        <f t="shared" si="0"/>
-        <v>3.9115869511425538E-2</v>
-      </c>
-    </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="559" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A559" t="s">
         <v>27</v>
       </c>
@@ -18453,12 +20251,8 @@
       <c r="D559">
         <v>1886.3643999999999</v>
       </c>
-      <c r="E559">
-        <f t="shared" si="0"/>
-        <v>4.493480198314137E-2</v>
-      </c>
-    </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="560" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A560" t="s">
         <v>27</v>
       </c>
@@ -18471,12 +20265,8 @@
       <c r="D560">
         <v>1643.3295000000001</v>
       </c>
-      <c r="E560">
-        <f t="shared" si="0"/>
-        <v>3.5601578085311947E-2</v>
-      </c>
-    </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A561" t="s">
         <v>27</v>
       </c>
@@ -18489,12 +20279,8 @@
       <c r="D561">
         <v>1473.9885999999999</v>
       </c>
-      <c r="E561">
-        <f t="shared" si="0"/>
-        <v>2.7017395661157129E-2</v>
-      </c>
-    </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A562" t="s">
         <v>27</v>
       </c>
@@ -18507,12 +20293,8 @@
       <c r="D562">
         <v>1357.7173</v>
       </c>
-      <c r="E562">
-        <f t="shared" si="0"/>
-        <v>4.3188086105070411E-3</v>
-      </c>
-    </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A563" t="s">
         <v>27</v>
       </c>
@@ -18525,12 +20307,8 @@
       <c r="D563">
         <v>1340.202</v>
       </c>
-      <c r="E563">
-        <f t="shared" si="0"/>
-        <v>-4.8545651681961566E-3</v>
-      </c>
-    </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A564" t="s">
         <v>27</v>
       </c>
@@ -18543,12 +20321,8 @@
       <c r="D564">
         <v>1359.8152</v>
       </c>
-      <c r="E564">
-        <f t="shared" si="0"/>
-        <v>6.1328732975290956E-3</v>
-      </c>
-    </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A565" t="s">
         <v>27</v>
       </c>
@@ -18561,12 +20335,8 @@
       <c r="D565">
         <v>1334.9495999999999</v>
       </c>
-      <c r="E565">
-        <f t="shared" si="0"/>
-        <v>2.3978235265527115E-2</v>
-      </c>
-    </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A566" t="s">
         <v>27</v>
       </c>
@@ -18579,12 +20349,8 @@
       <c r="D566">
         <v>1241.2046</v>
       </c>
-      <c r="E566">
-        <f t="shared" si="0"/>
-        <v>2.2534664832334794E-2</v>
-      </c>
-    </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A567" t="s">
         <v>27</v>
       </c>
@@ -18597,12 +20363,8 @@
       <c r="D567">
         <v>1159.1709000000001</v>
       </c>
-      <c r="E567">
-        <f t="shared" si="0"/>
-        <v>3.1715684727854909E-2</v>
-      </c>
-    </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A568" t="s">
         <v>27</v>
       </c>
@@ -18615,12 +20377,8 @@
       <c r="D568">
         <v>1052.3402000000001</v>
       </c>
-      <c r="E568">
-        <f t="shared" si="0"/>
-        <v>2.6845863961867167E-2</v>
-      </c>
-    </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="569" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A569" t="s">
         <v>27</v>
       </c>
@@ -18633,12 +20391,8 @@
       <c r="D569">
         <v>969.84216000000004</v>
       </c>
-      <c r="E569">
-        <f t="shared" ref="E569:E632" si="1">1-(D570/D569)^(1/3)</f>
-        <v>1.5611749689238619E-2</v>
-      </c>
-    </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="570" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A570" t="s">
         <v>27</v>
       </c>
@@ -18651,12 +20405,8 @@
       <c r="D570">
         <v>925.12480000000005</v>
       </c>
-      <c r="E570">
-        <f t="shared" si="1"/>
-        <v>1.2627478156006067E-2</v>
-      </c>
-    </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="571" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A571" t="s">
         <v>27</v>
       </c>
@@ -18669,12 +20419,8 @@
       <c r="D571">
         <v>890.51949999999999</v>
       </c>
-      <c r="E571">
-        <f t="shared" si="1"/>
-        <v>3.9567429501848883E-3</v>
-      </c>
-    </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A572" t="s">
         <v>27</v>
       </c>
@@ -18687,12 +20433,8 @@
       <c r="D572">
         <v>879.99059999999997</v>
       </c>
-      <c r="E572">
-        <f t="shared" si="1"/>
-        <v>-5.2000026181064918E-4</v>
-      </c>
-    </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A573" t="s">
         <v>27</v>
       </c>
@@ -18705,12 +20447,8 @@
       <c r="D573">
         <v>881.36410000000001</v>
       </c>
-      <c r="E573">
-        <f t="shared" si="1"/>
-        <v>1.1176986006800949E-2</v>
-      </c>
-    </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A574" t="s">
         <v>27</v>
       </c>
@@ -18723,12 +20461,8 @@
       <c r="D574">
         <v>852.14020000000005</v>
       </c>
-      <c r="E574">
-        <f t="shared" si="1"/>
-        <v>9.8149588636251561E-3</v>
-      </c>
-    </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A575" t="s">
         <v>27</v>
       </c>
@@ -18741,12 +20475,8 @@
       <c r="D575">
         <v>827.29449999999997</v>
       </c>
-      <c r="E575">
-        <f t="shared" si="1"/>
-        <v>1.9727001741748351E-3</v>
-      </c>
-    </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A576" t="s">
         <v>27</v>
       </c>
@@ -18759,12 +20489,8 @@
       <c r="D576">
         <v>822.40814</v>
       </c>
-      <c r="E576">
-        <f t="shared" si="1"/>
-        <v>1.2391418682567434E-2</v>
-      </c>
-    </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A577" t="s">
         <v>27</v>
       </c>
@@ -18777,12 +20503,8 @@
       <c r="D577">
         <v>792.21299999999997</v>
       </c>
-      <c r="E577">
-        <f t="shared" si="1"/>
-        <v>1.7984366088814596E-2</v>
-      </c>
-    </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A578" t="s">
         <v>27</v>
       </c>
@@ -18795,12 +20517,8 @@
       <c r="D578">
         <v>750.23473999999999</v>
       </c>
-      <c r="E578">
-        <f t="shared" si="1"/>
-        <v>2.1224338151307531E-2</v>
-      </c>
-    </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A579" t="s">
         <v>27</v>
       </c>
@@ -18813,12 +20531,8 @@
       <c r="D579">
         <v>703.47173999999995</v>
       </c>
-      <c r="E579">
-        <f t="shared" si="1"/>
-        <v>6.7181313634782081E-3</v>
-      </c>
-    </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A580" t="s">
         <v>27</v>
       </c>
@@ -18831,12 +20545,8 @@
       <c r="D580">
         <v>689.38873000000001</v>
       </c>
-      <c r="E580">
-        <f t="shared" si="1"/>
-        <v>7.7465035374666424E-3</v>
-      </c>
-    </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A581" t="s">
         <v>27</v>
       </c>
@@ -18849,12 +20559,8 @@
       <c r="D581">
         <v>673.49145999999996</v>
       </c>
-      <c r="E581">
-        <f t="shared" si="1"/>
-        <v>1.9048869588936368E-2</v>
-      </c>
-    </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A582" t="s">
         <v>27</v>
       </c>
@@ -18867,12 +20573,8 @@
       <c r="D582">
         <v>635.73220000000003</v>
       </c>
-      <c r="E582">
-        <f t="shared" si="1"/>
-        <v>1.2542963302364929E-2</v>
-      </c>
-    </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A583" t="s">
         <v>27</v>
       </c>
@@ -18885,12 +20587,8 @@
       <c r="D583">
         <v>612.10910000000001</v>
       </c>
-      <c r="E583">
-        <f t="shared" si="1"/>
-        <v>1.2967545025519445E-2</v>
-      </c>
-    </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A584" t="s">
         <v>27</v>
       </c>
@@ -18903,12 +20601,8 @@
       <c r="D584">
         <v>588.60389999999995</v>
       </c>
-      <c r="E584">
-        <f t="shared" si="1"/>
-        <v>3.0865127980137519E-2</v>
-      </c>
-    </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A585" t="s">
         <v>27</v>
       </c>
@@ -18921,12 +20615,8 @@
       <c r="D585">
         <v>535.76679999999999</v>
       </c>
-      <c r="E585">
-        <f t="shared" si="1"/>
-        <v>2.4839484380265398E-2</v>
-      </c>
-    </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A586" t="s">
         <v>27</v>
       </c>
@@ -18939,12 +20629,8 @@
       <c r="D586">
         <v>496.82578000000001</v>
       </c>
-      <c r="E586">
-        <f t="shared" si="1"/>
-        <v>1.5223023230940713E-2</v>
-      </c>
-    </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A587" t="s">
         <v>27</v>
       </c>
@@ -18957,12 +20643,8 @@
       <c r="D587">
         <v>474.47985999999997</v>
       </c>
-      <c r="E587">
-        <f t="shared" si="1"/>
-        <v>1.7000966997346434E-2</v>
-      </c>
-    </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A588" t="s">
         <v>27</v>
       </c>
@@ -18975,12 +20657,8 @@
       <c r="D588">
         <v>450.6891</v>
       </c>
-      <c r="E588">
-        <f t="shared" si="1"/>
-        <v>2.4306821240592469E-2</v>
-      </c>
-    </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A589" t="s">
         <v>27</v>
       </c>
@@ -18993,12 +20671,8 @@
       <c r="D589">
         <v>418.61700000000002</v>
       </c>
-      <c r="E589">
-        <f t="shared" si="1"/>
-        <v>2.475678837670392E-2</v>
-      </c>
-    </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A590" t="s">
         <v>27</v>
       </c>
@@ -19011,12 +20685,8 @@
       <c r="D590">
         <v>388.28951999999998</v>
       </c>
-      <c r="E590">
-        <f t="shared" si="1"/>
-        <v>3.3628953211946588E-2</v>
-      </c>
-    </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A591" t="s">
         <v>27</v>
       </c>
@@ -19029,12 +20699,8 @@
       <c r="D591">
         <v>350.41879999999998</v>
       </c>
-      <c r="E591">
-        <f t="shared" si="1"/>
-        <v>2.9390731573222806E-2</v>
-      </c>
-    </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A592" t="s">
         <v>27</v>
       </c>
@@ -19047,10 +20713,6 @@
       <c r="D592">
         <v>320.42079999999999</v>
       </c>
-      <c r="E592">
-        <f t="shared" si="1"/>
-        <v>2.9881979101241019E-2</v>
-      </c>
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A593" t="s">
@@ -19065,10 +20727,6 @@
       <c r="D593">
         <v>292.54617000000002</v>
       </c>
-      <c r="E593">
-        <f t="shared" si="1"/>
-        <v>1.9535642311593215E-2</v>
-      </c>
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A594" t="s">
@@ -19083,10 +20741,6 @@
       <c r="D594">
         <v>275.7337</v>
       </c>
-      <c r="E594">
-        <f t="shared" si="1"/>
-        <v>1.0492058765325329E-2</v>
-      </c>
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A595" t="s">
@@ -19101,10 +20755,6 @@
       <c r="D595">
         <v>267.1454</v>
       </c>
-      <c r="E595">
-        <f t="shared" si="1"/>
-        <v>6.4258662457740146E-3</v>
-      </c>
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A596" t="s">
@@ -19119,10 +20769,6 @@
       <c r="D596">
         <v>262.02850000000001</v>
       </c>
-      <c r="E596">
-        <f t="shared" si="1"/>
-        <v>3.2744135847959654E-3</v>
-      </c>
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A597" t="s">
@@ -19137,10 +20783,6 @@
       <c r="D597">
         <v>259.46294999999998</v>
       </c>
-      <c r="E597">
-        <f t="shared" si="1"/>
-        <v>3.8659837895718141E-3</v>
-      </c>
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A598" t="s">
@@ -19155,10 +20797,6 @@
       <c r="D598">
         <v>256.46532999999999</v>
       </c>
-      <c r="E598">
-        <f t="shared" si="1"/>
-        <v>9.913176748606034E-4</v>
-      </c>
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A599" t="s">
@@ -19173,10 +20811,6 @@
       <c r="D599">
         <v>255.70337000000001</v>
       </c>
-      <c r="E599">
-        <f t="shared" si="1"/>
-        <v>4.852054984761156E-3</v>
-      </c>
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A600" t="s">
@@ -19191,10 +20825,6 @@
       <c r="D600">
         <v>251.99933999999999</v>
       </c>
-      <c r="E600">
-        <f t="shared" si="1"/>
-        <v>1.1277202632863692E-2</v>
-      </c>
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A601" t="s">
@@ -19209,10 +20839,6 @@
       <c r="D601">
         <v>243.56958</v>
       </c>
-      <c r="E601">
-        <f t="shared" si="1"/>
-        <v>1.5676174688437627E-2</v>
-      </c>
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A602" t="s">
@@ -19227,10 +20853,6 @@
       <c r="D602">
         <v>232.29348999999999</v>
       </c>
-      <c r="E602">
-        <f t="shared" si="1"/>
-        <v>1.0455297707387623E-2</v>
-      </c>
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A603" t="s">
@@ -19245,10 +20867,6 @@
       <c r="D603">
         <v>225.08331000000001</v>
       </c>
-      <c r="E603">
-        <f t="shared" si="1"/>
-        <v>3.6347134674905579E-3</v>
-      </c>
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A604" t="s">
@@ -19262,10 +20880,6 @@
       </c>
       <c r="D604">
         <v>222.63788</v>
-      </c>
-      <c r="E604">
-        <f t="shared" si="1"/>
-        <v>-7.0129042097510919E-4</v>
       </c>
       <c r="F604">
         <f>D604/$D$604*100</f>
@@ -19285,12 +20899,8 @@
       <c r="D605">
         <v>223.10660999999999</v>
       </c>
-      <c r="E605">
-        <f t="shared" si="1"/>
-        <v>-1.5892989171964356E-2</v>
-      </c>
       <c r="F605">
-        <f t="shared" ref="F605:F668" si="2">D605/$D$604*100</f>
+        <f t="shared" ref="F605:F668" si="0">D605/$D$604*100</f>
         <v>100.21053470325893</v>
       </c>
     </row>
@@ -19307,12 +20917,8 @@
       <c r="D606">
         <v>233.91406000000001</v>
       </c>
-      <c r="E606">
-        <f t="shared" si="1"/>
-        <v>-3.8155476989343295E-3</v>
-      </c>
       <c r="F606">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>105.0648074802006</v>
       </c>
     </row>
@@ -19329,12 +20935,8 @@
       <c r="D607">
         <v>236.60182</v>
       </c>
-      <c r="E607">
-        <f t="shared" si="1"/>
-        <v>2.0020459338844221E-3</v>
-      </c>
       <c r="F607">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>106.27204139744772</v>
       </c>
     </row>
@@ -19351,12 +20953,8 @@
       <c r="D608">
         <v>235.18360000000001</v>
       </c>
-      <c r="E608">
-        <f t="shared" si="1"/>
-        <v>9.4639453229014014E-3</v>
-      </c>
       <c r="F608">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>105.6350338945017</v>
       </c>
     </row>
@@ -19373,12 +20971,8 @@
       <c r="D609">
         <v>228.5693</v>
       </c>
-      <c r="E609">
-        <f t="shared" si="1"/>
-        <v>2.2648341447700782E-3</v>
-      </c>
       <c r="F609">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>102.66415580313645</v>
       </c>
     </row>
@@ -19395,12 +20989,8 @@
       <c r="D610">
         <v>227.0198</v>
       </c>
-      <c r="E610">
-        <f t="shared" si="1"/>
-        <v>1.3520766194127232E-3</v>
-      </c>
       <c r="F610">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>101.96818259318677</v>
       </c>
     </row>
@@ -19417,12 +21007,8 @@
       <c r="D611">
         <v>226.1002</v>
       </c>
-      <c r="E611">
-        <f t="shared" si="1"/>
-        <v>3.1032747976889041E-4</v>
-      </c>
       <c r="F611">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>101.55513518184776</v>
       </c>
     </row>
@@ -19439,12 +21025,8 @@
       <c r="D612">
         <v>225.88977</v>
       </c>
-      <c r="E612">
-        <f t="shared" si="1"/>
-        <v>-1.7556645117098313E-3</v>
-      </c>
       <c r="F612">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>101.46061847157367</v>
       </c>
     </row>
@@ -19461,12 +21043,8 @@
       <c r="D613">
         <v>227.08161999999999</v>
       </c>
-      <c r="E613">
-        <f t="shared" si="1"/>
-        <v>-8.9173905579138513E-3</v>
-      </c>
       <c r="F613">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>101.99594965600642</v>
       </c>
     </row>
@@ -19483,12 +21061,8 @@
       <c r="D614">
         <v>233.21088</v>
       </c>
-      <c r="E614">
-        <f t="shared" si="1"/>
-        <v>1.4679229792087245E-3</v>
-      </c>
       <c r="F614">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>104.74896724672369</v>
       </c>
     </row>
@@ -19505,12 +21079,8 @@
       <c r="D615">
         <v>232.18538000000001</v>
       </c>
-      <c r="E615">
-        <f t="shared" si="1"/>
-        <v>1.1904867091897864E-2</v>
-      </c>
       <c r="F615">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>104.28835380574053</v>
       </c>
     </row>
@@ -19527,12 +21097,8 @@
       <c r="D616">
         <v>223.9913</v>
       </c>
-      <c r="E616">
-        <f t="shared" si="1"/>
-        <v>5.8247263584766396E-3</v>
-      </c>
       <c r="F616">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>100.60790194373033</v>
       </c>
     </row>
@@ -19549,12 +21115,8 @@
       <c r="D617">
         <v>220.09998999999999</v>
       </c>
-      <c r="E617">
-        <f t="shared" si="1"/>
-        <v>1.50058771399878E-2</v>
-      </c>
       <c r="F617">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>98.860081671636465</v>
       </c>
     </row>
@@ -19571,12 +21133,8 @@
       <c r="D618">
         <v>210.33955</v>
       </c>
-      <c r="E618">
-        <f t="shared" si="1"/>
-        <v>2.3990403260905513E-2</v>
-      </c>
       <c r="F618">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>94.476083764362116</v>
       </c>
     </row>
@@ -19593,12 +21151,8 @@
       <c r="D619">
         <v>195.56143</v>
       </c>
-      <c r="E619">
-        <f t="shared" si="1"/>
-        <v>1.9912996566426422E-2</v>
-      </c>
       <c r="F619">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>87.838345388484669</v>
       </c>
     </row>
@@ -19615,12 +21169,8 @@
       <c r="D620">
         <v>184.10988</v>
       </c>
-      <c r="E620">
-        <f t="shared" si="1"/>
-        <v>2.9824323174740819E-2</v>
-      </c>
       <c r="F620">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>82.694768742857235</v>
       </c>
     </row>
@@ -19637,12 +21187,8 @@
       <c r="D621">
         <v>168.12343000000001</v>
       </c>
-      <c r="E621">
-        <f t="shared" si="1"/>
-        <v>3.7438899696056294E-2</v>
-      </c>
       <c r="F621">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>75.514297027981044</v>
       </c>
     </row>
@@ -19659,12 +21205,8 @@
       <c r="D622">
         <v>149.9385</v>
       </c>
-      <c r="E622">
-        <f t="shared" si="1"/>
-        <v>-2.0336786904345816E-2</v>
-      </c>
       <c r="F622">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>67.346356334330892</v>
       </c>
     </row>
@@ -19681,12 +21223,8 @@
       <c r="D623">
         <v>159.27359999999999</v>
       </c>
-      <c r="E623">
-        <f t="shared" si="1"/>
-        <v>5.8731635531853454E-3</v>
-      </c>
       <c r="F623">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>71.539308584864344</v>
       </c>
     </row>
@@ -19703,12 +21241,8 @@
       <c r="D624">
         <v>156.48373000000001</v>
       </c>
-      <c r="E624">
-        <f t="shared" si="1"/>
-        <v>3.0322323928326123E-2</v>
-      </c>
       <c r="F624">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>70.286210953859253</v>
       </c>
     </row>
@@ -19725,12 +21259,8 @@
       <c r="D625">
         <v>142.67615000000001</v>
       </c>
-      <c r="E625">
-        <f t="shared" si="1"/>
-        <v>1.808593443418105E-2</v>
-      </c>
       <c r="F625">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>64.084400192815352</v>
       </c>
     </row>
@@ -19747,12 +21277,8 @@
       <c r="D626">
         <v>135.07401999999999</v>
       </c>
-      <c r="E626">
-        <f t="shared" si="1"/>
-        <v>1.3799013174697672E-2</v>
-      </c>
       <c r="F626">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>60.6698285125604</v>
       </c>
     </row>
@@ -19769,12 +21295,8 @@
       <c r="D627">
         <v>129.55915999999999</v>
       </c>
-      <c r="E627">
-        <f t="shared" si="1"/>
-        <v>7.2702867942258553E-2</v>
-      </c>
       <c r="F627">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>58.192774742555045</v>
       </c>
     </row>
@@ -19791,12 +21313,8 @@
       <c r="D628">
         <v>103.30584</v>
       </c>
-      <c r="E628">
-        <f t="shared" si="1"/>
-        <v>5.0649511559037963E-2</v>
-      </c>
       <c r="F628">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>46.400837090256161</v>
       </c>
     </row>
@@ -19813,12 +21331,8 @@
       <c r="D629">
         <v>88.390299999999996</v>
       </c>
-      <c r="E629">
-        <f t="shared" si="1"/>
-        <v>1.3241045556090625E-2</v>
-      </c>
       <c r="F629">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>39.701375165807363</v>
       </c>
     </row>
@@ -19835,12 +21349,8 @@
       <c r="D630">
         <v>84.925445999999994</v>
       </c>
-      <c r="E630">
-        <f t="shared" si="1"/>
-        <v>1.4793821466093204E-2</v>
-      </c>
       <c r="F630">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>38.145101812863111</v>
       </c>
     </row>
@@ -19857,12 +21367,8 @@
       <c r="D631">
         <v>81.211815000000001</v>
       </c>
-      <c r="E631">
-        <f t="shared" si="1"/>
-        <v>1.2145309209024902E-2</v>
-      </c>
       <c r="F631">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>36.477087816323085</v>
       </c>
     </row>
@@ -19879,12 +21385,8 @@
       <c r="D632">
         <v>78.288579999999996</v>
       </c>
-      <c r="E632">
-        <f t="shared" si="1"/>
-        <v>2.2559606755411354E-2</v>
-      </c>
       <c r="F632">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>35.164087979996935</v>
       </c>
     </row>
@@ -19901,12 +21403,8 @@
       <c r="D633">
         <v>73.108733999999998</v>
       </c>
-      <c r="E633">
-        <f t="shared" ref="E633:E696" si="3">1-(D634/D633)^(1/3)</f>
-        <v>1.6015505808920083E-2</v>
-      </c>
       <c r="F633">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>32.837509052817069</v>
       </c>
     </row>
@@ -19923,12 +21421,8 @@
       <c r="D634">
         <v>69.652069999999995</v>
       </c>
-      <c r="E634">
-        <f t="shared" si="3"/>
-        <v>1.3831565786541766E-2</v>
-      </c>
       <c r="F634">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>31.284914319162578</v>
       </c>
     </row>
@@ -19945,12 +21439,8 @@
       <c r="D635">
         <v>66.801670000000001</v>
       </c>
-      <c r="E635">
-        <f t="shared" si="3"/>
-        <v>7.333891635451617E-3</v>
-      </c>
       <c r="F635">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>30.004629041562918</v>
       </c>
     </row>
@@ -19967,12 +21457,8 @@
       <c r="D636">
         <v>65.342674000000002</v>
       </c>
-      <c r="E636">
-        <f t="shared" si="3"/>
-        <v>7.1473876457885943E-3</v>
-      </c>
       <c r="F636">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>29.349306595984476</v>
       </c>
     </row>
@@ -19989,12 +21475,8 @@
       <c r="D637">
         <v>63.951576000000003</v>
       </c>
-      <c r="E637">
-        <f t="shared" si="3"/>
-        <v>4.9333928938710692E-3</v>
-      </c>
       <c r="F637">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>28.72448120688178</v>
       </c>
     </row>
@@ -20011,12 +21493,8 @@
       <c r="D638">
         <v>63.009743</v>
       </c>
-      <c r="E638">
-        <f t="shared" si="3"/>
-        <v>7.1288806600395827E-3</v>
-      </c>
       <c r="F638">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>28.301447624276697</v>
       </c>
     </row>
@@ -20033,12 +21511,8 @@
       <c r="D639">
         <v>61.671759999999999</v>
       </c>
-      <c r="E639">
-        <f t="shared" si="3"/>
-        <v>8.6537300093257885E-3</v>
-      </c>
       <c r="F639">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>27.700479361373727</v>
       </c>
     </row>
@@ -20055,12 +21529,8 @@
       <c r="D640">
         <v>60.084502999999998</v>
       </c>
-      <c r="E640">
-        <f t="shared" si="3"/>
-        <v>1.1947355742268573E-2</v>
-      </c>
       <c r="F640">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>26.987547222422346</v>
       </c>
     </row>
@@ -20077,12 +21547,8 @@
       <c r="D641">
         <v>57.956577000000003</v>
       </c>
-      <c r="E641">
-        <f t="shared" si="3"/>
-        <v>1.1728673591114958E-2</v>
-      </c>
       <c r="F641">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>26.031768268724083</v>
       </c>
     </row>
@@ -20099,12 +21565,8 @@
       <c r="D642">
         <v>55.941139999999997</v>
       </c>
-      <c r="E642">
-        <f t="shared" si="3"/>
-        <v>1.2380740851375749E-2</v>
-      </c>
       <c r="F642">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>25.126514859016801</v>
       </c>
     </row>
@@ -20121,12 +21583,8 @@
       <c r="D643">
         <v>53.888979999999997</v>
       </c>
-      <c r="E643">
-        <f t="shared" si="3"/>
-        <v>5.0104081095577291E-2</v>
-      </c>
       <c r="F643">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>24.204766951607695</v>
       </c>
     </row>
@@ -20143,12 +21601,8 @@
       <c r="D644">
         <v>46.18788</v>
       </c>
-      <c r="E644">
-        <f t="shared" si="3"/>
-        <v>5.9205074672234459E-2</v>
-      </c>
       <c r="F644">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>20.74574191956912</v>
       </c>
     </row>
@@ -20165,12 +21619,8 @@
       <c r="D645">
         <v>38.460323000000002</v>
       </c>
-      <c r="E645">
-        <f t="shared" si="3"/>
-        <v>6.9768548656419793E-2</v>
-      </c>
       <c r="F645">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>17.274833464997062</v>
       </c>
     </row>
@@ -20187,12 +21637,8 @@
       <c r="D646">
         <v>30.958932999999998</v>
       </c>
-      <c r="E646">
-        <f t="shared" si="3"/>
-        <v>8.6147705758235493E-2</v>
-      </c>
       <c r="F646">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>13.905510149485792</v>
       </c>
     </row>
@@ -20209,12 +21655,9 @@
       <c r="D647" s="11">
         <v>23.627295</v>
       </c>
-      <c r="E647" s="11">
-        <f t="shared" si="3"/>
-        <v>0.10779382001893678</v>
-      </c>
+      <c r="E647" s="11"/>
       <c r="F647">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>10.612432619282936</v>
       </c>
     </row>
@@ -20231,12 +21674,9 @@
       <c r="D648" s="11">
         <v>16.780684999999998</v>
       </c>
-      <c r="E648" s="11">
-        <f t="shared" si="3"/>
-        <v>1.6929730042629876E-2</v>
-      </c>
+      <c r="E648" s="11"/>
       <c r="F648">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>7.537210199809663</v>
       </c>
     </row>
@@ -20253,12 +21693,9 @@
       <c r="D649" s="11">
         <v>15.942755</v>
       </c>
-      <c r="E649" s="11">
-        <f t="shared" si="3"/>
-        <v>1.5501580437288887E-2</v>
-      </c>
+      <c r="E649" s="11"/>
       <c r="F649">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>7.1608456745994893</v>
       </c>
     </row>
@@ -20275,12 +21712,8 @@
       <c r="D650">
         <v>15.212775000000001</v>
       </c>
-      <c r="E650">
-        <f t="shared" si="3"/>
-        <v>1.6357791297218816E-2</v>
-      </c>
       <c r="F650">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>6.8329679567556072</v>
       </c>
     </row>
@@ -20297,12 +21730,8 @@
       <c r="D651">
         <v>14.478377999999999</v>
       </c>
-      <c r="E651">
-        <f t="shared" si="3"/>
-        <v>2.0836011088602779E-2</v>
-      </c>
       <c r="F651">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>6.5031062997904936</v>
       </c>
     </row>
@@ -20319,12 +21748,8 @@
       <c r="D652">
         <v>13.592089</v>
       </c>
-      <c r="E652">
-        <f t="shared" si="3"/>
-        <v>2.1328547036540191E-2</v>
-      </c>
       <c r="F652">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>6.1050208526958665</v>
       </c>
     </row>
@@ -20341,12 +21766,8 @@
       <c r="D653">
         <v>12.740807999999999</v>
       </c>
-      <c r="E653">
-        <f t="shared" si="3"/>
-        <v>2.2366438626718943E-2</v>
-      </c>
       <c r="F653">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>5.7226595941355534</v>
       </c>
     </row>
@@ -20363,12 +21784,8 @@
       <c r="D654">
         <v>11.904887</v>
       </c>
-      <c r="E654">
-        <f t="shared" si="3"/>
-        <v>2.406217767721075E-2</v>
-      </c>
       <c r="F654">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>5.3471974310930381</v>
       </c>
     </row>
@@ -20385,12 +21802,8 @@
       <c r="D655">
         <v>11.066027</v>
       </c>
-      <c r="E655">
-        <f t="shared" si="3"/>
-        <v>2.1967540277233577E-2</v>
-      </c>
       <c r="F655">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4.9704151872089337</v>
       </c>
     </row>
@@ -20407,12 +21820,8 @@
       <c r="D656">
         <v>10.352650000000001</v>
       </c>
-      <c r="E656">
-        <f t="shared" si="3"/>
-        <v>1.9826699159524175E-2</v>
-      </c>
       <c r="F656">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4.6499948705943481</v>
       </c>
     </row>
@@ -20429,12 +21838,8 @@
       <c r="D657">
         <v>9.7490015000000003</v>
       </c>
-      <c r="E657">
-        <f t="shared" si="3"/>
-        <v>2.2958645247014853E-2</v>
-      </c>
       <c r="F657">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4.3788601921649635</v>
       </c>
     </row>
@@ -20451,12 +21856,8 @@
       <c r="D658">
         <v>9.0928280000000008</v>
       </c>
-      <c r="E658">
-        <f t="shared" si="3"/>
-        <v>2.3668345725598394E-2</v>
-      </c>
       <c r="F658">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4.0841333918558691</v>
       </c>
     </row>
@@ -20473,12 +21874,8 @@
       <c r="D659">
         <v>8.4623519999999992</v>
       </c>
-      <c r="E659">
-        <f t="shared" si="3"/>
-        <v>2.0443811982539861E-2</v>
-      </c>
       <c r="F659">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>3.8009488771632212</v>
       </c>
     </row>
@@ -20495,12 +21892,8 @@
       <c r="D660">
         <v>7.9538820000000001</v>
       </c>
-      <c r="E660">
-        <f t="shared" si="3"/>
-        <v>2.2151804170413625E-2</v>
-      </c>
       <c r="F660">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>3.5725645608914349</v>
       </c>
     </row>
@@ -20517,12 +21910,8 @@
       <c r="D661">
         <v>7.4369259999999997</v>
       </c>
-      <c r="E661">
-        <f t="shared" si="3"/>
-        <v>2.334562958988784E-2</v>
-      </c>
       <c r="F661">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>3.3403686740100116</v>
       </c>
     </row>
@@ -20539,12 +21928,8 @@
       <c r="D662">
         <v>6.9281319999999997</v>
       </c>
-      <c r="E662">
-        <f t="shared" si="3"/>
-        <v>2.5528528558412034E-2</v>
-      </c>
       <c r="F662">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>3.1118388299421462</v>
       </c>
     </row>
@@ -20561,12 +21946,8 @@
       <c r="D663">
         <v>6.4109670000000003</v>
       </c>
-      <c r="E663">
-        <f t="shared" si="3"/>
-        <v>2.7617084924857815E-2</v>
-      </c>
       <c r="F663">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.8795490686490548</v>
       </c>
     </row>
@@ -20583,12 +21964,8 @@
       <c r="D664">
         <v>5.8943443000000002</v>
       </c>
-      <c r="E664">
-        <f t="shared" si="3"/>
-        <v>3.6385318457765825E-2</v>
-      </c>
       <c r="F664">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.6475028867504489</v>
       </c>
     </row>
@@ -20605,12 +21982,8 @@
       <c r="D665">
         <v>5.2740679999999998</v>
       </c>
-      <c r="E665">
-        <f t="shared" si="3"/>
-        <v>3.4655949013951082E-2</v>
-      </c>
       <c r="F665">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.368899667927129</v>
       </c>
     </row>
@@ -20627,12 +22000,8 @@
       <c r="D666">
         <v>4.7445180000000002</v>
       </c>
-      <c r="E666">
-        <f t="shared" si="3"/>
-        <v>3.2192204916556943E-2</v>
-      </c>
       <c r="F666">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.1310470617129482</v>
       </c>
     </row>
@@ -20649,12 +22018,8 @@
       <c r="D667">
         <v>4.3009009999999996</v>
       </c>
-      <c r="E667">
-        <f t="shared" si="3"/>
-        <v>2.583682763896944E-2</v>
-      </c>
       <c r="F667">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.9317921101296869</v>
       </c>
     </row>
@@ -20671,12 +22036,8 @@
       <c r="D668">
         <v>3.9760749999999998</v>
       </c>
-      <c r="E668">
-        <f t="shared" si="3"/>
-        <v>1.843023687212475E-2</v>
-      </c>
       <c r="F668">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.7858933080031125</v>
       </c>
     </row>
@@ -20693,12 +22054,8 @@
       <c r="D669">
         <v>3.7602617999999999</v>
       </c>
-      <c r="E669">
-        <f t="shared" si="3"/>
-        <v>4.119408809546754E-3</v>
-      </c>
       <c r="F669">
-        <f t="shared" ref="F669:F727" si="4">D669/$D$604*100</f>
+        <f t="shared" ref="F669:F727" si="1">D669/$D$604*100</f>
         <v>1.6889586803467587</v>
       </c>
     </row>
@@ -20715,12 +22072,8 @@
       <c r="D670">
         <v>3.7139828000000001</v>
       </c>
-      <c r="E670">
-        <f t="shared" si="3"/>
-        <v>3.6289482169470366E-3</v>
-      </c>
       <c r="F670">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.6681720109803417</v>
       </c>
     </row>
@@ -20737,12 +22090,8 @@
       <c r="D671">
         <v>3.6736958</v>
       </c>
-      <c r="E671">
-        <f t="shared" si="3"/>
-        <v>1.2669333061525734E-3</v>
-      </c>
       <c r="F671">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.6500767075216491</v>
       </c>
     </row>
@@ -20759,12 +22108,8 @@
       <c r="D672">
         <v>3.6597504999999999</v>
       </c>
-      <c r="E672">
-        <f t="shared" si="3"/>
-        <v>4.6659242541748913E-3</v>
-      </c>
       <c r="F672">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.6438130384640746</v>
       </c>
     </row>
@@ -20781,12 +22126,8 @@
       <c r="D673">
         <v>3.6087608000000002</v>
       </c>
-      <c r="E673">
-        <f t="shared" si="3"/>
-        <v>9.5034924489183492E-3</v>
-      </c>
       <c r="F673">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.6209105117242404</v>
       </c>
     </row>
@@ -20803,12 +22144,8 @@
       <c r="D674">
         <v>3.5068480000000002</v>
       </c>
-      <c r="E674">
-        <f t="shared" si="3"/>
-        <v>9.1601795232674199E-3</v>
-      </c>
       <c r="F674">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.5751353722915435</v>
       </c>
     </row>
@@ -20825,12 +22162,8 @@
       <c r="D675">
         <v>3.4113579999999999</v>
       </c>
-      <c r="E675">
-        <f t="shared" si="3"/>
-        <v>9.5830300360634224E-3</v>
-      </c>
       <c r="F675">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.5322450968361718</v>
       </c>
     </row>
@@ -20847,12 +22180,8 @@
       <c r="D676">
         <v>3.3142214000000001</v>
       </c>
-      <c r="E676">
-        <f t="shared" si="3"/>
-        <v>1.7797124608409098E-2</v>
-      </c>
       <c r="F676">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.4886152347480133</v>
       </c>
     </row>
@@ -20869,12 +22198,8 @@
       <c r="D677">
         <v>3.1404011000000001</v>
       </c>
-      <c r="E677">
-        <f t="shared" si="3"/>
-        <v>8.3577386110472718E-3</v>
-      </c>
       <c r="F677">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.4105421323631002</v>
       </c>
     </row>
@@ -20891,12 +22216,8 @@
       <c r="D678">
         <v>3.0623174</v>
       </c>
-      <c r="E678">
-        <f t="shared" si="3"/>
-        <v>-5.2085537318125041E-3</v>
-      </c>
       <c r="F678">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.3754700682561298</v>
       </c>
     </row>
@@ -20913,12 +22234,8 @@
       <c r="D679">
         <v>3.1104178</v>
       </c>
-      <c r="E679">
-        <f t="shared" si="3"/>
-        <v>-8.5486937121705964E-3</v>
-      </c>
       <c r="F679">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.3970748373996376</v>
       </c>
     </row>
@@ -20935,12 +22252,8 @@
       <c r="D680">
         <v>3.1908717000000002</v>
       </c>
-      <c r="E680">
-        <f t="shared" si="3"/>
-        <v>-9.09620314308901E-3</v>
-      </c>
       <c r="F680">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.4332115002173038</v>
       </c>
     </row>
@@ -20957,12 +22270,8 @@
       <c r="D681">
         <v>3.2787405999999999</v>
       </c>
-      <c r="E681">
-        <f t="shared" si="3"/>
-        <v>-1.5817404375966682E-2</v>
-      </c>
       <c r="F681">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.472678683429792</v>
       </c>
     </row>
@@ -20979,12 +22288,8 @@
       <c r="D682">
         <v>3.436798</v>
       </c>
-      <c r="E682">
-        <f t="shared" si="3"/>
-        <v>-9.8898951459949203E-3</v>
-      </c>
       <c r="F682">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.5436717237875244</v>
       </c>
     </row>
@@ -21001,12 +22306,8 @@
       <c r="D683">
         <v>3.5397785000000002</v>
       </c>
-      <c r="E683">
-        <f t="shared" si="3"/>
-        <v>-8.6230451431159594E-3</v>
-      </c>
       <c r="F683">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.5899264312074839</v>
       </c>
     </row>
@@ -21023,12 +22324,8 @@
       <c r="D684">
         <v>3.6321414000000001</v>
       </c>
-      <c r="E684">
-        <f t="shared" si="3"/>
-        <v>-1.0126734197899223E-2</v>
-      </c>
       <c r="F684">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.6314121388507654</v>
       </c>
     </row>
@@ -21045,12 +22342,8 @@
       <c r="D685">
         <v>3.7436077999999999</v>
       </c>
-      <c r="E685">
-        <f t="shared" si="3"/>
-        <v>-1.1234562625229483E-2</v>
-      </c>
       <c r="F685">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.6814783719643753</v>
       </c>
     </row>
@@ -21067,12 +22360,8 @@
       <c r="D686">
         <v>3.8712040000000001</v>
       </c>
-      <c r="E686">
-        <f t="shared" si="3"/>
-        <v>-7.2308780226522096E-3</v>
-      </c>
       <c r="F686">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.7387894638594297</v>
       </c>
     </row>
@@ -21089,12 +22378,8 @@
       <c r="D687">
         <v>3.9557893000000002</v>
       </c>
-      <c r="E687">
-        <f t="shared" si="3"/>
-        <v>-5.799414939487324E-3</v>
-      </c>
       <c r="F687">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.7767817857410428</v>
       </c>
     </row>
@@ -21111,12 +22396,8 @@
       <c r="D688">
         <v>4.0250130000000004</v>
       </c>
-      <c r="E688">
-        <f t="shared" si="3"/>
-        <v>1.2095745206757158E-3</v>
-      </c>
       <c r="F688">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.8078742934490755</v>
       </c>
     </row>
@@ -21133,12 +22414,8 @@
       <c r="D689">
         <v>4.0104249999999997</v>
       </c>
-      <c r="E689">
-        <f t="shared" si="3"/>
-        <v>6.5777242468024744E-3</v>
-      </c>
       <c r="F689">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.801321949346625</v>
       </c>
     </row>
@@ -21155,12 +22432,8 @@
       <c r="D690">
         <v>3.9318059999999999</v>
       </c>
-      <c r="E690">
-        <f t="shared" si="3"/>
-        <v>1.065908713488628E-2</v>
-      </c>
       <c r="F690">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.76600944996422</v>
       </c>
     </row>
@@ -21177,12 +22450,8 @@
       <c r="D691">
         <v>3.8074129999999999</v>
       </c>
-      <c r="E691">
-        <f t="shared" si="3"/>
-        <v>8.6881832298524309E-3</v>
-      </c>
       <c r="F691">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.71013710694694</v>
       </c>
     </row>
@@ -21199,12 +22468,8 @@
       <c r="D692">
         <v>3.7090342000000001</v>
       </c>
-      <c r="E692">
-        <f t="shared" si="3"/>
-        <v>5.4345264507075219E-3</v>
-      </c>
       <c r="F692">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.6659492984751743</v>
       </c>
     </row>
@@ -21221,12 +22486,8 @@
       <c r="D693">
         <v>3.6488917000000001</v>
       </c>
-      <c r="E693">
-        <f t="shared" si="3"/>
-        <v>6.1782488070024622E-3</v>
-      </c>
       <c r="F693">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.6389357013280939</v>
       </c>
     </row>
@@ -21243,12 +22504,8 @@
       <c r="D694">
         <v>3.5816773999999998</v>
       </c>
-      <c r="E694">
-        <f t="shared" si="3"/>
-        <v>5.2075116059974169E-3</v>
-      </c>
       <c r="F694">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.608745735451667</v>
       </c>
     </row>
@@ -21265,12 +22522,8 @@
       <c r="D695">
         <v>3.5260134000000001</v>
       </c>
-      <c r="E695">
-        <f t="shared" si="3"/>
-        <v>1.0884745995861644E-3</v>
-      </c>
       <c r="F695">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.5837437007574811</v>
       </c>
     </row>
@@ -21287,12 +22540,8 @@
       <c r="D696">
         <v>3.5145119999999999</v>
       </c>
-      <c r="E696">
-        <f t="shared" si="3"/>
-        <v>2.5774353458439814E-3</v>
-      </c>
       <c r="F696">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.5785777334926117</v>
       </c>
     </row>
@@ -21309,12 +22558,8 @@
       <c r="D697">
         <v>3.4874067000000002</v>
       </c>
-      <c r="E697">
-        <f t="shared" ref="E697:E726" si="5">1-(D698/D697)^(1/3)</f>
-        <v>4.9125686779992739E-3</v>
-      </c>
       <c r="F697">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.566403120619007</v>
       </c>
     </row>
@@ -21331,12 +22576,8 @@
       <c r="D698">
         <v>3.4362623999999999</v>
       </c>
-      <c r="E698">
-        <f t="shared" si="5"/>
-        <v>5.4295183854543572E-3</v>
-      </c>
       <c r="F698">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.5434311537641303</v>
       </c>
     </row>
@@ -21353,12 +22594,8 @@
       <c r="D699">
         <v>3.3805939999999999</v>
       </c>
-      <c r="E699">
-        <f t="shared" si="5"/>
-        <v>1.0360865108667849E-2</v>
-      </c>
       <c r="F699">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.518427142766541</v>
       </c>
     </row>
@@ -21375,12 +22612,8 @@
       <c r="D700">
         <v>3.2766012999999998</v>
       </c>
-      <c r="E700">
-        <f t="shared" si="5"/>
-        <v>1.6871011318583373E-2</v>
-      </c>
       <c r="F700">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.4717177957317953</v>
       </c>
     </row>
@@ -21397,12 +22630,8 @@
       <c r="D701">
         <v>3.1135446999999998</v>
       </c>
-      <c r="E701">
-        <f t="shared" si="5"/>
-        <v>1.956639995145959E-2</v>
-      </c>
       <c r="F701">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.3984793153797548</v>
       </c>
     </row>
@@ -21419,12 +22648,8 @@
       <c r="D702">
         <v>2.9343347999999998</v>
       </c>
-      <c r="E702">
-        <f t="shared" si="5"/>
-        <v>2.4065231082712413E-2</v>
-      </c>
       <c r="F702">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.3179854209894559</v>
       </c>
     </row>
@@ -21441,12 +22666,8 @@
       <c r="D703">
         <v>2.7275456999999999</v>
       </c>
-      <c r="E703">
-        <f t="shared" si="5"/>
-        <v>2.5840076006339197E-2</v>
-      </c>
       <c r="F703">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.2251040568657949</v>
       </c>
     </row>
@@ -21463,12 +22684,8 @@
       <c r="D704">
         <v>2.5215223</v>
       </c>
-      <c r="E704">
-        <f t="shared" si="5"/>
-        <v>2.5009036716553301E-2</v>
-      </c>
       <c r="F704">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.1325666144503352</v>
       </c>
     </row>
@@ -21485,12 +22702,8 @@
       <c r="D705">
         <v>2.3370316</v>
       </c>
-      <c r="E705">
-        <f t="shared" si="5"/>
-        <v>2.0595992025693288E-2</v>
-      </c>
       <c r="F705">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.0497007966479019</v>
       </c>
     </row>
@@ -21507,12 +22720,8 @@
       <c r="D706">
         <v>2.1955847999999998</v>
       </c>
-      <c r="E706">
-        <f t="shared" si="5"/>
-        <v>1.8489529158601026E-2</v>
-      </c>
       <c r="F706">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.9861685711344359</v>
       </c>
     </row>
@@ -21529,12 +22738,8 @@
       <c r="D707">
         <v>2.0760367</v>
       </c>
-      <c r="E707">
-        <f t="shared" si="5"/>
-        <v>6.5269798880100982E-3</v>
-      </c>
       <c r="F707">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.93247236274438117</v>
       </c>
     </row>
@@ -21551,12 +22756,8 @@
       <c r="D708">
         <v>2.0356507000000001</v>
       </c>
-      <c r="E708">
-        <f t="shared" si="5"/>
-        <v>-2.4338809585555676E-3</v>
-      </c>
       <c r="F708">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.91433259245910903</v>
       </c>
     </row>
@@ -21573,12 +22774,8 @@
       <c r="D709">
         <v>2.0505504999999999</v>
       </c>
-      <c r="E709">
-        <f t="shared" si="5"/>
-        <v>-1.8508314952853766E-2</v>
-      </c>
       <c r="F709">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.92102498460729154</v>
       </c>
     </row>
@@ -21595,12 +22792,8 @@
       <c r="D710">
         <v>2.1665274999999999</v>
       </c>
-      <c r="E710">
-        <f t="shared" si="5"/>
-        <v>-1.7634309812835536E-2</v>
-      </c>
       <c r="F710">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.97311719820544462</v>
       </c>
     </row>
@@ -21617,12 +22810,8 @@
       <c r="D711">
         <v>2.2831762000000002</v>
       </c>
-      <c r="E711">
-        <f t="shared" si="5"/>
-        <v>-2.4252674904408078E-2</v>
-      </c>
       <c r="F711">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.0255111124845424</v>
       </c>
     </row>
@@ -21639,12 +22828,8 @@
       <c r="D712">
         <v>2.453357</v>
       </c>
-      <c r="E712">
-        <f t="shared" si="5"/>
-        <v>-1.0243152365097208E-2</v>
-      </c>
       <c r="F712">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.1019494975428261</v>
       </c>
     </row>
@@ -21661,12 +22846,8 @@
       <c r="D713">
         <v>2.5295222000000002</v>
       </c>
-      <c r="E713">
-        <f t="shared" si="5"/>
-        <v>3.5429010160741292E-3</v>
-      </c>
       <c r="F713">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.1361598484498685</v>
       </c>
     </row>
@@ -21683,12 +22864,8 @@
       <c r="D714">
         <v>2.5027317999999998</v>
       </c>
-      <c r="E714">
-        <f t="shared" si="5"/>
-        <v>1.6867069977601901E-2</v>
-      </c>
       <c r="F714">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.1241266760175761</v>
       </c>
     </row>
@@ -21705,12 +22882,8 @@
       <c r="D715">
         <v>2.3782146000000002</v>
       </c>
-      <c r="E715">
-        <f t="shared" si="5"/>
-        <v>1.9143954595589596E-2</v>
-      </c>
       <c r="F715">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.068198547345133</v>
       </c>
     </row>
@@ -21727,12 +22900,8 @@
       <c r="D716">
         <v>2.2442274000000002</v>
       </c>
-      <c r="E716">
-        <f t="shared" si="5"/>
-        <v>2.763102049446442E-2</v>
-      </c>
       <c r="F716">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1.0080168747564431</v>
       </c>
     </row>
@@ -21749,12 +22918,8 @@
       <c r="D717">
         <v>2.0632893999999999</v>
       </c>
-      <c r="E717">
-        <f t="shared" si="5"/>
-        <v>2.3346030845981747E-2</v>
-      </c>
       <c r="F717">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.92674678720440562</v>
       </c>
     </row>
@@ -21771,12 +22936,8 @@
       <c r="D718">
         <v>1.9221280000000001</v>
       </c>
-      <c r="E718">
-        <f t="shared" si="5"/>
-        <v>1.0230212897538116E-2</v>
-      </c>
       <c r="F718">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.86334275191625076</v>
       </c>
     </row>
@@ -21793,12 +22954,8 @@
       <c r="D719">
         <v>1.8637381</v>
       </c>
-      <c r="E719">
-        <f t="shared" si="5"/>
-        <v>7.4765990171041796E-3</v>
-      </c>
       <c r="F719">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.83711635234758797</v>
       </c>
     </row>
@@ -21815,12 +22972,8 @@
       <c r="D720">
         <v>1.8222465999999999</v>
       </c>
-      <c r="E720">
-        <f t="shared" si="5"/>
-        <v>3.5591538829646829E-3</v>
-      </c>
       <c r="F720">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.81848003583217743</v>
       </c>
     </row>
@@ -21837,12 +22990,8 @@
       <c r="D721">
         <v>1.8028588000000001</v>
       </c>
-      <c r="E721">
-        <f t="shared" si="5"/>
-        <v>-5.2470566409223984E-4</v>
-      </c>
       <c r="F721">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.80977181421238842</v>
       </c>
     </row>
@@ -21859,12 +23008,8 @@
       <c r="D722">
         <v>1.8056981999999999</v>
       </c>
-      <c r="E722">
-        <f t="shared" si="5"/>
-        <v>-6.8189765432347116E-3</v>
-      </c>
       <c r="F722">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.81104715873147915</v>
       </c>
     </row>
@@ -21881,12 +23026,8 @@
       <c r="D723">
         <v>1.8428897</v>
       </c>
-      <c r="E723">
-        <f t="shared" si="5"/>
-        <v>-7.0837159838348374E-3</v>
-      </c>
       <c r="F723">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.82775208782979792</v>
       </c>
     </row>
@@ -21903,12 +23044,8 @@
       <c r="D724">
         <v>1.8823312999999999</v>
       </c>
-      <c r="E724">
-        <f t="shared" si="5"/>
-        <v>-8.1496852073827952E-3</v>
-      </c>
       <c r="F724">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.84546767153909297</v>
       </c>
     </row>
@@ -21925,12 +23062,8 @@
       <c r="D725">
         <v>1.9287285999999999</v>
       </c>
-      <c r="E725">
-        <f t="shared" si="5"/>
-        <v>-2.1830148773220204E-2</v>
-      </c>
       <c r="F725">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.86630747651747309</v>
       </c>
     </row>
@@ -21947,12 +23080,8 @@
       <c r="D726">
         <v>2.0578194000000001</v>
       </c>
-      <c r="E726">
-        <f t="shared" si="5"/>
-        <v>-1.4438491684777732E-2</v>
-      </c>
       <c r="F726">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.92428988274591906</v>
       </c>
     </row>
@@ -21970,7 +23099,7 @@
         <v>2.1482480000000002</v>
       </c>
       <c r="F727">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.96490678046341449</v>
       </c>
     </row>
@@ -22011,7 +23140,7 @@
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
@@ -22919,7 +24048,7 @@
       <c r="J8" s="18"/>
       <c r="K8" s="18"/>
       <c r="M8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="N8" t="s">
         <v>22</v>
@@ -22977,7 +24106,7 @@
         <v>39923.748099999997</v>
       </c>
       <c r="Q9">
-        <f t="shared" ref="Q9:Q40" si="0">P9/$P$14*100</f>
+        <f>P9/$P$22*100</f>
         <v>1001.8387007934033</v>
       </c>
     </row>
@@ -23026,7 +24155,7 @@
         <v>39722.835899999998</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="Q10:Q73" si="0">P10/$P$22*100</f>
         <v>996.797049470552</v>
       </c>
     </row>
@@ -24625,7 +25754,7 @@
         <v>0.5212</v>
       </c>
       <c r="Q41">
-        <f t="shared" ref="Q41:Q72" si="2">P41/$P$14*100</f>
+        <f t="shared" si="0"/>
         <v>1.3078890527653684E-2</v>
       </c>
     </row>
@@ -24678,7 +25807,7 @@
         <v>0.5212</v>
       </c>
       <c r="Q42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.3078890527653684E-2</v>
       </c>
     </row>
@@ -24731,7 +25860,7 @@
         <v>0.5212</v>
       </c>
       <c r="Q43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.3078890527653684E-2</v>
       </c>
     </row>
@@ -24784,7 +25913,7 @@
         <v>0.1779</v>
       </c>
       <c r="Q44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4.4641876916147174E-3</v>
       </c>
     </row>
@@ -24837,7 +25966,7 @@
         <v>0.1779</v>
       </c>
       <c r="Q45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4.4641876916147174E-3</v>
       </c>
     </row>
@@ -24890,7 +26019,7 @@
         <v>0.1779</v>
       </c>
       <c r="Q46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4.4641876916147174E-3</v>
       </c>
     </row>
@@ -24943,7 +26072,7 @@
         <v>0.1779</v>
       </c>
       <c r="Q47">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4.4641876916147174E-3</v>
       </c>
     </row>
@@ -24996,7 +26125,7 @@
         <v>9.2600000000000002E-2</v>
       </c>
       <c r="Q48">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.3236862295869746E-3</v>
       </c>
     </row>
@@ -25049,7 +26178,7 @@
         <v>9.2600000000000002E-2</v>
       </c>
       <c r="Q49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.3236862295869746E-3</v>
       </c>
     </row>
@@ -25102,7 +26231,7 @@
         <v>9.2600000000000002E-2</v>
       </c>
       <c r="Q50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.3236862295869746E-3</v>
       </c>
     </row>
@@ -25155,7 +26284,7 @@
         <v>9.2600000000000002E-2</v>
       </c>
       <c r="Q51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.3236862295869746E-3</v>
       </c>
     </row>
@@ -25208,7 +26337,7 @@
         <v>9.2600000000000002E-2</v>
       </c>
       <c r="Q52">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.3236862295869746E-3</v>
       </c>
     </row>
@@ -25261,7 +26390,7 @@
         <v>9.2600000000000002E-2</v>
       </c>
       <c r="Q53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.3236862295869746E-3</v>
       </c>
     </row>
@@ -25314,7 +26443,7 @@
         <v>1.26E-2</v>
       </c>
       <c r="Q54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>3.161819275679901E-4</v>
       </c>
     </row>
@@ -25367,7 +26496,7 @@
         <v>2.8999999999999998E-3</v>
       </c>
       <c r="Q55">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>7.2772030948188199E-5</v>
       </c>
     </row>
@@ -25420,7 +26549,7 @@
         <v>2.8999999999999998E-3</v>
       </c>
       <c r="Q56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>7.2772030948188199E-5</v>
       </c>
     </row>
@@ -25473,7 +26602,7 @@
         <v>2.8999999999999998E-3</v>
       </c>
       <c r="Q57">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>7.2772030948188199E-5</v>
       </c>
     </row>
@@ -25526,7 +26655,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.2546901887618654E-5</v>
       </c>
     </row>
@@ -25579,7 +26708,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q59">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.2546901887618654E-5</v>
       </c>
     </row>
@@ -25632,7 +26761,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q60">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.2546901887618654E-5</v>
       </c>
     </row>
@@ -25685,7 +26814,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.2546901887618654E-5</v>
       </c>
     </row>
@@ -25738,7 +26867,7 @@
         <v>1E-4</v>
       </c>
       <c r="Q62">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.509380377523731E-6</v>
       </c>
     </row>
@@ -25791,7 +26920,7 @@
         <v>1E-4</v>
       </c>
       <c r="Q63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.509380377523731E-6</v>
       </c>
     </row>
@@ -25844,7 +26973,7 @@
         <v>1.9000000000000001E-5</v>
       </c>
       <c r="Q64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4.7678227172950892E-7</v>
       </c>
     </row>
@@ -25897,7 +27026,7 @@
         <v>1.9000000000000001E-5</v>
       </c>
       <c r="Q65">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4.7678227172950892E-7</v>
       </c>
     </row>
@@ -25950,7 +27079,7 @@
         <v>6.0000000000000002E-6</v>
       </c>
       <c r="Q66">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.5056282265142386E-7</v>
       </c>
     </row>
@@ -26003,7 +27132,7 @@
         <v>6.0000000000000002E-6</v>
       </c>
       <c r="Q67">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.5056282265142386E-7</v>
       </c>
     </row>
@@ -26056,7 +27185,7 @@
         <v>1.9999999999999999E-6</v>
       </c>
       <c r="Q68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>5.0187607550474612E-8</v>
       </c>
     </row>
@@ -26109,7 +27238,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="Q69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.5093803775237306E-8</v>
       </c>
     </row>
@@ -26162,7 +27291,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="Q70">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.5093803775237306E-8</v>
       </c>
     </row>
@@ -26215,7 +27344,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="Q71">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.5093803775237306E-8</v>
       </c>
     </row>
@@ -26268,7 +27397,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="Q72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.5093803775237306E-8</v>
       </c>
     </row>
@@ -26321,7 +27450,7 @@
         <v>2.3799999999999999E-7</v>
       </c>
       <c r="Q73">
-        <f t="shared" ref="Q73:Q76" si="3">P73/$P$14*100</f>
+        <f t="shared" si="0"/>
         <v>5.972325298506479E-9</v>
       </c>
     </row>
@@ -26374,7 +27503,7 @@
         <v>1.49E-7</v>
       </c>
       <c r="Q74">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="Q74:Q76" si="2">P74/$P$22*100</f>
         <v>3.7389767625103586E-9</v>
       </c>
     </row>
@@ -26427,7 +27556,7 @@
         <v>1.49E-7</v>
       </c>
       <c r="Q75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.7389767625103586E-9</v>
       </c>
     </row>
@@ -26480,7 +27609,7 @@
         <v>4.0900000000000002E-8</v>
       </c>
       <c r="Q76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1.0263365744072059E-9</v>
       </c>
     </row>
@@ -28175,7 +29304,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>4</v>
@@ -42214,7 +43343,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
@@ -42224,7 +43353,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">

--- a/data/Cost declines by tech.xlsx
+++ b/data/Cost declines by tech.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9a072a59b81ab8f9/Documents/Work/Clients ^0 prospects/EpochAI/inference-cost/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1237" documentId="8_{237EF59B-240D-4B45-BBDB-12EDD86E70D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D5CFCC3-0D9C-47D3-9E82-7716AAE62D33}"/>
+  <xr:revisionPtr revIDLastSave="1254" documentId="8_{237EF59B-240D-4B45-BBDB-12EDD86E70D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CB458B8-6EB5-40FF-8D89-91F2292BC039}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" xr2:uid="{55FDA7DF-2265-4D1B-B569-857BE3FE3144}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" activeTab="1" xr2:uid="{55FDA7DF-2265-4D1B-B569-857BE3FE3144}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="4" r:id="rId1"/>
-    <sheet name="Electricity" sheetId="8" r:id="rId2"/>
-    <sheet name="Illumination" sheetId="6" r:id="rId3"/>
-    <sheet name="Lithium batteries" sheetId="5" r:id="rId4"/>
-    <sheet name="Compute" sheetId="7" r:id="rId5"/>
-    <sheet name="DNA sequencing" sheetId="1" r:id="rId6"/>
-    <sheet name="CPI" sheetId="3" r:id="rId7"/>
-    <sheet name="Sources" sheetId="2" r:id="rId8"/>
+    <sheet name="Figure data" sheetId="9" r:id="rId2"/>
+    <sheet name="Electricity" sheetId="8" r:id="rId3"/>
+    <sheet name="Illumination" sheetId="6" r:id="rId4"/>
+    <sheet name="Lithium batteries" sheetId="5" r:id="rId5"/>
+    <sheet name="Compute" sheetId="7" r:id="rId6"/>
+    <sheet name="DNA sequencing" sheetId="1" r:id="rId7"/>
+    <sheet name="CPI" sheetId="3" r:id="rId8"/>
+    <sheet name="Sources" sheetId="2" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Electricity!$A$6:$B$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Electricity!$A$6:$B$140</definedName>
     <definedName name="fn">'DNA sequencing'!$J$20</definedName>
     <definedName name="Year_span">'DNA sequencing'!$I$1</definedName>
   </definedNames>
@@ -73,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="236">
   <si>
     <t>World</t>
   </si>
@@ -2274,13 +2275,37 @@
     <t>1940–2001</t>
   </si>
   <si>
-    <t>Chart source data (index, first observation = 100)</t>
-  </si>
-  <si>
     <t>2001–22</t>
   </si>
   <si>
     <t>Price drops expressed as compounded quarterly rates, after inflation adjustment.</t>
+  </si>
+  <si>
+    <t>Electricity t</t>
+  </si>
+  <si>
+    <t>Electricity index</t>
+  </si>
+  <si>
+    <t>Battery t</t>
+  </si>
+  <si>
+    <t>Battery index</t>
+  </si>
+  <si>
+    <t>Compute t</t>
+  </si>
+  <si>
+    <t>Compute index</t>
+  </si>
+  <si>
+    <t>DNA sequencing t</t>
+  </si>
+  <si>
+    <t>DNA sequencing index</t>
+  </si>
+  <si>
+    <t>LLM t</t>
   </si>
 </sst>
 </file>
@@ -2495,7 +2520,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2652,11 +2677,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2863,7 +2887,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Table!$AD$5:$AD$6</c:f>
+              <c:f>'Figure data'!$I$3:$I$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2878,7 +2902,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Table!$AE$5:$AE$6</c:f>
+              <c:f>'Figure data'!$J$3:$J$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2918,7 +2942,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Table!$Z$4:$Z$58</c:f>
+              <c:f>'Figure data'!$E$2:$E$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="55"/>
@@ -3092,7 +3116,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Table!$AA$4:$AA$58</c:f>
+              <c:f>'Figure data'!$F$2:$F$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="55"/>
@@ -3291,7 +3315,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Table!$X$4:$X$37</c:f>
+              <c:f>'Figure data'!$C$2:$C$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="34"/>
@@ -3402,7 +3426,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Table!$Y$4:$Y$37</c:f>
+              <c:f>'Figure data'!$D$2:$D$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="34"/>
@@ -3538,7 +3562,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Table!$AB$4:$AB$81</c:f>
+              <c:f>'Figure data'!$G$2:$G$79</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="78"/>
@@ -3781,7 +3805,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Table!$AC$4:$AC$81</c:f>
+              <c:f>'Figure data'!$H$2:$H$79</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="78"/>
@@ -4049,7 +4073,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Table!$AD$4:$AD$5</c:f>
+              <c:f>'Figure data'!$I$2:$I$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4064,7 +4088,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Table!$AE$4:$AE$5</c:f>
+              <c:f>'Figure data'!$J$2:$J$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4104,7 +4128,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Table!$V$4:$V$58</c:f>
+              <c:f>'Figure data'!$A$2:$A$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="55"/>
@@ -4278,7 +4302,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Table!$W$4:$W$58</c:f>
+              <c:f>'Figure data'!$B$2:$B$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="55"/>
@@ -7781,7 +7805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937B7894-4F69-400D-85CE-13DD92AA35D6}">
-  <dimension ref="A1:AE81"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16.41796875" customWidth="1"/>
@@ -7796,7 +7820,7 @@
     <col min="22" max="31" width="10.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:22" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="49" t="s">
         <v>10</v>
       </c>
@@ -7818,11 +7842,9 @@
       </c>
       <c r="H1" s="58"/>
       <c r="I1" s="58"/>
-      <c r="V1" s="11" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="V1" s="11"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4" t="s">
         <v>197</v>
       </c>
@@ -7850,28 +7872,8 @@
         <f t="shared" ref="I2:I6" si="1">(1-D2)^-4</f>
         <v>1.0481922705785034</v>
       </c>
-      <c r="V2" s="65" t="s">
-        <v>197</v>
-      </c>
-      <c r="W2" s="65"/>
-      <c r="X2" s="65" t="s">
-        <v>195</v>
-      </c>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="AA2" s="65"/>
-      <c r="AB2" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC2" s="65"/>
-      <c r="AD2" s="65" t="s">
-        <v>200</v>
-      </c>
-      <c r="AE2" s="65"/>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>195</v>
       </c>
@@ -7902,38 +7904,8 @@
         <f t="shared" si="1"/>
         <v>1.155561883967176</v>
       </c>
-      <c r="V3" s="64" t="s">
-        <v>216</v>
-      </c>
-      <c r="W3" s="64" t="s">
-        <v>203</v>
-      </c>
-      <c r="X3" s="64" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y3" s="64" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z3" s="64" t="s">
-        <v>216</v>
-      </c>
-      <c r="AA3" s="64" t="s">
-        <v>203</v>
-      </c>
-      <c r="AB3" s="64" t="s">
-        <v>216</v>
-      </c>
-      <c r="AC3" s="64" t="s">
-        <v>203</v>
-      </c>
-      <c r="AD3" s="64" t="s">
-        <v>216</v>
-      </c>
-      <c r="AE3" s="64" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4" t="s">
         <v>192</v>
       </c>
@@ -7965,48 +7937,8 @@
         <v>1.0378413449321391</v>
       </c>
       <c r="J4" s="4"/>
-      <c r="V4">
-        <f>Electricity!K4</f>
-        <v>0</v>
-      </c>
-      <c r="W4" s="66">
-        <f>Electricity!L4</f>
-        <v>100</v>
-      </c>
-      <c r="X4">
-        <f>'Lithium batteries'!D4</f>
-        <v>0</v>
-      </c>
-      <c r="Y4" s="66">
-        <f>'Lithium batteries'!F4</f>
-        <v>100</v>
-      </c>
-      <c r="Z4">
-        <f>Compute!M22</f>
-        <v>0</v>
-      </c>
-      <c r="AA4" s="66">
-        <f>Compute!Q22</f>
-        <v>100</v>
-      </c>
-      <c r="AB4">
-        <f>'DNA sequencing'!C6</f>
-        <v>0</v>
-      </c>
-      <c r="AC4" s="66">
-        <f>'DNA sequencing'!J6</f>
-        <v>100</v>
-      </c>
-      <c r="AD4">
-        <f>$B11</f>
-        <v>0</v>
-      </c>
-      <c r="AE4" s="66">
-        <f>$C11</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>202</v>
       </c>
@@ -8034,53 +7966,13 @@
         <f t="shared" si="1"/>
         <v>1.5140589684406742</v>
       </c>
-      <c r="V5">
-        <f>Electricity!K5</f>
-        <v>5</v>
-      </c>
-      <c r="W5" s="66">
-        <f>Electricity!L5</f>
-        <v>98.103137396321642</v>
-      </c>
-      <c r="X5">
-        <f>'Lithium batteries'!D5</f>
-        <v>1</v>
-      </c>
-      <c r="Y5" s="66">
-        <f>'Lithium batteries'!F5</f>
-        <v>80.216650398524251</v>
-      </c>
-      <c r="Z5">
-        <f>Compute!M23</f>
-        <v>1</v>
-      </c>
-      <c r="AA5" s="66">
-        <f>Compute!Q23</f>
-        <v>100</v>
-      </c>
-      <c r="AB5">
-        <f>'DNA sequencing'!C7</f>
-        <v>0.49828884325802392</v>
-      </c>
-      <c r="AC5" s="66">
-        <f>'DNA sequencing'!J7</f>
-        <v>72.966450166975193</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" ref="AD5:AD6" si="3">$B12</f>
-        <v>1.6163586584530094</v>
-      </c>
-      <c r="AE5" s="66">
-        <f t="shared" ref="AE5:AE6" si="4">$C12</f>
-        <v>1.6493911422653169</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>198</v>
@@ -8106,48 +7998,8 @@
         <f t="shared" si="1"/>
         <v>1.8414054111435121</v>
       </c>
-      <c r="V6">
-        <f>Electricity!K6</f>
-        <v>10</v>
-      </c>
-      <c r="W6" s="66">
-        <f>Electricity!L6</f>
-        <v>77.924442228328303</v>
-      </c>
-      <c r="X6">
-        <f>'Lithium batteries'!D6</f>
-        <v>2</v>
-      </c>
-      <c r="Y6" s="66">
-        <f>'Lithium batteries'!F6</f>
-        <v>63.861393255108737</v>
-      </c>
-      <c r="Z6">
-        <f>Compute!M24</f>
-        <v>2</v>
-      </c>
-      <c r="AA6" s="66">
-        <f>Compute!Q24</f>
-        <v>35.11547603886779</v>
-      </c>
-      <c r="AB6">
-        <f>'DNA sequencing'!C8</f>
-        <v>0.99931553730334599</v>
-      </c>
-      <c r="AC6" s="66">
-        <f>'DNA sequencing'!J8</f>
-        <v>63.222391132945198</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="3"/>
-        <v>4.7829586584530261</v>
-      </c>
-      <c r="AE6" s="66">
-        <f t="shared" si="4"/>
-        <v>5.3075186958275811E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="48" t="s">
         <v>200</v>
       </c>
@@ -8177,42 +8029,10 @@
         <f>(1-D7)^-4</f>
         <v>12.673498611808327</v>
       </c>
-      <c r="V7">
-        <f>Electricity!K7</f>
-        <v>15</v>
-      </c>
-      <c r="W7" s="66">
-        <f>Electricity!L7</f>
-        <v>46.036688553442083</v>
-      </c>
-      <c r="X7">
-        <f>'Lithium batteries'!D7</f>
-        <v>3</v>
-      </c>
-      <c r="Y7" s="66">
-        <f>'Lithium batteries'!F7</f>
-        <v>72.902084964219142</v>
-      </c>
-      <c r="Z7">
-        <f>Compute!M25</f>
-        <v>3</v>
-      </c>
-      <c r="AA7" s="66">
-        <f>Compute!Q25</f>
-        <v>7.8033172753900661</v>
-      </c>
-      <c r="AB7">
-        <f>'DNA sequencing'!C9</f>
-        <v>1.4976043805613699</v>
-      </c>
-      <c r="AC7" s="66">
-        <f>'DNA sequencing'!J9</f>
-        <v>54.699705192006995</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="62" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B8" s="62"/>
       <c r="C8" s="62"/>
@@ -8222,74 +8042,8 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
-      <c r="V8">
-        <f>Electricity!K8</f>
-        <v>20</v>
-      </c>
-      <c r="W8" s="66">
-        <f>Electricity!L8</f>
-        <v>38.533537553467681</v>
-      </c>
-      <c r="X8">
-        <f>'Lithium batteries'!D8</f>
-        <v>4</v>
-      </c>
-      <c r="Y8" s="66">
-        <f>'Lithium batteries'!F8</f>
-        <v>68.422648511492127</v>
-      </c>
-      <c r="Z8">
-        <f>Compute!M26</f>
-        <v>4</v>
-      </c>
-      <c r="AA8" s="66">
-        <f>Compute!Q26</f>
-        <v>7.8033172753900661</v>
-      </c>
-      <c r="AB8">
-        <f>'DNA sequencing'!C10</f>
-        <v>2.0835044490077053</v>
-      </c>
-      <c r="AC8" s="66">
-        <f>'DNA sequencing'!J10</f>
-        <v>40.468201668292465</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.55000000000000004">
-      <c r="V9">
-        <f>Electricity!K9</f>
-        <v>25</v>
-      </c>
-      <c r="W9" s="66">
-        <f>Electricity!L9</f>
-        <v>24.21568181818181</v>
-      </c>
-      <c r="X9">
-        <f>'Lithium batteries'!D9</f>
-        <v>5</v>
-      </c>
-      <c r="Y9" s="66">
-        <f>'Lithium batteries'!F9</f>
-        <v>57.629766031901482</v>
-      </c>
-      <c r="Z9">
-        <f>Compute!M27</f>
-        <v>5</v>
-      </c>
-      <c r="AA9" s="66">
-        <f>Compute!Q27</f>
-        <v>7.8033172753900661</v>
-      </c>
-      <c r="AB9">
-        <f>'DNA sequencing'!C11</f>
-        <v>2.3353867214236743</v>
-      </c>
-      <c r="AC9" s="66">
-        <f>'DNA sequencing'!J11</f>
-        <v>28.73892560087431</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -8299,40 +8053,8 @@
       <c r="C10" t="s">
         <v>200</v>
       </c>
-      <c r="V10">
-        <f>Electricity!K10</f>
-        <v>30</v>
-      </c>
-      <c r="W10" s="66">
-        <f>Electricity!L10</f>
-        <v>18.106558441558441</v>
-      </c>
-      <c r="X10">
-        <f>'Lithium batteries'!D10</f>
-        <v>6</v>
-      </c>
-      <c r="Y10" s="66">
-        <f>'Lithium batteries'!F10</f>
-        <v>49.3504776753675</v>
-      </c>
-      <c r="Z10">
-        <f>Compute!M28</f>
-        <v>6</v>
-      </c>
-      <c r="AA10" s="66">
-        <f>Compute!Q28</f>
-        <v>4.6382056926548554</v>
-      </c>
-      <c r="AB10">
-        <f>'DNA sequencing'!C12</f>
-        <v>2.5817932922657292</v>
-      </c>
-      <c r="AC10" s="66">
-        <f>'DNA sequencing'!J12</f>
-        <v>20.250436288913715</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="6">
         <f>DATEVALUE("2021-11-18")/365.25+1900</f>
         <v>2021.883641341547</v>
@@ -8344,40 +8066,8 @@
       <c r="C11" s="55">
         <v>100</v>
       </c>
-      <c r="V11">
-        <f>Electricity!K11</f>
-        <v>34</v>
-      </c>
-      <c r="W11" s="66">
-        <f>Electricity!L11</f>
-        <v>16.300975860297893</v>
-      </c>
-      <c r="X11">
-        <f>'Lithium batteries'!D11</f>
-        <v>7</v>
-      </c>
-      <c r="Y11" s="66">
-        <f>'Lithium batteries'!F11</f>
-        <v>39.704364603272666</v>
-      </c>
-      <c r="Z11">
-        <f>Compute!M29</f>
-        <v>7</v>
-      </c>
-      <c r="AA11" s="66">
-        <f>Compute!Q29</f>
-        <v>4.6382056926548554</v>
-      </c>
-      <c r="AB11">
-        <f>'DNA sequencing'!C13</f>
-        <v>2.8336755646816982</v>
-      </c>
-      <c r="AC11" s="66">
-        <f>'DNA sequencing'!J13</f>
-        <v>19.64261179806801</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="6">
         <v>2023.5</v>
       </c>
@@ -8389,40 +8079,8 @@
         <f>$C$11*(1-$D$7)^(4*(A12-$A$11))</f>
         <v>1.6493911422653169</v>
       </c>
-      <c r="V12">
-        <f>Electricity!K12</f>
-        <v>35</v>
-      </c>
-      <c r="W12" s="66">
-        <f>Electricity!L12</f>
-        <v>16.155632183908043</v>
-      </c>
-      <c r="X12">
-        <f>'Lithium batteries'!D12</f>
-        <v>8</v>
-      </c>
-      <c r="Y12" s="66">
-        <f>'Lithium batteries'!F12</f>
-        <v>30.073870033647371</v>
-      </c>
-      <c r="Z12">
-        <f>Compute!M30</f>
-        <v>8</v>
-      </c>
-      <c r="AA12" s="66">
-        <f>Compute!Q30</f>
-        <v>4.6382056926548554</v>
-      </c>
-      <c r="AB12">
-        <f>'DNA sequencing'!C14</f>
-        <v>3.0855578370978947</v>
-      </c>
-      <c r="AC12" s="66">
-        <f>'DNA sequencing'!J14</f>
-        <v>18.010307127461044</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="6">
         <v>2026.6666</v>
       </c>
@@ -8433,1630 +8091,6 @@
       <c r="C13" s="5">
         <f>$C$11*(1-$D$7)^(4*(A13-$A$11))</f>
         <v>5.3075186958275811E-4</v>
-      </c>
-      <c r="V13">
-        <f>Electricity!K13</f>
-        <v>36</v>
-      </c>
-      <c r="W13" s="66">
-        <f>Electricity!L13</f>
-        <v>15.98108452950558</v>
-      </c>
-      <c r="X13">
-        <f>'Lithium batteries'!D13</f>
-        <v>9</v>
-      </c>
-      <c r="Y13" s="66">
-        <f>'Lithium batteries'!F13</f>
-        <v>29.213463724575828</v>
-      </c>
-      <c r="Z13">
-        <f>Compute!M31</f>
-        <v>9</v>
-      </c>
-      <c r="AA13" s="66">
-        <f>Compute!Q31</f>
-        <v>0.57840715825846489</v>
-      </c>
-      <c r="AB13">
-        <f>'DNA sequencing'!C15</f>
-        <v>3.3374401095140911</v>
-      </c>
-      <c r="AC13" s="66">
-        <f>'DNA sequencing'!J15</f>
-        <v>16.990976065198431</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.55000000000000004">
-      <c r="V14">
-        <f>Electricity!K14</f>
-        <v>37</v>
-      </c>
-      <c r="W14" s="66">
-        <f>Electricity!L14</f>
-        <v>15.257958532695373</v>
-      </c>
-      <c r="X14">
-        <f>'Lithium batteries'!D14</f>
-        <v>10</v>
-      </c>
-      <c r="Y14" s="66">
-        <f>'Lithium batteries'!F14</f>
-        <v>20.390688397575303</v>
-      </c>
-      <c r="Z14">
-        <f>Compute!M32</f>
-        <v>10</v>
-      </c>
-      <c r="AA14" s="66">
-        <f>Compute!Q32</f>
-        <v>0.57840715825846489</v>
-      </c>
-      <c r="AB14">
-        <f>'DNA sequencing'!C16</f>
-        <v>3.5811088295688478</v>
-      </c>
-      <c r="AC14" s="66">
-        <f>'DNA sequencing'!J16</f>
-        <v>15.56131540651009</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.55000000000000004">
-      <c r="V15">
-        <f>Electricity!K15</f>
-        <v>38</v>
-      </c>
-      <c r="W15" s="66">
-        <f>Electricity!L15</f>
-        <v>14.882972237343495</v>
-      </c>
-      <c r="X15">
-        <f>'Lithium batteries'!D15</f>
-        <v>11</v>
-      </c>
-      <c r="Y15" s="66">
-        <f>'Lithium batteries'!F15</f>
-        <v>14.609075994844863</v>
-      </c>
-      <c r="Z15">
-        <f>Compute!M33</f>
-        <v>11</v>
-      </c>
-      <c r="AA15" s="66">
-        <f>Compute!Q33</f>
-        <v>0.57840715825846489</v>
-      </c>
-      <c r="AB15">
-        <f>'DNA sequencing'!C17</f>
-        <v>3.8329911019850442</v>
-      </c>
-      <c r="AC15" s="66">
-        <f>'DNA sequencing'!J17</f>
-        <v>15.382443136010684</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.55000000000000004">
-      <c r="V16">
-        <f>Electricity!K16</f>
-        <v>39</v>
-      </c>
-      <c r="W16" s="66">
-        <f>Electricity!L16</f>
-        <v>15.673755980861243</v>
-      </c>
-      <c r="X16">
-        <f>'Lithium batteries'!D16</f>
-        <v>12</v>
-      </c>
-      <c r="Y16" s="66">
-        <f>'Lithium batteries'!F16</f>
-        <v>11.295786315868334</v>
-      </c>
-      <c r="Z16">
-        <f>Compute!M34</f>
-        <v>12</v>
-      </c>
-      <c r="AA16" s="66">
-        <f>Compute!Q34</f>
-        <v>0.57840715825846489</v>
-      </c>
-      <c r="AB16">
-        <f>'DNA sequencing'!C18</f>
-        <v>4.0848733744012407</v>
-      </c>
-      <c r="AC16" s="66">
-        <f>'DNA sequencing'!J18</f>
-        <v>12.988182068984196</v>
-      </c>
-    </row>
-    <row r="17" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V17">
-        <f>Electricity!K17</f>
-        <v>40</v>
-      </c>
-      <c r="W17" s="66">
-        <f>Electricity!L17</f>
-        <v>16.878394160583941</v>
-      </c>
-      <c r="X17">
-        <f>'Lithium batteries'!D17</f>
-        <v>13</v>
-      </c>
-      <c r="Y17" s="66">
-        <f>'Lithium batteries'!F17</f>
-        <v>10.107282119990488</v>
-      </c>
-      <c r="Z17">
-        <f>Compute!M35</f>
-        <v>13</v>
-      </c>
-      <c r="AA17" s="66">
-        <f>Compute!Q35</f>
-        <v>0.11894462989462484</v>
-      </c>
-      <c r="AB17">
-        <f>'DNA sequencing'!C19</f>
-        <v>4.3367556468174371</v>
-      </c>
-      <c r="AC17" s="66">
-        <f>'DNA sequencing'!J19</f>
-        <v>11.76709291497095</v>
-      </c>
-    </row>
-    <row r="18" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V18">
-        <f>Electricity!K18</f>
-        <v>41</v>
-      </c>
-      <c r="W18" s="66">
-        <f>Electricity!L18</f>
-        <v>17.501874125874121</v>
-      </c>
-      <c r="X18">
-        <f>'Lithium batteries'!D18</f>
-        <v>14</v>
-      </c>
-      <c r="Y18" s="66">
-        <f>'Lithium batteries'!F18</f>
-        <v>8.7135380983971089</v>
-      </c>
-      <c r="Z18">
-        <f>Compute!M36</f>
-        <v>14</v>
-      </c>
-      <c r="AA18" s="66">
-        <f>Compute!Q36</f>
-        <v>0.11894462989462484</v>
-      </c>
-      <c r="AB18">
-        <f>'DNA sequencing'!C20</f>
-        <v>4.5804243668721938</v>
-      </c>
-      <c r="AC18" s="66">
-        <f>'DNA sequencing'!J20</f>
-        <v>10.865918549877641</v>
-      </c>
-    </row>
-    <row r="19" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V19">
-        <f>Electricity!K19</f>
-        <v>42</v>
-      </c>
-      <c r="W19" s="66">
-        <f>Electricity!L19</f>
-        <v>16.394993215739483</v>
-      </c>
-      <c r="X19">
-        <f>'Lithium batteries'!D19</f>
-        <v>15</v>
-      </c>
-      <c r="Y19" s="66">
-        <f>'Lithium batteries'!F19</f>
-        <v>7.4623091931471857</v>
-      </c>
-      <c r="Z19">
-        <f>Compute!M37</f>
-        <v>15</v>
-      </c>
-      <c r="AA19" s="66">
-        <f>Compute!Q37</f>
-        <v>3.9869035438097035E-2</v>
-      </c>
-      <c r="AB19">
-        <f>'DNA sequencing'!C21</f>
-        <v>4.8323066392881628</v>
-      </c>
-      <c r="AC19" s="66">
-        <f>'DNA sequencing'!J21</f>
-        <v>10.479033872157595</v>
-      </c>
-    </row>
-    <row r="20" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V20">
-        <f>Electricity!K20</f>
-        <v>43</v>
-      </c>
-      <c r="W20" s="66">
-        <f>Electricity!L20</f>
-        <v>15.073218314532181</v>
-      </c>
-      <c r="X20">
-        <f>'Lithium batteries'!D20</f>
-        <v>16</v>
-      </c>
-      <c r="Y20" s="66">
-        <f>'Lithium batteries'!F20</f>
-        <v>7.1207342270497049</v>
-      </c>
-      <c r="Z20">
-        <f>Compute!M38</f>
-        <v>18</v>
-      </c>
-      <c r="AA20" s="66">
-        <f>Compute!Q38</f>
-        <v>3.9869035438097035E-2</v>
-      </c>
-      <c r="AB20">
-        <f>'DNA sequencing'!C22</f>
-        <v>5.0841889117043593</v>
-      </c>
-      <c r="AC20" s="66">
-        <f>'DNA sequencing'!J22</f>
-        <v>9.6672432806743718</v>
-      </c>
-    </row>
-    <row r="21" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V21">
-        <f>Electricity!K21</f>
-        <v>44</v>
-      </c>
-      <c r="W21" s="66">
-        <f>Electricity!L21</f>
-        <v>13.848122956180505</v>
-      </c>
-      <c r="X21">
-        <f>'Lithium batteries'!D21</f>
-        <v>17</v>
-      </c>
-      <c r="Y21" s="66">
-        <f>'Lithium batteries'!F21</f>
-        <v>7.4662293992658171</v>
-      </c>
-      <c r="Z21">
-        <f>Compute!M39</f>
-        <v>19</v>
-      </c>
-      <c r="AA21" s="66">
-        <f>Compute!Q39</f>
-        <v>3.9869035438097035E-2</v>
-      </c>
-      <c r="AB21">
-        <f>'DNA sequencing'!C23</f>
-        <v>5.3360711841205557</v>
-      </c>
-      <c r="AC21" s="66">
-        <f>'DNA sequencing'!J23</f>
-        <v>8.5889241079984053</v>
-      </c>
-    </row>
-    <row r="22" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V22">
-        <f>Electricity!K22</f>
-        <v>45</v>
-      </c>
-      <c r="W22" s="66">
-        <f>Electricity!L22</f>
-        <v>12.279583333333331</v>
-      </c>
-      <c r="X22">
-        <f>'Lithium batteries'!D22</f>
-        <v>18</v>
-      </c>
-      <c r="Y22" s="66">
-        <f>'Lithium batteries'!F22</f>
-        <v>6.6510416135101948</v>
-      </c>
-      <c r="Z22">
-        <f>Compute!M40</f>
-        <v>20</v>
-      </c>
-      <c r="AA22" s="66">
-        <f>Compute!Q40</f>
-        <v>1.4230696120937077E-2</v>
-      </c>
-      <c r="AB22">
-        <f>'DNA sequencing'!C24</f>
-        <v>5.5797399041753124</v>
-      </c>
-      <c r="AC22" s="66">
-        <f>'DNA sequencing'!J24</f>
-        <v>8.1576880020311346</v>
-      </c>
-    </row>
-    <row r="23" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V23">
-        <f>Electricity!K23</f>
-        <v>46</v>
-      </c>
-      <c r="W23" s="66">
-        <f>Electricity!L23</f>
-        <v>12.102359767891679</v>
-      </c>
-      <c r="X23">
-        <f>'Lithium batteries'!D23</f>
-        <v>19</v>
-      </c>
-      <c r="Y23" s="66">
-        <f>'Lithium batteries'!F23</f>
-        <v>5.9794450301458273</v>
-      </c>
-      <c r="Z23">
-        <f>Compute!M41</f>
-        <v>21</v>
-      </c>
-      <c r="AA23" s="66">
-        <f>Compute!Q41</f>
-        <v>1.3078890527653684E-2</v>
-      </c>
-      <c r="AB23">
-        <f>'DNA sequencing'!C25</f>
-        <v>5.8316221765915088</v>
-      </c>
-      <c r="AC23" s="66">
-        <f>'DNA sequencing'!J25</f>
-        <v>8.0144379342313012</v>
-      </c>
-    </row>
-    <row r="24" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V24">
-        <f>Electricity!K24</f>
-        <v>47</v>
-      </c>
-      <c r="W24" s="66">
-        <f>Electricity!L24</f>
-        <v>11.861347285807716</v>
-      </c>
-      <c r="X24">
-        <f>'Lithium batteries'!D24</f>
-        <v>20</v>
-      </c>
-      <c r="Y24" s="66">
-        <f>'Lithium batteries'!F24</f>
-        <v>5.6958182368952777</v>
-      </c>
-      <c r="Z24">
-        <f>Compute!M42</f>
-        <v>22</v>
-      </c>
-      <c r="AA24" s="66">
-        <f>Compute!Q42</f>
-        <v>1.3078890527653684E-2</v>
-      </c>
-      <c r="AB24">
-        <f>'DNA sequencing'!C26</f>
-        <v>6.0835044490077053</v>
-      </c>
-      <c r="AC24" s="66">
-        <f>'DNA sequencing'!J26</f>
-        <v>6.3202787487277767</v>
-      </c>
-    </row>
-    <row r="25" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V25">
-        <f>Electricity!K25</f>
-        <v>48</v>
-      </c>
-      <c r="W25" s="66">
-        <f>Electricity!L25</f>
-        <v>11.305558441558441</v>
-      </c>
-      <c r="X25">
-        <f>'Lithium batteries'!D25</f>
-        <v>21</v>
-      </c>
-      <c r="Y25" s="66">
-        <f>'Lithium batteries'!F25</f>
-        <v>5.8597070865765568</v>
-      </c>
-      <c r="Z25">
-        <f>Compute!M43</f>
-        <v>23</v>
-      </c>
-      <c r="AA25" s="66">
-        <f>Compute!Q43</f>
-        <v>1.3078890527653684E-2</v>
-      </c>
-      <c r="AB25">
-        <f>'DNA sequencing'!C27</f>
-        <v>6.3353867214236743</v>
-      </c>
-      <c r="AC25" s="66">
-        <f>'DNA sequencing'!J27</f>
-        <v>2.6855959871058328</v>
-      </c>
-    </row>
-    <row r="26" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V26">
-        <f>Electricity!K26</f>
-        <v>49</v>
-      </c>
-      <c r="W26" s="66">
-        <f>Electricity!L26</f>
-        <v>10.458763141620283</v>
-      </c>
-      <c r="X26">
-        <f>'Lithium batteries'!D26</f>
-        <v>22</v>
-      </c>
-      <c r="Y26" s="66">
-        <f>'Lithium batteries'!F26</f>
-        <v>5.3298723267497126</v>
-      </c>
-      <c r="Z26">
-        <f>Compute!M44</f>
-        <v>24</v>
-      </c>
-      <c r="AA26" s="66">
-        <f>Compute!Q44</f>
-        <v>4.4641876916147174E-3</v>
-      </c>
-      <c r="AB26">
-        <f>'DNA sequencing'!C28</f>
-        <v>6.5817932922657292</v>
-      </c>
-      <c r="AC26" s="66">
-        <f>'DNA sequencing'!J28</f>
-        <v>1.1720659796107069</v>
-      </c>
-    </row>
-    <row r="27" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V27">
-        <f>Electricity!K27</f>
-        <v>50</v>
-      </c>
-      <c r="W27" s="66">
-        <f>Electricity!L27</f>
-        <v>9.3056999442275501</v>
-      </c>
-      <c r="X27">
-        <f>'Lithium batteries'!D27</f>
-        <v>23</v>
-      </c>
-      <c r="Y27" s="66">
-        <f>'Lithium batteries'!F27</f>
-        <v>4.715082033782001</v>
-      </c>
-      <c r="Z27">
-        <f>Compute!M45</f>
-        <v>25</v>
-      </c>
-      <c r="AA27" s="66">
-        <f>Compute!Q45</f>
-        <v>4.4641876916147174E-3</v>
-      </c>
-      <c r="AB27">
-        <f>'DNA sequencing'!C29</f>
-        <v>6.8336755646816982</v>
-      </c>
-      <c r="AC27" s="66">
-        <f>'DNA sequencing'!J29</f>
-        <v>0.64114083441616443</v>
-      </c>
-    </row>
-    <row r="28" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V28">
-        <f>Electricity!K28</f>
-        <v>51</v>
-      </c>
-      <c r="W28" s="66">
-        <f>Electricity!L28</f>
-        <v>8.5771939043615344</v>
-      </c>
-      <c r="X28">
-        <f>'Lithium batteries'!D28</f>
-        <v>24</v>
-      </c>
-      <c r="Y28" s="66">
-        <f>'Lithium batteries'!F28</f>
-        <v>3.6040658050884722</v>
-      </c>
-      <c r="Z28">
-        <f>Compute!M46</f>
-        <v>26</v>
-      </c>
-      <c r="AA28" s="66">
-        <f>Compute!Q46</f>
-        <v>4.4641876916147174E-3</v>
-      </c>
-      <c r="AB28">
-        <f>'DNA sequencing'!C30</f>
-        <v>7.0855578370978947</v>
-      </c>
-      <c r="AC28" s="66">
-        <f>'DNA sequencing'!J30</f>
-        <v>0.29956434297798684</v>
-      </c>
-    </row>
-    <row r="29" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V29">
-        <f>Electricity!K29</f>
-        <v>52</v>
-      </c>
-      <c r="W29" s="66">
-        <f>Electricity!L29</f>
-        <v>8.2202169421487579</v>
-      </c>
-      <c r="X29">
-        <f>'Lithium batteries'!D29</f>
-        <v>25</v>
-      </c>
-      <c r="Y29" s="66">
-        <f>'Lithium batteries'!F29</f>
-        <v>2.8120904689676589</v>
-      </c>
-      <c r="Z29">
-        <f>Compute!M47</f>
-        <v>27</v>
-      </c>
-      <c r="AA29" s="66">
-        <f>Compute!Q47</f>
-        <v>4.4641876916147174E-3</v>
-      </c>
-      <c r="AB29">
-        <f>'DNA sequencing'!C31</f>
-        <v>7.3374401095140911</v>
-      </c>
-      <c r="AC29" s="66">
-        <f>'DNA sequencing'!J31</f>
-        <v>0.20398733178367293</v>
-      </c>
-    </row>
-    <row r="30" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V30">
-        <f>Electricity!K30</f>
-        <v>53</v>
-      </c>
-      <c r="W30" s="66">
-        <f>Electricity!L30</f>
-        <v>7.8085555555555537</v>
-      </c>
-      <c r="X30">
-        <f>'Lithium batteries'!D30</f>
-        <v>26</v>
-      </c>
-      <c r="Y30" s="66">
-        <f>'Lithium batteries'!F30</f>
-        <v>2.0303510335789658</v>
-      </c>
-      <c r="Z30">
-        <f>Compute!M48</f>
-        <v>29</v>
-      </c>
-      <c r="AA30" s="66">
-        <f>Compute!Q48</f>
-        <v>2.3236862295869746E-3</v>
-      </c>
-      <c r="AB30">
-        <f>'DNA sequencing'!C32</f>
-        <v>7.5811088295688478</v>
-      </c>
-      <c r="AC30" s="66">
-        <f>'DNA sequencing'!J32</f>
-        <v>0.13540116803166066</v>
-      </c>
-    </row>
-    <row r="31" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V31">
-        <f>Electricity!K31</f>
-        <v>54</v>
-      </c>
-      <c r="W31" s="66">
-        <f>Electricity!L31</f>
-        <v>6.8062843822843817</v>
-      </c>
-      <c r="X31">
-        <f>'Lithium batteries'!D31</f>
-        <v>27</v>
-      </c>
-      <c r="Y31" s="66">
-        <f>'Lithium batteries'!F31</f>
-        <v>1.7046262688336773</v>
-      </c>
-      <c r="Z31">
-        <f>Compute!M49</f>
-        <v>30</v>
-      </c>
-      <c r="AA31" s="66">
-        <f>Compute!Q49</f>
-        <v>2.3236862295869746E-3</v>
-      </c>
-      <c r="AB31">
-        <f>'DNA sequencing'!C33</f>
-        <v>7.8329911019850442</v>
-      </c>
-      <c r="AC31" s="66">
-        <f>'DNA sequencing'!J33</f>
-        <v>9.351205005827852E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V32">
-        <f>Electricity!K32</f>
-        <v>55</v>
-      </c>
-      <c r="W32" s="66">
-        <f>Electricity!L32</f>
-        <v>5.7113982878108427</v>
-      </c>
-      <c r="X32">
-        <f>'Lithium batteries'!D32</f>
-        <v>28</v>
-      </c>
-      <c r="Y32" s="66">
-        <f>'Lithium batteries'!F32</f>
-        <v>1.4331889648792702</v>
-      </c>
-      <c r="Z32">
-        <f>Compute!M50</f>
-        <v>31</v>
-      </c>
-      <c r="AA32" s="66">
-        <f>Compute!Q50</f>
-        <v>2.3236862295869746E-3</v>
-      </c>
-      <c r="AB32">
-        <f>'DNA sequencing'!C34</f>
-        <v>8.0848733744012407</v>
-      </c>
-      <c r="AC32" s="66">
-        <f>'DNA sequencing'!J34</f>
-        <v>6.0360355326899352E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V33">
-        <f>Electricity!K33</f>
-        <v>56</v>
-      </c>
-      <c r="W33" s="66">
-        <f>Electricity!L33</f>
-        <v>5.1479969822708398</v>
-      </c>
-      <c r="X33">
-        <f>'Lithium batteries'!D33</f>
-        <v>29</v>
-      </c>
-      <c r="Y33" s="66">
-        <f>'Lithium batteries'!F33</f>
-        <v>1.3354715354556836</v>
-      </c>
-      <c r="Z33">
-        <f>Compute!M51</f>
-        <v>32</v>
-      </c>
-      <c r="AA33" s="66">
-        <f>Compute!Q51</f>
-        <v>2.3236862295869746E-3</v>
-      </c>
-      <c r="AB33">
-        <f>'DNA sequencing'!C35</f>
-        <v>8.3367556468174371</v>
-      </c>
-      <c r="AC33" s="66">
-        <f>'DNA sequencing'!J35</f>
-        <v>4.0133189210794687E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V34">
-        <f>Electricity!K34</f>
-        <v>57</v>
-      </c>
-      <c r="W34" s="66">
-        <f>Electricity!L34</f>
-        <v>5.1089763177998471</v>
-      </c>
-      <c r="X34">
-        <f>'Lithium batteries'!D34</f>
-        <v>30</v>
-      </c>
-      <c r="Y34" s="66">
-        <f>'Lithium batteries'!F34</f>
-        <v>1.2920415668229785</v>
-      </c>
-      <c r="Z34">
-        <f>Compute!M52</f>
-        <v>33</v>
-      </c>
-      <c r="AA34" s="66">
-        <f>Compute!Q52</f>
-        <v>2.3236862295869746E-3</v>
-      </c>
-      <c r="AB34">
-        <f>'DNA sequencing'!C36</f>
-        <v>8.5804243668721938</v>
-      </c>
-      <c r="AC34" s="66">
-        <f>'DNA sequencing'!J36</f>
-        <v>2.7036791526076815E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V35">
-        <f>Electricity!K35</f>
-        <v>58</v>
-      </c>
-      <c r="W35" s="66">
-        <f>Electricity!L35</f>
-        <v>4.925658242172763</v>
-      </c>
-      <c r="X35">
-        <f>'Lithium batteries'!D35</f>
-        <v>31</v>
-      </c>
-      <c r="Y35" s="66">
-        <f>'Lithium batteries'!F35</f>
-        <v>1.4331889648792702</v>
-      </c>
-      <c r="Z35">
-        <f>Compute!M53</f>
-        <v>35</v>
-      </c>
-      <c r="AA35" s="66">
-        <f>Compute!Q53</f>
-        <v>2.3236862295869746E-3</v>
-      </c>
-      <c r="AB35">
-        <f>'DNA sequencing'!C37</f>
-        <v>8.8323066392881628</v>
-      </c>
-      <c r="AC35" s="66">
-        <f>'DNA sequencing'!J37</f>
-        <v>2.662711554270181E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V36">
-        <f>Electricity!K36</f>
-        <v>59</v>
-      </c>
-      <c r="W36" s="66">
-        <f>Electricity!L36</f>
-        <v>4.454734265734265</v>
-      </c>
-      <c r="X36">
-        <f>'Lithium batteries'!D36</f>
-        <v>32</v>
-      </c>
-      <c r="Y36" s="66">
-        <f>'Lithium batteries'!F36</f>
-        <v>1.2051816295575681</v>
-      </c>
-      <c r="Z36">
-        <f>Compute!M54</f>
-        <v>36</v>
-      </c>
-      <c r="AA36" s="66">
-        <f>Compute!Q54</f>
-        <v>3.161819275679901E-4</v>
-      </c>
-      <c r="AB36">
-        <f>'DNA sequencing'!C38</f>
-        <v>9.0841889117043593</v>
-      </c>
-      <c r="AC36" s="66">
-        <f>'DNA sequencing'!J38</f>
-        <v>2.4698775629687982E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V37">
-        <f>Electricity!K37</f>
-        <v>60</v>
-      </c>
-      <c r="W37" s="66">
-        <f>Electricity!L37</f>
-        <v>4.3084665523156085</v>
-      </c>
-      <c r="X37">
-        <f>'Lithium batteries'!D37</f>
-        <v>33</v>
-      </c>
-      <c r="Y37" s="66">
-        <f>'Lithium batteries'!F37</f>
-        <v>0.84688438833775048</v>
-      </c>
-      <c r="Z37">
-        <f>Compute!M55</f>
-        <v>37</v>
-      </c>
-      <c r="AA37" s="66">
-        <f>Compute!Q55</f>
-        <v>7.2772030948188199E-5</v>
-      </c>
-      <c r="AB37">
-        <f>'DNA sequencing'!C39</f>
-        <v>9.3360711841205557</v>
-      </c>
-      <c r="AC37" s="66">
-        <f>'DNA sequencing'!J39</f>
-        <v>1.7612212416533383E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V38">
-        <f>Electricity!K38</f>
-        <v>61</v>
-      </c>
-      <c r="W38" s="66">
-        <f>Electricity!L38</f>
-        <v>4.2298808307797069</v>
-      </c>
-      <c r="Z38">
-        <f>Compute!M56</f>
-        <v>38</v>
-      </c>
-      <c r="AA38" s="66">
-        <f>Compute!Q56</f>
-        <v>7.2772030948188199E-5</v>
-      </c>
-      <c r="AB38">
-        <f>'DNA sequencing'!C40</f>
-        <v>9.5797399041753124</v>
-      </c>
-      <c r="AC38" s="66">
-        <f>'DNA sequencing'!J40</f>
-        <v>1.3859234684711133E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V39">
-        <f>Electricity!K39</f>
-        <v>62</v>
-      </c>
-      <c r="W39" s="66">
-        <f>Electricity!L39</f>
-        <v>4.1218181818181812</v>
-      </c>
-      <c r="Z39">
-        <f>Compute!M57</f>
-        <v>40</v>
-      </c>
-      <c r="AA39" s="66">
-        <f>Compute!Q57</f>
-        <v>7.2772030948188199E-5</v>
-      </c>
-      <c r="AB39">
-        <f>'DNA sequencing'!C41</f>
-        <v>9.8316221765915088</v>
-      </c>
-      <c r="AC39" s="66">
-        <f>'DNA sequencing'!J41</f>
-        <v>8.6550335982576426E-3</v>
-      </c>
-    </row>
-    <row r="40" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V40">
-        <f>Electricity!K40</f>
-        <v>63</v>
-      </c>
-      <c r="W40" s="66">
-        <f>Electricity!L40</f>
-        <v>4.0602985074626865</v>
-      </c>
-      <c r="Z40">
-        <f>Compute!M58</f>
-        <v>42</v>
-      </c>
-      <c r="AA40" s="66">
-        <f>Compute!Q58</f>
-        <v>1.2546901887618654E-5</v>
-      </c>
-      <c r="AB40">
-        <f>'DNA sequencing'!C42</f>
-        <v>10.080766598220407</v>
-      </c>
-      <c r="AC40" s="66">
-        <f>'DNA sequencing'!J42</f>
-        <v>6.3548184017738268E-3</v>
-      </c>
-    </row>
-    <row r="41" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V41">
-        <f>Electricity!K41</f>
-        <v>64</v>
-      </c>
-      <c r="W41" s="66">
-        <f>Electricity!L41</f>
-        <v>3.9399732620320855</v>
-      </c>
-      <c r="Z41">
-        <f>Compute!M59</f>
-        <v>43</v>
-      </c>
-      <c r="AA41" s="66">
-        <f>Compute!Q59</f>
-        <v>1.2546901887618654E-5</v>
-      </c>
-      <c r="AB41">
-        <f>'DNA sequencing'!C43</f>
-        <v>10.335386721423674</v>
-      </c>
-      <c r="AC41" s="66">
-        <f>'DNA sequencing'!J43</f>
-        <v>6.259483926466778E-3</v>
-      </c>
-    </row>
-    <row r="42" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V42">
-        <f>Electricity!K42</f>
-        <v>65</v>
-      </c>
-      <c r="W42" s="66">
-        <f>Electricity!L42</f>
-        <v>3.7551083791653181</v>
-      </c>
-      <c r="Z42">
-        <f>Compute!M60</f>
-        <v>44</v>
-      </c>
-      <c r="AA42" s="66">
-        <f>Compute!Q60</f>
-        <v>1.2546901887618654E-5</v>
-      </c>
-      <c r="AB42">
-        <f>'DNA sequencing'!C44</f>
-        <v>10.581793292265729</v>
-      </c>
-      <c r="AC42" s="66">
-        <f>'DNA sequencing'!J44</f>
-        <v>4.8103278850098871E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V43">
-        <f>Electricity!K43</f>
-        <v>66</v>
-      </c>
-      <c r="W43" s="66">
-        <f>Electricity!L43</f>
-        <v>3.6083737024221443</v>
-      </c>
-      <c r="Z43">
-        <f>Compute!M61</f>
-        <v>45</v>
-      </c>
-      <c r="AA43" s="66">
-        <f>Compute!Q61</f>
-        <v>1.2546901887618654E-5</v>
-      </c>
-      <c r="AB43">
-        <f>'DNA sequencing'!C45</f>
-        <v>10.833675564681698</v>
-      </c>
-      <c r="AC43" s="66">
-        <f>'DNA sequencing'!J45</f>
-        <v>4.85276588713253E-3</v>
-      </c>
-    </row>
-    <row r="44" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V44">
-        <f>Electricity!K44</f>
-        <v>67</v>
-      </c>
-      <c r="W44" s="66">
-        <f>Electricity!L44</f>
-        <v>3.541080912214932</v>
-      </c>
-      <c r="Z44">
-        <f>Compute!M62</f>
-        <v>46</v>
-      </c>
-      <c r="AA44" s="66">
-        <f>Compute!Q62</f>
-        <v>2.509380377523731E-6</v>
-      </c>
-      <c r="AB44">
-        <f>'DNA sequencing'!C46</f>
-        <v>11.085557837097895</v>
-      </c>
-      <c r="AC44" s="66">
-        <f>'DNA sequencing'!J46</f>
-        <v>5.3356606328380223E-3</v>
-      </c>
-    </row>
-    <row r="45" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V45">
-        <f>Electricity!K45</f>
-        <v>68</v>
-      </c>
-      <c r="W45" s="66">
-        <f>Electricity!L45</f>
-        <v>3.4394901719901712</v>
-      </c>
-      <c r="Z45">
-        <f>Compute!M63</f>
-        <v>47</v>
-      </c>
-      <c r="AA45" s="66">
-        <f>Compute!Q63</f>
-        <v>2.509380377523731E-6</v>
-      </c>
-      <c r="AB45">
-        <f>'DNA sequencing'!C47</f>
-        <v>11.337440109514091</v>
-      </c>
-      <c r="AC45" s="66">
-        <f>'DNA sequencing'!J47</f>
-        <v>4.5390613351393473E-3</v>
-      </c>
-    </row>
-    <row r="46" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V46">
-        <f>Electricity!K46</f>
-        <v>69</v>
-      </c>
-      <c r="W46" s="66">
-        <f>Electricity!L46</f>
-        <v>3.3774095469747647</v>
-      </c>
-      <c r="Z46">
-        <f>Compute!M64</f>
-        <v>48</v>
-      </c>
-      <c r="AA46" s="66">
-        <f>Compute!Q64</f>
-        <v>4.7678227172950892E-7</v>
-      </c>
-      <c r="AB46">
-        <f>'DNA sequencing'!C48</f>
-        <v>11.581108829568848</v>
-      </c>
-      <c r="AC46" s="66">
-        <f>'DNA sequencing'!J48</f>
-        <v>4.4621528929781468E-3</v>
-      </c>
-    </row>
-    <row r="47" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V47">
-        <f>Electricity!K47</f>
-        <v>70</v>
-      </c>
-      <c r="W47" s="66">
-        <f>Electricity!L47</f>
-        <v>3.2892655027092115</v>
-      </c>
-      <c r="Z47">
-        <f>Compute!M65</f>
-        <v>50</v>
-      </c>
-      <c r="AA47" s="66">
-        <f>Compute!Q65</f>
-        <v>4.7678227172950892E-7</v>
-      </c>
-      <c r="AB47">
-        <f>'DNA sequencing'!C49</f>
-        <v>11.832991101985044</v>
-      </c>
-      <c r="AC47" s="66">
-        <f>'DNA sequencing'!J49</f>
-        <v>4.432278548469012E-3</v>
-      </c>
-    </row>
-    <row r="48" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V48">
-        <f>Electricity!K48</f>
-        <v>71</v>
-      </c>
-      <c r="W48" s="66">
-        <f>Electricity!L48</f>
-        <v>3.1923885918003561</v>
-      </c>
-      <c r="Z48">
-        <f>Compute!M66</f>
-        <v>51</v>
-      </c>
-      <c r="AA48" s="66">
-        <f>Compute!Q66</f>
-        <v>1.5056282265142386E-7</v>
-      </c>
-      <c r="AB48">
-        <f>'DNA sequencing'!C50</f>
-        <v>12.084873374401241</v>
-      </c>
-      <c r="AC48" s="66">
-        <f>'DNA sequencing'!J50</f>
-        <v>4.0583822454023444E-3</v>
-      </c>
-    </row>
-    <row r="49" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V49">
-        <f>Electricity!K49</f>
-        <v>72</v>
-      </c>
-      <c r="W49" s="66">
-        <f>Electricity!L49</f>
-        <v>3.0714193548387092</v>
-      </c>
-      <c r="Z49">
-        <f>Compute!M67</f>
-        <v>52</v>
-      </c>
-      <c r="AA49" s="66">
-        <f>Compute!Q67</f>
-        <v>1.5056282265142386E-7</v>
-      </c>
-      <c r="AB49">
-        <f>'DNA sequencing'!C51</f>
-        <v>12.336755646817437</v>
-      </c>
-      <c r="AC49" s="66">
-        <f>'DNA sequencing'!J51</f>
-        <v>3.1723427881520981E-3</v>
-      </c>
-    </row>
-    <row r="50" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V50">
-        <f>Electricity!K50</f>
-        <v>73</v>
-      </c>
-      <c r="W50" s="66">
-        <f>Electricity!L50</f>
-        <v>2.9441558441558433</v>
-      </c>
-      <c r="Z50">
-        <f>Compute!M68</f>
-        <v>53</v>
-      </c>
-      <c r="AA50" s="66">
-        <f>Compute!Q68</f>
-        <v>5.0187607550474612E-8</v>
-      </c>
-      <c r="AB50">
-        <f>'DNA sequencing'!C52</f>
-        <v>12.580424366872194</v>
-      </c>
-      <c r="AC50" s="66">
-        <f>'DNA sequencing'!J52</f>
-        <v>3.8719458844008944E-3</v>
-      </c>
-    </row>
-    <row r="51" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V51">
-        <f>Electricity!K51</f>
-        <v>74</v>
-      </c>
-      <c r="W51" s="66">
-        <f>Electricity!L51</f>
-        <v>2.7987654320987652</v>
-      </c>
-      <c r="Z51">
-        <f>Compute!M69</f>
-        <v>54</v>
-      </c>
-      <c r="AA51" s="66">
-        <f>Compute!Q69</f>
-        <v>2.5093803775237306E-8</v>
-      </c>
-      <c r="AB51">
-        <f>'DNA sequencing'!C53</f>
-        <v>12.832306639288163</v>
-      </c>
-      <c r="AC51" s="66">
-        <f>'DNA sequencing'!J53</f>
-        <v>3.8508215680075619E-3</v>
-      </c>
-    </row>
-    <row r="52" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V52">
-        <f>Electricity!K52</f>
-        <v>75</v>
-      </c>
-      <c r="W52" s="66">
-        <f>Electricity!L52</f>
-        <v>2.6779477408818719</v>
-      </c>
-      <c r="Z52">
-        <f>Compute!M70</f>
-        <v>55</v>
-      </c>
-      <c r="AA52" s="66">
-        <f>Compute!Q70</f>
-        <v>2.5093803775237306E-8</v>
-      </c>
-      <c r="AB52">
-        <f>'DNA sequencing'!C54</f>
-        <v>13.084188911704359</v>
-      </c>
-      <c r="AC52" s="66">
-        <f>'DNA sequencing'!J54</f>
-        <v>4.5084089040370572E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V53">
-        <f>Electricity!K53</f>
-        <v>76</v>
-      </c>
-      <c r="W53" s="66">
-        <f>Electricity!L53</f>
-        <v>2.5109926854754439</v>
-      </c>
-      <c r="Z53">
-        <f>Compute!M71</f>
-        <v>56</v>
-      </c>
-      <c r="AA53" s="66">
-        <f>Compute!Q71</f>
-        <v>2.5093803775237306E-8</v>
-      </c>
-      <c r="AB53">
-        <f>'DNA sequencing'!C55</f>
-        <v>13.336071184120556</v>
-      </c>
-      <c r="AC53" s="66">
-        <f>'DNA sequencing'!J55</f>
-        <v>3.1447903655264526E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V54">
-        <f>Electricity!K54</f>
-        <v>77</v>
-      </c>
-      <c r="W54" s="66">
-        <f>Electricity!L54</f>
-        <v>2.3473024523160757</v>
-      </c>
-      <c r="Z54">
-        <f>Compute!M72</f>
-        <v>57</v>
-      </c>
-      <c r="AA54" s="66">
-        <f>Compute!Q72</f>
-        <v>2.5093803775237306E-8</v>
-      </c>
-      <c r="AB54">
-        <f>'DNA sequencing'!C56</f>
-        <v>13.579739904175312</v>
-      </c>
-      <c r="AC54" s="66">
-        <f>'DNA sequencing'!J56</f>
-        <v>3.3123140454630736E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V55">
-        <f>Electricity!K55</f>
-        <v>78</v>
-      </c>
-      <c r="W55" s="66">
-        <f>Electricity!L55</f>
-        <v>2.2308809746954079</v>
-      </c>
-      <c r="Z55">
-        <f>Compute!M73</f>
-        <v>58</v>
-      </c>
-      <c r="AA55" s="66">
-        <f>Compute!Q73</f>
-        <v>5.972325298506479E-9</v>
-      </c>
-      <c r="AB55">
-        <f>'DNA sequencing'!C57</f>
-        <v>13.831622176591509</v>
-      </c>
-      <c r="AC55" s="66">
-        <f>'DNA sequencing'!J57</f>
-        <v>1.067710707139257E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V56">
-        <f>Electricity!K56</f>
-        <v>79</v>
-      </c>
-      <c r="W56" s="66">
-        <f>Electricity!L56</f>
-        <v>2.2288350168350166</v>
-      </c>
-      <c r="Z56">
-        <f>Compute!M74</f>
-        <v>59</v>
-      </c>
-      <c r="AA56" s="66">
-        <f>Compute!Q74</f>
-        <v>3.7389767625103586E-9</v>
-      </c>
-      <c r="AB56">
-        <f>'DNA sequencing'!C58</f>
-        <v>14.083504449007705</v>
-      </c>
-      <c r="AC56" s="66">
-        <f>'DNA sequencing'!J58</f>
-        <v>9.7541058846892562E-4</v>
-      </c>
-    </row>
-    <row r="57" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V57">
-        <f>Electricity!K57</f>
-        <v>80</v>
-      </c>
-      <c r="W57" s="66">
-        <f>Electricity!L57</f>
-        <v>2.2581252718573293</v>
-      </c>
-      <c r="Z57">
-        <f>Compute!M75</f>
-        <v>60</v>
-      </c>
-      <c r="AA57" s="66">
-        <f>Compute!Q75</f>
-        <v>3.7389767625103586E-9</v>
-      </c>
-      <c r="AB57">
-        <f>'DNA sequencing'!C59</f>
-        <v>14.666666666666742</v>
-      </c>
-      <c r="AC57" s="66">
-        <f>'DNA sequencing'!J59</f>
-        <v>9.12469670315097E-4</v>
-      </c>
-    </row>
-    <row r="58" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="V58">
-        <f>Electricity!K58</f>
-        <v>81</v>
-      </c>
-      <c r="W58" s="66">
-        <f>Electricity!L58</f>
-        <v>2.209443079443079</v>
-      </c>
-      <c r="Z58">
-        <f>Compute!M76</f>
-        <v>61</v>
-      </c>
-      <c r="AA58" s="66">
-        <f>Compute!Q76</f>
-        <v>1.0263365744072059E-9</v>
-      </c>
-      <c r="AB58">
-        <f>'DNA sequencing'!C60</f>
-        <v>14.918548939082939</v>
-      </c>
-      <c r="AC58" s="66">
-        <f>'DNA sequencing'!J60</f>
-        <v>1.1655187674886646E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB59">
-        <f>'DNA sequencing'!C61</f>
-        <v>15.167693360711837</v>
-      </c>
-      <c r="AC59" s="66">
-        <f>'DNA sequencing'!J61</f>
-        <v>1.0417268640705677E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB60">
-        <f>'DNA sequencing'!C62</f>
-        <v>15.414099931553892</v>
-      </c>
-      <c r="AC60" s="66">
-        <f>'DNA sequencing'!J62</f>
-        <v>7.7616015133699081E-4</v>
-      </c>
-    </row>
-    <row r="61" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB61">
-        <f>'DNA sequencing'!C63</f>
-        <v>15.665982203969861</v>
-      </c>
-      <c r="AC61" s="66">
-        <f>'DNA sequencing'!J63</f>
-        <v>1.0181197746957041E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB62">
-        <f>'DNA sequencing'!C64</f>
-        <v>15.917864476386058</v>
-      </c>
-      <c r="AC62" s="66">
-        <f>'DNA sequencing'!J64</f>
-        <v>8.5785382607503542E-4</v>
-      </c>
-    </row>
-    <row r="63" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB63">
-        <f>'DNA sequencing'!C65</f>
-        <v>16.167008898015183</v>
-      </c>
-      <c r="AC63" s="66">
-        <f>'DNA sequencing'!J65</f>
-        <v>1.3873546008372642E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="22:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB64">
-        <f>'DNA sequencing'!C66</f>
-        <v>16.413415468857011</v>
-      </c>
-      <c r="AC64" s="66">
-        <f>'DNA sequencing'!J66</f>
-        <v>9.2049523124533008E-4</v>
-      </c>
-    </row>
-    <row r="65" spans="28:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB65">
-        <f>'DNA sequencing'!C67</f>
-        <v>16.665297741273207</v>
-      </c>
-      <c r="AC65" s="66">
-        <f>'DNA sequencing'!J67</f>
-        <v>1.0866685918468429E-3</v>
-      </c>
-    </row>
-    <row r="66" spans="28:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB66">
-        <f>'DNA sequencing'!C68</f>
-        <v>16.917180013689403</v>
-      </c>
-      <c r="AC66" s="66">
-        <f>'DNA sequencing'!J68</f>
-        <v>1.0847204116506927E-3</v>
-      </c>
-    </row>
-    <row r="67" spans="28:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB67">
-        <f>'DNA sequencing'!C69</f>
-        <v>17.166324435318302</v>
-      </c>
-      <c r="AC67" s="66">
-        <f>'DNA sequencing'!J69</f>
-        <v>1.0264509761350724E-3</v>
-      </c>
-    </row>
-    <row r="68" spans="28:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB68">
-        <f>'DNA sequencing'!C70</f>
-        <v>17.412731006160357</v>
-      </c>
-      <c r="AC68" s="66">
-        <f>'DNA sequencing'!J70</f>
-        <v>7.2814851439087123E-4</v>
-      </c>
-    </row>
-    <row r="69" spans="28:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB69">
-        <f>'DNA sequencing'!C71</f>
-        <v>17.582477754962383</v>
-      </c>
-      <c r="AC69" s="66">
-        <f>'DNA sequencing'!J71</f>
-        <v>4.4276553363266954E-4</v>
-      </c>
-    </row>
-    <row r="70" spans="28:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB70">
-        <f>'DNA sequencing'!C72</f>
-        <v>17.83436002737858</v>
-      </c>
-      <c r="AC70" s="66">
-        <f>'DNA sequencing'!J72</f>
-        <v>6.8601844627310087E-4</v>
-      </c>
-    </row>
-    <row r="71" spans="28:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB71">
-        <f>'DNA sequencing'!C73</f>
-        <v>18.165639972621648</v>
-      </c>
-      <c r="AC71" s="66">
-        <f>'DNA sequencing'!J73</f>
-        <v>5.012544478800742E-4</v>
-      </c>
-    </row>
-    <row r="72" spans="28:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB72">
-        <f>'DNA sequencing'!C74</f>
-        <v>18.412046543463475</v>
-      </c>
-      <c r="AC72" s="66">
-        <f>'DNA sequencing'!J74</f>
-        <v>4.6566339492538819E-4</v>
-      </c>
-    </row>
-    <row r="73" spans="28:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB73">
-        <f>'DNA sequencing'!C75</f>
-        <v>18.666666666666742</v>
-      </c>
-      <c r="AC73" s="66">
-        <f>'DNA sequencing'!J75</f>
-        <v>5.0883900051850264E-4</v>
-      </c>
-    </row>
-    <row r="74" spans="28:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB74">
-        <f>'DNA sequencing'!C76</f>
-        <v>18.918548939082939</v>
-      </c>
-      <c r="AC74" s="66">
-        <f>'DNA sequencing'!J76</f>
-        <v>4.9373666442219515E-4</v>
-      </c>
-    </row>
-    <row r="75" spans="28:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB75">
-        <f>'DNA sequencing'!C77</f>
-        <v>19.167693360711837</v>
-      </c>
-      <c r="AC75" s="66">
-        <f>'DNA sequencing'!J77</f>
-        <v>3.6423861203251415E-4</v>
-      </c>
-    </row>
-    <row r="76" spans="28:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB76">
-        <f>'DNA sequencing'!C78</f>
-        <v>19.414099931553892</v>
-      </c>
-      <c r="AC76" s="66">
-        <f>'DNA sequencing'!J78</f>
-        <v>5.9866651559596358E-4</v>
-      </c>
-    </row>
-    <row r="77" spans="28:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB77">
-        <f>'DNA sequencing'!C79</f>
-        <v>19.665982203969861</v>
-      </c>
-      <c r="AC77" s="66">
-        <f>'DNA sequencing'!J79</f>
-        <v>3.1275476067508102E-4</v>
-      </c>
-    </row>
-    <row r="78" spans="28:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB78">
-        <f>'DNA sequencing'!C80</f>
-        <v>19.917864476386058</v>
-      </c>
-      <c r="AC78" s="66">
-        <f>'DNA sequencing'!J80</f>
-        <v>3.826328938425051E-4</v>
-      </c>
-    </row>
-    <row r="79" spans="28:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB79">
-        <f>'DNA sequencing'!C81</f>
-        <v>20.167008898015183</v>
-      </c>
-      <c r="AC79" s="66">
-        <f>'DNA sequencing'!J81</f>
-        <v>3.6656030166835174E-4</v>
-      </c>
-    </row>
-    <row r="80" spans="28:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB80">
-        <f>'DNA sequencing'!C82</f>
-        <v>20.413415468857011</v>
-      </c>
-      <c r="AC80" s="66">
-        <f>'DNA sequencing'!J82</f>
-        <v>3.3999026951282637E-4</v>
-      </c>
-    </row>
-    <row r="81" spans="28:29" x14ac:dyDescent="0.55000000000000004">
-      <c r="AB81">
-        <f>'DNA sequencing'!C83</f>
-        <v>20.665297741273207</v>
-      </c>
-      <c r="AC81" s="66">
-        <f>'DNA sequencing'!J83</f>
-        <v>3.3159531996810655E-4</v>
       </c>
     </row>
   </sheetData>
@@ -10070,6 +8104,2004 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB6D3A4C-6A59-45C5-A01B-D7EEAB9986AE}">
+  <dimension ref="A1:J79"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:10" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="65" t="s">
+        <v>227</v>
+      </c>
+      <c r="B1" s="65" t="s">
+        <v>228</v>
+      </c>
+      <c r="C1" s="65" t="s">
+        <v>229</v>
+      </c>
+      <c r="D1" s="65" t="s">
+        <v>230</v>
+      </c>
+      <c r="E1" s="65" t="s">
+        <v>231</v>
+      </c>
+      <c r="F1" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="G1" s="65" t="s">
+        <v>233</v>
+      </c>
+      <c r="H1" s="65" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1" s="65" t="s">
+        <v>235</v>
+      </c>
+      <c r="J1" s="65" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <f>Electricity!K4</f>
+        <v>0</v>
+      </c>
+      <c r="B2" s="64">
+        <f>Electricity!L4</f>
+        <v>100</v>
+      </c>
+      <c r="C2">
+        <f>'Lithium batteries'!D4</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="64">
+        <f>'Lithium batteries'!F4</f>
+        <v>100</v>
+      </c>
+      <c r="E2">
+        <f>Compute!M22</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="64">
+        <f>Compute!Q22</f>
+        <v>100</v>
+      </c>
+      <c r="G2">
+        <f>'DNA sequencing'!C6</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="64">
+        <f>'DNA sequencing'!J6</f>
+        <v>100</v>
+      </c>
+      <c r="I2">
+        <f>Table!$B11</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="64">
+        <f>Table!$C11</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <f>Electricity!K5</f>
+        <v>5</v>
+      </c>
+      <c r="B3" s="64">
+        <f>Electricity!L5</f>
+        <v>98.103137396321642</v>
+      </c>
+      <c r="C3">
+        <f>'Lithium batteries'!D5</f>
+        <v>1</v>
+      </c>
+      <c r="D3" s="64">
+        <f>'Lithium batteries'!F5</f>
+        <v>80.216650398524251</v>
+      </c>
+      <c r="E3">
+        <f>Compute!M23</f>
+        <v>1</v>
+      </c>
+      <c r="F3" s="64">
+        <f>Compute!Q23</f>
+        <v>100</v>
+      </c>
+      <c r="G3">
+        <f>'DNA sequencing'!C7</f>
+        <v>0.49828884325802392</v>
+      </c>
+      <c r="H3" s="64">
+        <f>'DNA sequencing'!J7</f>
+        <v>72.966450166975193</v>
+      </c>
+      <c r="I3">
+        <f>Table!$B12</f>
+        <v>1.6163586584530094</v>
+      </c>
+      <c r="J3" s="64">
+        <f>Table!$C12</f>
+        <v>1.6493911422653169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <f>Electricity!K6</f>
+        <v>10</v>
+      </c>
+      <c r="B4" s="64">
+        <f>Electricity!L6</f>
+        <v>77.924442228328303</v>
+      </c>
+      <c r="C4">
+        <f>'Lithium batteries'!D6</f>
+        <v>2</v>
+      </c>
+      <c r="D4" s="64">
+        <f>'Lithium batteries'!F6</f>
+        <v>63.861393255108737</v>
+      </c>
+      <c r="E4">
+        <f>Compute!M24</f>
+        <v>2</v>
+      </c>
+      <c r="F4" s="64">
+        <f>Compute!Q24</f>
+        <v>35.11547603886779</v>
+      </c>
+      <c r="G4">
+        <f>'DNA sequencing'!C8</f>
+        <v>0.99931553730334599</v>
+      </c>
+      <c r="H4" s="64">
+        <f>'DNA sequencing'!J8</f>
+        <v>63.222391132945198</v>
+      </c>
+      <c r="I4">
+        <f>Table!$B13</f>
+        <v>4.7829586584530261</v>
+      </c>
+      <c r="J4" s="64">
+        <f>Table!$C13</f>
+        <v>5.3075186958275811E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <f>Electricity!K7</f>
+        <v>15</v>
+      </c>
+      <c r="B5" s="64">
+        <f>Electricity!L7</f>
+        <v>46.036688553442083</v>
+      </c>
+      <c r="C5">
+        <f>'Lithium batteries'!D7</f>
+        <v>3</v>
+      </c>
+      <c r="D5" s="64">
+        <f>'Lithium batteries'!F7</f>
+        <v>72.902084964219142</v>
+      </c>
+      <c r="E5">
+        <f>Compute!M25</f>
+        <v>3</v>
+      </c>
+      <c r="F5" s="64">
+        <f>Compute!Q25</f>
+        <v>7.8033172753900661</v>
+      </c>
+      <c r="G5">
+        <f>'DNA sequencing'!C9</f>
+        <v>1.4976043805613699</v>
+      </c>
+      <c r="H5" s="64">
+        <f>'DNA sequencing'!J9</f>
+        <v>54.699705192006995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <f>Electricity!K8</f>
+        <v>20</v>
+      </c>
+      <c r="B6" s="64">
+        <f>Electricity!L8</f>
+        <v>38.533537553467681</v>
+      </c>
+      <c r="C6">
+        <f>'Lithium batteries'!D8</f>
+        <v>4</v>
+      </c>
+      <c r="D6" s="64">
+        <f>'Lithium batteries'!F8</f>
+        <v>68.422648511492127</v>
+      </c>
+      <c r="E6">
+        <f>Compute!M26</f>
+        <v>4</v>
+      </c>
+      <c r="F6" s="64">
+        <f>Compute!Q26</f>
+        <v>7.8033172753900661</v>
+      </c>
+      <c r="G6">
+        <f>'DNA sequencing'!C10</f>
+        <v>2.0835044490077053</v>
+      </c>
+      <c r="H6" s="64">
+        <f>'DNA sequencing'!J10</f>
+        <v>40.468201668292465</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <f>Electricity!K9</f>
+        <v>25</v>
+      </c>
+      <c r="B7" s="64">
+        <f>Electricity!L9</f>
+        <v>24.21568181818181</v>
+      </c>
+      <c r="C7">
+        <f>'Lithium batteries'!D9</f>
+        <v>5</v>
+      </c>
+      <c r="D7" s="64">
+        <f>'Lithium batteries'!F9</f>
+        <v>57.629766031901482</v>
+      </c>
+      <c r="E7">
+        <f>Compute!M27</f>
+        <v>5</v>
+      </c>
+      <c r="F7" s="64">
+        <f>Compute!Q27</f>
+        <v>7.8033172753900661</v>
+      </c>
+      <c r="G7">
+        <f>'DNA sequencing'!C11</f>
+        <v>2.3353867214236743</v>
+      </c>
+      <c r="H7" s="64">
+        <f>'DNA sequencing'!J11</f>
+        <v>28.73892560087431</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
+        <f>Electricity!K10</f>
+        <v>30</v>
+      </c>
+      <c r="B8" s="64">
+        <f>Electricity!L10</f>
+        <v>18.106558441558441</v>
+      </c>
+      <c r="C8">
+        <f>'Lithium batteries'!D10</f>
+        <v>6</v>
+      </c>
+      <c r="D8" s="64">
+        <f>'Lithium batteries'!F10</f>
+        <v>49.3504776753675</v>
+      </c>
+      <c r="E8">
+        <f>Compute!M28</f>
+        <v>6</v>
+      </c>
+      <c r="F8" s="64">
+        <f>Compute!Q28</f>
+        <v>4.6382056926548554</v>
+      </c>
+      <c r="G8">
+        <f>'DNA sequencing'!C12</f>
+        <v>2.5817932922657292</v>
+      </c>
+      <c r="H8" s="64">
+        <f>'DNA sequencing'!J12</f>
+        <v>20.250436288913715</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9">
+        <f>Electricity!K11</f>
+        <v>34</v>
+      </c>
+      <c r="B9" s="64">
+        <f>Electricity!L11</f>
+        <v>16.300975860297893</v>
+      </c>
+      <c r="C9">
+        <f>'Lithium batteries'!D11</f>
+        <v>7</v>
+      </c>
+      <c r="D9" s="64">
+        <f>'Lithium batteries'!F11</f>
+        <v>39.704364603272666</v>
+      </c>
+      <c r="E9">
+        <f>Compute!M29</f>
+        <v>7</v>
+      </c>
+      <c r="F9" s="64">
+        <f>Compute!Q29</f>
+        <v>4.6382056926548554</v>
+      </c>
+      <c r="G9">
+        <f>'DNA sequencing'!C13</f>
+        <v>2.8336755646816982</v>
+      </c>
+      <c r="H9" s="64">
+        <f>'DNA sequencing'!J13</f>
+        <v>19.64261179806801</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <f>Electricity!K12</f>
+        <v>35</v>
+      </c>
+      <c r="B10" s="64">
+        <f>Electricity!L12</f>
+        <v>16.155632183908043</v>
+      </c>
+      <c r="C10">
+        <f>'Lithium batteries'!D12</f>
+        <v>8</v>
+      </c>
+      <c r="D10" s="64">
+        <f>'Lithium batteries'!F12</f>
+        <v>30.073870033647371</v>
+      </c>
+      <c r="E10">
+        <f>Compute!M30</f>
+        <v>8</v>
+      </c>
+      <c r="F10" s="64">
+        <f>Compute!Q30</f>
+        <v>4.6382056926548554</v>
+      </c>
+      <c r="G10">
+        <f>'DNA sequencing'!C14</f>
+        <v>3.0855578370978947</v>
+      </c>
+      <c r="H10" s="64">
+        <f>'DNA sequencing'!J14</f>
+        <v>18.010307127461044</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <f>Electricity!K13</f>
+        <v>36</v>
+      </c>
+      <c r="B11" s="64">
+        <f>Electricity!L13</f>
+        <v>15.98108452950558</v>
+      </c>
+      <c r="C11">
+        <f>'Lithium batteries'!D13</f>
+        <v>9</v>
+      </c>
+      <c r="D11" s="64">
+        <f>'Lithium batteries'!F13</f>
+        <v>29.213463724575828</v>
+      </c>
+      <c r="E11">
+        <f>Compute!M31</f>
+        <v>9</v>
+      </c>
+      <c r="F11" s="64">
+        <f>Compute!Q31</f>
+        <v>0.57840715825846489</v>
+      </c>
+      <c r="G11">
+        <f>'DNA sequencing'!C15</f>
+        <v>3.3374401095140911</v>
+      </c>
+      <c r="H11" s="64">
+        <f>'DNA sequencing'!J15</f>
+        <v>16.990976065198431</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <f>Electricity!K14</f>
+        <v>37</v>
+      </c>
+      <c r="B12" s="64">
+        <f>Electricity!L14</f>
+        <v>15.257958532695373</v>
+      </c>
+      <c r="C12">
+        <f>'Lithium batteries'!D14</f>
+        <v>10</v>
+      </c>
+      <c r="D12" s="64">
+        <f>'Lithium batteries'!F14</f>
+        <v>20.390688397575303</v>
+      </c>
+      <c r="E12">
+        <f>Compute!M32</f>
+        <v>10</v>
+      </c>
+      <c r="F12" s="64">
+        <f>Compute!Q32</f>
+        <v>0.57840715825846489</v>
+      </c>
+      <c r="G12">
+        <f>'DNA sequencing'!C16</f>
+        <v>3.5811088295688478</v>
+      </c>
+      <c r="H12" s="64">
+        <f>'DNA sequencing'!J16</f>
+        <v>15.56131540651009</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
+        <f>Electricity!K15</f>
+        <v>38</v>
+      </c>
+      <c r="B13" s="64">
+        <f>Electricity!L15</f>
+        <v>14.882972237343495</v>
+      </c>
+      <c r="C13">
+        <f>'Lithium batteries'!D15</f>
+        <v>11</v>
+      </c>
+      <c r="D13" s="64">
+        <f>'Lithium batteries'!F15</f>
+        <v>14.609075994844863</v>
+      </c>
+      <c r="E13">
+        <f>Compute!M33</f>
+        <v>11</v>
+      </c>
+      <c r="F13" s="64">
+        <f>Compute!Q33</f>
+        <v>0.57840715825846489</v>
+      </c>
+      <c r="G13">
+        <f>'DNA sequencing'!C17</f>
+        <v>3.8329911019850442</v>
+      </c>
+      <c r="H13" s="64">
+        <f>'DNA sequencing'!J17</f>
+        <v>15.382443136010684</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
+        <f>Electricity!K16</f>
+        <v>39</v>
+      </c>
+      <c r="B14" s="64">
+        <f>Electricity!L16</f>
+        <v>15.673755980861243</v>
+      </c>
+      <c r="C14">
+        <f>'Lithium batteries'!D16</f>
+        <v>12</v>
+      </c>
+      <c r="D14" s="64">
+        <f>'Lithium batteries'!F16</f>
+        <v>11.295786315868334</v>
+      </c>
+      <c r="E14">
+        <f>Compute!M34</f>
+        <v>12</v>
+      </c>
+      <c r="F14" s="64">
+        <f>Compute!Q34</f>
+        <v>0.57840715825846489</v>
+      </c>
+      <c r="G14">
+        <f>'DNA sequencing'!C18</f>
+        <v>4.0848733744012407</v>
+      </c>
+      <c r="H14" s="64">
+        <f>'DNA sequencing'!J18</f>
+        <v>12.988182068984196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
+        <f>Electricity!K17</f>
+        <v>40</v>
+      </c>
+      <c r="B15" s="64">
+        <f>Electricity!L17</f>
+        <v>16.878394160583941</v>
+      </c>
+      <c r="C15">
+        <f>'Lithium batteries'!D17</f>
+        <v>13</v>
+      </c>
+      <c r="D15" s="64">
+        <f>'Lithium batteries'!F17</f>
+        <v>10.107282119990488</v>
+      </c>
+      <c r="E15">
+        <f>Compute!M35</f>
+        <v>13</v>
+      </c>
+      <c r="F15" s="64">
+        <f>Compute!Q35</f>
+        <v>0.11894462989462484</v>
+      </c>
+      <c r="G15">
+        <f>'DNA sequencing'!C19</f>
+        <v>4.3367556468174371</v>
+      </c>
+      <c r="H15" s="64">
+        <f>'DNA sequencing'!J19</f>
+        <v>11.76709291497095</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16">
+        <f>Electricity!K18</f>
+        <v>41</v>
+      </c>
+      <c r="B16" s="64">
+        <f>Electricity!L18</f>
+        <v>17.501874125874121</v>
+      </c>
+      <c r="C16">
+        <f>'Lithium batteries'!D18</f>
+        <v>14</v>
+      </c>
+      <c r="D16" s="64">
+        <f>'Lithium batteries'!F18</f>
+        <v>8.7135380983971089</v>
+      </c>
+      <c r="E16">
+        <f>Compute!M36</f>
+        <v>14</v>
+      </c>
+      <c r="F16" s="64">
+        <f>Compute!Q36</f>
+        <v>0.11894462989462484</v>
+      </c>
+      <c r="G16">
+        <f>'DNA sequencing'!C20</f>
+        <v>4.5804243668721938</v>
+      </c>
+      <c r="H16" s="64">
+        <f>'DNA sequencing'!J20</f>
+        <v>10.865918549877641</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17">
+        <f>Electricity!K19</f>
+        <v>42</v>
+      </c>
+      <c r="B17" s="64">
+        <f>Electricity!L19</f>
+        <v>16.394993215739483</v>
+      </c>
+      <c r="C17">
+        <f>'Lithium batteries'!D19</f>
+        <v>15</v>
+      </c>
+      <c r="D17" s="64">
+        <f>'Lithium batteries'!F19</f>
+        <v>7.4623091931471857</v>
+      </c>
+      <c r="E17">
+        <f>Compute!M37</f>
+        <v>15</v>
+      </c>
+      <c r="F17" s="64">
+        <f>Compute!Q37</f>
+        <v>3.9869035438097035E-2</v>
+      </c>
+      <c r="G17">
+        <f>'DNA sequencing'!C21</f>
+        <v>4.8323066392881628</v>
+      </c>
+      <c r="H17" s="64">
+        <f>'DNA sequencing'!J21</f>
+        <v>10.479033872157595</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18">
+        <f>Electricity!K20</f>
+        <v>43</v>
+      </c>
+      <c r="B18" s="64">
+        <f>Electricity!L20</f>
+        <v>15.073218314532181</v>
+      </c>
+      <c r="C18">
+        <f>'Lithium batteries'!D20</f>
+        <v>16</v>
+      </c>
+      <c r="D18" s="64">
+        <f>'Lithium batteries'!F20</f>
+        <v>7.1207342270497049</v>
+      </c>
+      <c r="E18">
+        <f>Compute!M38</f>
+        <v>18</v>
+      </c>
+      <c r="F18" s="64">
+        <f>Compute!Q38</f>
+        <v>3.9869035438097035E-2</v>
+      </c>
+      <c r="G18">
+        <f>'DNA sequencing'!C22</f>
+        <v>5.0841889117043593</v>
+      </c>
+      <c r="H18" s="64">
+        <f>'DNA sequencing'!J22</f>
+        <v>9.6672432806743718</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19">
+        <f>Electricity!K21</f>
+        <v>44</v>
+      </c>
+      <c r="B19" s="64">
+        <f>Electricity!L21</f>
+        <v>13.848122956180505</v>
+      </c>
+      <c r="C19">
+        <f>'Lithium batteries'!D21</f>
+        <v>17</v>
+      </c>
+      <c r="D19" s="64">
+        <f>'Lithium batteries'!F21</f>
+        <v>7.4662293992658171</v>
+      </c>
+      <c r="E19">
+        <f>Compute!M39</f>
+        <v>19</v>
+      </c>
+      <c r="F19" s="64">
+        <f>Compute!Q39</f>
+        <v>3.9869035438097035E-2</v>
+      </c>
+      <c r="G19">
+        <f>'DNA sequencing'!C23</f>
+        <v>5.3360711841205557</v>
+      </c>
+      <c r="H19" s="64">
+        <f>'DNA sequencing'!J23</f>
+        <v>8.5889241079984053</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20">
+        <f>Electricity!K22</f>
+        <v>45</v>
+      </c>
+      <c r="B20" s="64">
+        <f>Electricity!L22</f>
+        <v>12.279583333333331</v>
+      </c>
+      <c r="C20">
+        <f>'Lithium batteries'!D22</f>
+        <v>18</v>
+      </c>
+      <c r="D20" s="64">
+        <f>'Lithium batteries'!F22</f>
+        <v>6.6510416135101948</v>
+      </c>
+      <c r="E20">
+        <f>Compute!M40</f>
+        <v>20</v>
+      </c>
+      <c r="F20" s="64">
+        <f>Compute!Q40</f>
+        <v>1.4230696120937077E-2</v>
+      </c>
+      <c r="G20">
+        <f>'DNA sequencing'!C24</f>
+        <v>5.5797399041753124</v>
+      </c>
+      <c r="H20" s="64">
+        <f>'DNA sequencing'!J24</f>
+        <v>8.1576880020311346</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21">
+        <f>Electricity!K23</f>
+        <v>46</v>
+      </c>
+      <c r="B21" s="64">
+        <f>Electricity!L23</f>
+        <v>12.102359767891679</v>
+      </c>
+      <c r="C21">
+        <f>'Lithium batteries'!D23</f>
+        <v>19</v>
+      </c>
+      <c r="D21" s="64">
+        <f>'Lithium batteries'!F23</f>
+        <v>5.9794450301458273</v>
+      </c>
+      <c r="E21">
+        <f>Compute!M41</f>
+        <v>21</v>
+      </c>
+      <c r="F21" s="64">
+        <f>Compute!Q41</f>
+        <v>1.3078890527653684E-2</v>
+      </c>
+      <c r="G21">
+        <f>'DNA sequencing'!C25</f>
+        <v>5.8316221765915088</v>
+      </c>
+      <c r="H21" s="64">
+        <f>'DNA sequencing'!J25</f>
+        <v>8.0144379342313012</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22">
+        <f>Electricity!K24</f>
+        <v>47</v>
+      </c>
+      <c r="B22" s="64">
+        <f>Electricity!L24</f>
+        <v>11.861347285807716</v>
+      </c>
+      <c r="C22">
+        <f>'Lithium batteries'!D24</f>
+        <v>20</v>
+      </c>
+      <c r="D22" s="64">
+        <f>'Lithium batteries'!F24</f>
+        <v>5.6958182368952777</v>
+      </c>
+      <c r="E22">
+        <f>Compute!M42</f>
+        <v>22</v>
+      </c>
+      <c r="F22" s="64">
+        <f>Compute!Q42</f>
+        <v>1.3078890527653684E-2</v>
+      </c>
+      <c r="G22">
+        <f>'DNA sequencing'!C26</f>
+        <v>6.0835044490077053</v>
+      </c>
+      <c r="H22" s="64">
+        <f>'DNA sequencing'!J26</f>
+        <v>6.3202787487277767</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23">
+        <f>Electricity!K25</f>
+        <v>48</v>
+      </c>
+      <c r="B23" s="64">
+        <f>Electricity!L25</f>
+        <v>11.305558441558441</v>
+      </c>
+      <c r="C23">
+        <f>'Lithium batteries'!D25</f>
+        <v>21</v>
+      </c>
+      <c r="D23" s="64">
+        <f>'Lithium batteries'!F25</f>
+        <v>5.8597070865765568</v>
+      </c>
+      <c r="E23">
+        <f>Compute!M43</f>
+        <v>23</v>
+      </c>
+      <c r="F23" s="64">
+        <f>Compute!Q43</f>
+        <v>1.3078890527653684E-2</v>
+      </c>
+      <c r="G23">
+        <f>'DNA sequencing'!C27</f>
+        <v>6.3353867214236743</v>
+      </c>
+      <c r="H23" s="64">
+        <f>'DNA sequencing'!J27</f>
+        <v>2.6855959871058328</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24">
+        <f>Electricity!K26</f>
+        <v>49</v>
+      </c>
+      <c r="B24" s="64">
+        <f>Electricity!L26</f>
+        <v>10.458763141620283</v>
+      </c>
+      <c r="C24">
+        <f>'Lithium batteries'!D26</f>
+        <v>22</v>
+      </c>
+      <c r="D24" s="64">
+        <f>'Lithium batteries'!F26</f>
+        <v>5.3298723267497126</v>
+      </c>
+      <c r="E24">
+        <f>Compute!M44</f>
+        <v>24</v>
+      </c>
+      <c r="F24" s="64">
+        <f>Compute!Q44</f>
+        <v>4.4641876916147174E-3</v>
+      </c>
+      <c r="G24">
+        <f>'DNA sequencing'!C28</f>
+        <v>6.5817932922657292</v>
+      </c>
+      <c r="H24" s="64">
+        <f>'DNA sequencing'!J28</f>
+        <v>1.1720659796107069</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25">
+        <f>Electricity!K27</f>
+        <v>50</v>
+      </c>
+      <c r="B25" s="64">
+        <f>Electricity!L27</f>
+        <v>9.3056999442275501</v>
+      </c>
+      <c r="C25">
+        <f>'Lithium batteries'!D27</f>
+        <v>23</v>
+      </c>
+      <c r="D25" s="64">
+        <f>'Lithium batteries'!F27</f>
+        <v>4.715082033782001</v>
+      </c>
+      <c r="E25">
+        <f>Compute!M45</f>
+        <v>25</v>
+      </c>
+      <c r="F25" s="64">
+        <f>Compute!Q45</f>
+        <v>4.4641876916147174E-3</v>
+      </c>
+      <c r="G25">
+        <f>'DNA sequencing'!C29</f>
+        <v>6.8336755646816982</v>
+      </c>
+      <c r="H25" s="64">
+        <f>'DNA sequencing'!J29</f>
+        <v>0.64114083441616443</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26">
+        <f>Electricity!K28</f>
+        <v>51</v>
+      </c>
+      <c r="B26" s="64">
+        <f>Electricity!L28</f>
+        <v>8.5771939043615344</v>
+      </c>
+      <c r="C26">
+        <f>'Lithium batteries'!D28</f>
+        <v>24</v>
+      </c>
+      <c r="D26" s="64">
+        <f>'Lithium batteries'!F28</f>
+        <v>3.6040658050884722</v>
+      </c>
+      <c r="E26">
+        <f>Compute!M46</f>
+        <v>26</v>
+      </c>
+      <c r="F26" s="64">
+        <f>Compute!Q46</f>
+        <v>4.4641876916147174E-3</v>
+      </c>
+      <c r="G26">
+        <f>'DNA sequencing'!C30</f>
+        <v>7.0855578370978947</v>
+      </c>
+      <c r="H26" s="64">
+        <f>'DNA sequencing'!J30</f>
+        <v>0.29956434297798684</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27">
+        <f>Electricity!K29</f>
+        <v>52</v>
+      </c>
+      <c r="B27" s="64">
+        <f>Electricity!L29</f>
+        <v>8.2202169421487579</v>
+      </c>
+      <c r="C27">
+        <f>'Lithium batteries'!D29</f>
+        <v>25</v>
+      </c>
+      <c r="D27" s="64">
+        <f>'Lithium batteries'!F29</f>
+        <v>2.8120904689676589</v>
+      </c>
+      <c r="E27">
+        <f>Compute!M47</f>
+        <v>27</v>
+      </c>
+      <c r="F27" s="64">
+        <f>Compute!Q47</f>
+        <v>4.4641876916147174E-3</v>
+      </c>
+      <c r="G27">
+        <f>'DNA sequencing'!C31</f>
+        <v>7.3374401095140911</v>
+      </c>
+      <c r="H27" s="64">
+        <f>'DNA sequencing'!J31</f>
+        <v>0.20398733178367293</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28">
+        <f>Electricity!K30</f>
+        <v>53</v>
+      </c>
+      <c r="B28" s="64">
+        <f>Electricity!L30</f>
+        <v>7.8085555555555537</v>
+      </c>
+      <c r="C28">
+        <f>'Lithium batteries'!D30</f>
+        <v>26</v>
+      </c>
+      <c r="D28" s="64">
+        <f>'Lithium batteries'!F30</f>
+        <v>2.0303510335789658</v>
+      </c>
+      <c r="E28">
+        <f>Compute!M48</f>
+        <v>29</v>
+      </c>
+      <c r="F28" s="64">
+        <f>Compute!Q48</f>
+        <v>2.3236862295869746E-3</v>
+      </c>
+      <c r="G28">
+        <f>'DNA sequencing'!C32</f>
+        <v>7.5811088295688478</v>
+      </c>
+      <c r="H28" s="64">
+        <f>'DNA sequencing'!J32</f>
+        <v>0.13540116803166066</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29">
+        <f>Electricity!K31</f>
+        <v>54</v>
+      </c>
+      <c r="B29" s="64">
+        <f>Electricity!L31</f>
+        <v>6.8062843822843817</v>
+      </c>
+      <c r="C29">
+        <f>'Lithium batteries'!D31</f>
+        <v>27</v>
+      </c>
+      <c r="D29" s="64">
+        <f>'Lithium batteries'!F31</f>
+        <v>1.7046262688336773</v>
+      </c>
+      <c r="E29">
+        <f>Compute!M49</f>
+        <v>30</v>
+      </c>
+      <c r="F29" s="64">
+        <f>Compute!Q49</f>
+        <v>2.3236862295869746E-3</v>
+      </c>
+      <c r="G29">
+        <f>'DNA sequencing'!C33</f>
+        <v>7.8329911019850442</v>
+      </c>
+      <c r="H29" s="64">
+        <f>'DNA sequencing'!J33</f>
+        <v>9.351205005827852E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30">
+        <f>Electricity!K32</f>
+        <v>55</v>
+      </c>
+      <c r="B30" s="64">
+        <f>Electricity!L32</f>
+        <v>5.7113982878108427</v>
+      </c>
+      <c r="C30">
+        <f>'Lithium batteries'!D32</f>
+        <v>28</v>
+      </c>
+      <c r="D30" s="64">
+        <f>'Lithium batteries'!F32</f>
+        <v>1.4331889648792702</v>
+      </c>
+      <c r="E30">
+        <f>Compute!M50</f>
+        <v>31</v>
+      </c>
+      <c r="F30" s="64">
+        <f>Compute!Q50</f>
+        <v>2.3236862295869746E-3</v>
+      </c>
+      <c r="G30">
+        <f>'DNA sequencing'!C34</f>
+        <v>8.0848733744012407</v>
+      </c>
+      <c r="H30" s="64">
+        <f>'DNA sequencing'!J34</f>
+        <v>6.0360355326899352E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31">
+        <f>Electricity!K33</f>
+        <v>56</v>
+      </c>
+      <c r="B31" s="64">
+        <f>Electricity!L33</f>
+        <v>5.1479969822708398</v>
+      </c>
+      <c r="C31">
+        <f>'Lithium batteries'!D33</f>
+        <v>29</v>
+      </c>
+      <c r="D31" s="64">
+        <f>'Lithium batteries'!F33</f>
+        <v>1.3354715354556836</v>
+      </c>
+      <c r="E31">
+        <f>Compute!M51</f>
+        <v>32</v>
+      </c>
+      <c r="F31" s="64">
+        <f>Compute!Q51</f>
+        <v>2.3236862295869746E-3</v>
+      </c>
+      <c r="G31">
+        <f>'DNA sequencing'!C35</f>
+        <v>8.3367556468174371</v>
+      </c>
+      <c r="H31" s="64">
+        <f>'DNA sequencing'!J35</f>
+        <v>4.0133189210794687E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32">
+        <f>Electricity!K34</f>
+        <v>57</v>
+      </c>
+      <c r="B32" s="64">
+        <f>Electricity!L34</f>
+        <v>5.1089763177998471</v>
+      </c>
+      <c r="C32">
+        <f>'Lithium batteries'!D34</f>
+        <v>30</v>
+      </c>
+      <c r="D32" s="64">
+        <f>'Lithium batteries'!F34</f>
+        <v>1.2920415668229785</v>
+      </c>
+      <c r="E32">
+        <f>Compute!M52</f>
+        <v>33</v>
+      </c>
+      <c r="F32" s="64">
+        <f>Compute!Q52</f>
+        <v>2.3236862295869746E-3</v>
+      </c>
+      <c r="G32">
+        <f>'DNA sequencing'!C36</f>
+        <v>8.5804243668721938</v>
+      </c>
+      <c r="H32" s="64">
+        <f>'DNA sequencing'!J36</f>
+        <v>2.7036791526076815E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33">
+        <f>Electricity!K35</f>
+        <v>58</v>
+      </c>
+      <c r="B33" s="64">
+        <f>Electricity!L35</f>
+        <v>4.925658242172763</v>
+      </c>
+      <c r="C33">
+        <f>'Lithium batteries'!D35</f>
+        <v>31</v>
+      </c>
+      <c r="D33" s="64">
+        <f>'Lithium batteries'!F35</f>
+        <v>1.4331889648792702</v>
+      </c>
+      <c r="E33">
+        <f>Compute!M53</f>
+        <v>35</v>
+      </c>
+      <c r="F33" s="64">
+        <f>Compute!Q53</f>
+        <v>2.3236862295869746E-3</v>
+      </c>
+      <c r="G33">
+        <f>'DNA sequencing'!C37</f>
+        <v>8.8323066392881628</v>
+      </c>
+      <c r="H33" s="64">
+        <f>'DNA sequencing'!J37</f>
+        <v>2.662711554270181E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34">
+        <f>Electricity!K36</f>
+        <v>59</v>
+      </c>
+      <c r="B34" s="64">
+        <f>Electricity!L36</f>
+        <v>4.454734265734265</v>
+      </c>
+      <c r="C34">
+        <f>'Lithium batteries'!D36</f>
+        <v>32</v>
+      </c>
+      <c r="D34" s="64">
+        <f>'Lithium batteries'!F36</f>
+        <v>1.2051816295575681</v>
+      </c>
+      <c r="E34">
+        <f>Compute!M54</f>
+        <v>36</v>
+      </c>
+      <c r="F34" s="64">
+        <f>Compute!Q54</f>
+        <v>3.161819275679901E-4</v>
+      </c>
+      <c r="G34">
+        <f>'DNA sequencing'!C38</f>
+        <v>9.0841889117043593</v>
+      </c>
+      <c r="H34" s="64">
+        <f>'DNA sequencing'!J38</f>
+        <v>2.4698775629687982E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35">
+        <f>Electricity!K37</f>
+        <v>60</v>
+      </c>
+      <c r="B35" s="64">
+        <f>Electricity!L37</f>
+        <v>4.3084665523156085</v>
+      </c>
+      <c r="C35">
+        <f>'Lithium batteries'!D37</f>
+        <v>33</v>
+      </c>
+      <c r="D35" s="64">
+        <f>'Lithium batteries'!F37</f>
+        <v>0.84688438833775048</v>
+      </c>
+      <c r="E35">
+        <f>Compute!M55</f>
+        <v>37</v>
+      </c>
+      <c r="F35" s="64">
+        <f>Compute!Q55</f>
+        <v>7.2772030948188199E-5</v>
+      </c>
+      <c r="G35">
+        <f>'DNA sequencing'!C39</f>
+        <v>9.3360711841205557</v>
+      </c>
+      <c r="H35" s="64">
+        <f>'DNA sequencing'!J39</f>
+        <v>1.7612212416533383E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36">
+        <f>Electricity!K38</f>
+        <v>61</v>
+      </c>
+      <c r="B36" s="64">
+        <f>Electricity!L38</f>
+        <v>4.2298808307797069</v>
+      </c>
+      <c r="E36">
+        <f>Compute!M56</f>
+        <v>38</v>
+      </c>
+      <c r="F36" s="64">
+        <f>Compute!Q56</f>
+        <v>7.2772030948188199E-5</v>
+      </c>
+      <c r="G36">
+        <f>'DNA sequencing'!C40</f>
+        <v>9.5797399041753124</v>
+      </c>
+      <c r="H36" s="64">
+        <f>'DNA sequencing'!J40</f>
+        <v>1.3859234684711133E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37">
+        <f>Electricity!K39</f>
+        <v>62</v>
+      </c>
+      <c r="B37" s="64">
+        <f>Electricity!L39</f>
+        <v>4.1218181818181812</v>
+      </c>
+      <c r="E37">
+        <f>Compute!M57</f>
+        <v>40</v>
+      </c>
+      <c r="F37" s="64">
+        <f>Compute!Q57</f>
+        <v>7.2772030948188199E-5</v>
+      </c>
+      <c r="G37">
+        <f>'DNA sequencing'!C41</f>
+        <v>9.8316221765915088</v>
+      </c>
+      <c r="H37" s="64">
+        <f>'DNA sequencing'!J41</f>
+        <v>8.6550335982576426E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38">
+        <f>Electricity!K40</f>
+        <v>63</v>
+      </c>
+      <c r="B38" s="64">
+        <f>Electricity!L40</f>
+        <v>4.0602985074626865</v>
+      </c>
+      <c r="E38">
+        <f>Compute!M58</f>
+        <v>42</v>
+      </c>
+      <c r="F38" s="64">
+        <f>Compute!Q58</f>
+        <v>1.2546901887618654E-5</v>
+      </c>
+      <c r="G38">
+        <f>'DNA sequencing'!C42</f>
+        <v>10.080766598220407</v>
+      </c>
+      <c r="H38" s="64">
+        <f>'DNA sequencing'!J42</f>
+        <v>6.3548184017738268E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39">
+        <f>Electricity!K41</f>
+        <v>64</v>
+      </c>
+      <c r="B39" s="64">
+        <f>Electricity!L41</f>
+        <v>3.9399732620320855</v>
+      </c>
+      <c r="E39">
+        <f>Compute!M59</f>
+        <v>43</v>
+      </c>
+      <c r="F39" s="64">
+        <f>Compute!Q59</f>
+        <v>1.2546901887618654E-5</v>
+      </c>
+      <c r="G39">
+        <f>'DNA sequencing'!C43</f>
+        <v>10.335386721423674</v>
+      </c>
+      <c r="H39" s="64">
+        <f>'DNA sequencing'!J43</f>
+        <v>6.259483926466778E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40">
+        <f>Electricity!K42</f>
+        <v>65</v>
+      </c>
+      <c r="B40" s="64">
+        <f>Electricity!L42</f>
+        <v>3.7551083791653181</v>
+      </c>
+      <c r="E40">
+        <f>Compute!M60</f>
+        <v>44</v>
+      </c>
+      <c r="F40" s="64">
+        <f>Compute!Q60</f>
+        <v>1.2546901887618654E-5</v>
+      </c>
+      <c r="G40">
+        <f>'DNA sequencing'!C44</f>
+        <v>10.581793292265729</v>
+      </c>
+      <c r="H40" s="64">
+        <f>'DNA sequencing'!J44</f>
+        <v>4.8103278850098871E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41">
+        <f>Electricity!K43</f>
+        <v>66</v>
+      </c>
+      <c r="B41" s="64">
+        <f>Electricity!L43</f>
+        <v>3.6083737024221443</v>
+      </c>
+      <c r="E41">
+        <f>Compute!M61</f>
+        <v>45</v>
+      </c>
+      <c r="F41" s="64">
+        <f>Compute!Q61</f>
+        <v>1.2546901887618654E-5</v>
+      </c>
+      <c r="G41">
+        <f>'DNA sequencing'!C45</f>
+        <v>10.833675564681698</v>
+      </c>
+      <c r="H41" s="64">
+        <f>'DNA sequencing'!J45</f>
+        <v>4.85276588713253E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42">
+        <f>Electricity!K44</f>
+        <v>67</v>
+      </c>
+      <c r="B42" s="64">
+        <f>Electricity!L44</f>
+        <v>3.541080912214932</v>
+      </c>
+      <c r="E42">
+        <f>Compute!M62</f>
+        <v>46</v>
+      </c>
+      <c r="F42" s="64">
+        <f>Compute!Q62</f>
+        <v>2.509380377523731E-6</v>
+      </c>
+      <c r="G42">
+        <f>'DNA sequencing'!C46</f>
+        <v>11.085557837097895</v>
+      </c>
+      <c r="H42" s="64">
+        <f>'DNA sequencing'!J46</f>
+        <v>5.3356606328380223E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43">
+        <f>Electricity!K45</f>
+        <v>68</v>
+      </c>
+      <c r="B43" s="64">
+        <f>Electricity!L45</f>
+        <v>3.4394901719901712</v>
+      </c>
+      <c r="E43">
+        <f>Compute!M63</f>
+        <v>47</v>
+      </c>
+      <c r="F43" s="64">
+        <f>Compute!Q63</f>
+        <v>2.509380377523731E-6</v>
+      </c>
+      <c r="G43">
+        <f>'DNA sequencing'!C47</f>
+        <v>11.337440109514091</v>
+      </c>
+      <c r="H43" s="64">
+        <f>'DNA sequencing'!J47</f>
+        <v>4.5390613351393473E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44">
+        <f>Electricity!K46</f>
+        <v>69</v>
+      </c>
+      <c r="B44" s="64">
+        <f>Electricity!L46</f>
+        <v>3.3774095469747647</v>
+      </c>
+      <c r="E44">
+        <f>Compute!M64</f>
+        <v>48</v>
+      </c>
+      <c r="F44" s="64">
+        <f>Compute!Q64</f>
+        <v>4.7678227172950892E-7</v>
+      </c>
+      <c r="G44">
+        <f>'DNA sequencing'!C48</f>
+        <v>11.581108829568848</v>
+      </c>
+      <c r="H44" s="64">
+        <f>'DNA sequencing'!J48</f>
+        <v>4.4621528929781468E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45">
+        <f>Electricity!K47</f>
+        <v>70</v>
+      </c>
+      <c r="B45" s="64">
+        <f>Electricity!L47</f>
+        <v>3.2892655027092115</v>
+      </c>
+      <c r="E45">
+        <f>Compute!M65</f>
+        <v>50</v>
+      </c>
+      <c r="F45" s="64">
+        <f>Compute!Q65</f>
+        <v>4.7678227172950892E-7</v>
+      </c>
+      <c r="G45">
+        <f>'DNA sequencing'!C49</f>
+        <v>11.832991101985044</v>
+      </c>
+      <c r="H45" s="64">
+        <f>'DNA sequencing'!J49</f>
+        <v>4.432278548469012E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46">
+        <f>Electricity!K48</f>
+        <v>71</v>
+      </c>
+      <c r="B46" s="64">
+        <f>Electricity!L48</f>
+        <v>3.1923885918003561</v>
+      </c>
+      <c r="E46">
+        <f>Compute!M66</f>
+        <v>51</v>
+      </c>
+      <c r="F46" s="64">
+        <f>Compute!Q66</f>
+        <v>1.5056282265142386E-7</v>
+      </c>
+      <c r="G46">
+        <f>'DNA sequencing'!C50</f>
+        <v>12.084873374401241</v>
+      </c>
+      <c r="H46" s="64">
+        <f>'DNA sequencing'!J50</f>
+        <v>4.0583822454023444E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47">
+        <f>Electricity!K49</f>
+        <v>72</v>
+      </c>
+      <c r="B47" s="64">
+        <f>Electricity!L49</f>
+        <v>3.0714193548387092</v>
+      </c>
+      <c r="E47">
+        <f>Compute!M67</f>
+        <v>52</v>
+      </c>
+      <c r="F47" s="64">
+        <f>Compute!Q67</f>
+        <v>1.5056282265142386E-7</v>
+      </c>
+      <c r="G47">
+        <f>'DNA sequencing'!C51</f>
+        <v>12.336755646817437</v>
+      </c>
+      <c r="H47" s="64">
+        <f>'DNA sequencing'!J51</f>
+        <v>3.1723427881520981E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48">
+        <f>Electricity!K50</f>
+        <v>73</v>
+      </c>
+      <c r="B48" s="64">
+        <f>Electricity!L50</f>
+        <v>2.9441558441558433</v>
+      </c>
+      <c r="E48">
+        <f>Compute!M68</f>
+        <v>53</v>
+      </c>
+      <c r="F48" s="64">
+        <f>Compute!Q68</f>
+        <v>5.0187607550474612E-8</v>
+      </c>
+      <c r="G48">
+        <f>'DNA sequencing'!C52</f>
+        <v>12.580424366872194</v>
+      </c>
+      <c r="H48" s="64">
+        <f>'DNA sequencing'!J52</f>
+        <v>3.8719458844008944E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49">
+        <f>Electricity!K51</f>
+        <v>74</v>
+      </c>
+      <c r="B49" s="64">
+        <f>Electricity!L51</f>
+        <v>2.7987654320987652</v>
+      </c>
+      <c r="E49">
+        <f>Compute!M69</f>
+        <v>54</v>
+      </c>
+      <c r="F49" s="64">
+        <f>Compute!Q69</f>
+        <v>2.5093803775237306E-8</v>
+      </c>
+      <c r="G49">
+        <f>'DNA sequencing'!C53</f>
+        <v>12.832306639288163</v>
+      </c>
+      <c r="H49" s="64">
+        <f>'DNA sequencing'!J53</f>
+        <v>3.8508215680075619E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50">
+        <f>Electricity!K52</f>
+        <v>75</v>
+      </c>
+      <c r="B50" s="64">
+        <f>Electricity!L52</f>
+        <v>2.6779477408818719</v>
+      </c>
+      <c r="E50">
+        <f>Compute!M70</f>
+        <v>55</v>
+      </c>
+      <c r="F50" s="64">
+        <f>Compute!Q70</f>
+        <v>2.5093803775237306E-8</v>
+      </c>
+      <c r="G50">
+        <f>'DNA sequencing'!C54</f>
+        <v>13.084188911704359</v>
+      </c>
+      <c r="H50" s="64">
+        <f>'DNA sequencing'!J54</f>
+        <v>4.5084089040370572E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51">
+        <f>Electricity!K53</f>
+        <v>76</v>
+      </c>
+      <c r="B51" s="64">
+        <f>Electricity!L53</f>
+        <v>2.5109926854754439</v>
+      </c>
+      <c r="E51">
+        <f>Compute!M71</f>
+        <v>56</v>
+      </c>
+      <c r="F51" s="64">
+        <f>Compute!Q71</f>
+        <v>2.5093803775237306E-8</v>
+      </c>
+      <c r="G51">
+        <f>'DNA sequencing'!C55</f>
+        <v>13.336071184120556</v>
+      </c>
+      <c r="H51" s="64">
+        <f>'DNA sequencing'!J55</f>
+        <v>3.1447903655264526E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52">
+        <f>Electricity!K54</f>
+        <v>77</v>
+      </c>
+      <c r="B52" s="64">
+        <f>Electricity!L54</f>
+        <v>2.3473024523160757</v>
+      </c>
+      <c r="E52">
+        <f>Compute!M72</f>
+        <v>57</v>
+      </c>
+      <c r="F52" s="64">
+        <f>Compute!Q72</f>
+        <v>2.5093803775237306E-8</v>
+      </c>
+      <c r="G52">
+        <f>'DNA sequencing'!C56</f>
+        <v>13.579739904175312</v>
+      </c>
+      <c r="H52" s="64">
+        <f>'DNA sequencing'!J56</f>
+        <v>3.3123140454630736E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53">
+        <f>Electricity!K55</f>
+        <v>78</v>
+      </c>
+      <c r="B53" s="64">
+        <f>Electricity!L55</f>
+        <v>2.2308809746954079</v>
+      </c>
+      <c r="E53">
+        <f>Compute!M73</f>
+        <v>58</v>
+      </c>
+      <c r="F53" s="64">
+        <f>Compute!Q73</f>
+        <v>5.972325298506479E-9</v>
+      </c>
+      <c r="G53">
+        <f>'DNA sequencing'!C57</f>
+        <v>13.831622176591509</v>
+      </c>
+      <c r="H53" s="64">
+        <f>'DNA sequencing'!J57</f>
+        <v>1.067710707139257E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54">
+        <f>Electricity!K56</f>
+        <v>79</v>
+      </c>
+      <c r="B54" s="64">
+        <f>Electricity!L56</f>
+        <v>2.2288350168350166</v>
+      </c>
+      <c r="E54">
+        <f>Compute!M74</f>
+        <v>59</v>
+      </c>
+      <c r="F54" s="64">
+        <f>Compute!Q74</f>
+        <v>3.7389767625103586E-9</v>
+      </c>
+      <c r="G54">
+        <f>'DNA sequencing'!C58</f>
+        <v>14.083504449007705</v>
+      </c>
+      <c r="H54" s="64">
+        <f>'DNA sequencing'!J58</f>
+        <v>9.7541058846892562E-4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55">
+        <f>Electricity!K57</f>
+        <v>80</v>
+      </c>
+      <c r="B55" s="64">
+        <f>Electricity!L57</f>
+        <v>2.2581252718573293</v>
+      </c>
+      <c r="E55">
+        <f>Compute!M75</f>
+        <v>60</v>
+      </c>
+      <c r="F55" s="64">
+        <f>Compute!Q75</f>
+        <v>3.7389767625103586E-9</v>
+      </c>
+      <c r="G55">
+        <f>'DNA sequencing'!C59</f>
+        <v>14.666666666666742</v>
+      </c>
+      <c r="H55" s="64">
+        <f>'DNA sequencing'!J59</f>
+        <v>9.12469670315097E-4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56">
+        <f>Electricity!K58</f>
+        <v>81</v>
+      </c>
+      <c r="B56" s="64">
+        <f>Electricity!L58</f>
+        <v>2.209443079443079</v>
+      </c>
+      <c r="E56">
+        <f>Compute!M76</f>
+        <v>61</v>
+      </c>
+      <c r="F56" s="64">
+        <f>Compute!Q76</f>
+        <v>1.0263365744072059E-9</v>
+      </c>
+      <c r="G56">
+        <f>'DNA sequencing'!C60</f>
+        <v>14.918548939082939</v>
+      </c>
+      <c r="H56" s="64">
+        <f>'DNA sequencing'!J60</f>
+        <v>1.1655187674886646E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G57">
+        <f>'DNA sequencing'!C61</f>
+        <v>15.167693360711837</v>
+      </c>
+      <c r="H57" s="64">
+        <f>'DNA sequencing'!J61</f>
+        <v>1.0417268640705677E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G58">
+        <f>'DNA sequencing'!C62</f>
+        <v>15.414099931553892</v>
+      </c>
+      <c r="H58" s="64">
+        <f>'DNA sequencing'!J62</f>
+        <v>7.7616015133699081E-4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G59">
+        <f>'DNA sequencing'!C63</f>
+        <v>15.665982203969861</v>
+      </c>
+      <c r="H59" s="64">
+        <f>'DNA sequencing'!J63</f>
+        <v>1.0181197746957041E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G60">
+        <f>'DNA sequencing'!C64</f>
+        <v>15.917864476386058</v>
+      </c>
+      <c r="H60" s="64">
+        <f>'DNA sequencing'!J64</f>
+        <v>8.5785382607503542E-4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G61">
+        <f>'DNA sequencing'!C65</f>
+        <v>16.167008898015183</v>
+      </c>
+      <c r="H61" s="64">
+        <f>'DNA sequencing'!J65</f>
+        <v>1.3873546008372642E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G62">
+        <f>'DNA sequencing'!C66</f>
+        <v>16.413415468857011</v>
+      </c>
+      <c r="H62" s="64">
+        <f>'DNA sequencing'!J66</f>
+        <v>9.2049523124533008E-4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G63">
+        <f>'DNA sequencing'!C67</f>
+        <v>16.665297741273207</v>
+      </c>
+      <c r="H63" s="64">
+        <f>'DNA sequencing'!J67</f>
+        <v>1.0866685918468429E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G64">
+        <f>'DNA sequencing'!C68</f>
+        <v>16.917180013689403</v>
+      </c>
+      <c r="H64" s="64">
+        <f>'DNA sequencing'!J68</f>
+        <v>1.0847204116506927E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="7:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G65">
+        <f>'DNA sequencing'!C69</f>
+        <v>17.166324435318302</v>
+      </c>
+      <c r="H65" s="64">
+        <f>'DNA sequencing'!J69</f>
+        <v>1.0264509761350724E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="7:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G66">
+        <f>'DNA sequencing'!C70</f>
+        <v>17.412731006160357</v>
+      </c>
+      <c r="H66" s="64">
+        <f>'DNA sequencing'!J70</f>
+        <v>7.2814851439087123E-4</v>
+      </c>
+    </row>
+    <row r="67" spans="7:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G67">
+        <f>'DNA sequencing'!C71</f>
+        <v>17.582477754962383</v>
+      </c>
+      <c r="H67" s="64">
+        <f>'DNA sequencing'!J71</f>
+        <v>4.4276553363266954E-4</v>
+      </c>
+    </row>
+    <row r="68" spans="7:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G68">
+        <f>'DNA sequencing'!C72</f>
+        <v>17.83436002737858</v>
+      </c>
+      <c r="H68" s="64">
+        <f>'DNA sequencing'!J72</f>
+        <v>6.8601844627310087E-4</v>
+      </c>
+    </row>
+    <row r="69" spans="7:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G69">
+        <f>'DNA sequencing'!C73</f>
+        <v>18.165639972621648</v>
+      </c>
+      <c r="H69" s="64">
+        <f>'DNA sequencing'!J73</f>
+        <v>5.012544478800742E-4</v>
+      </c>
+    </row>
+    <row r="70" spans="7:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G70">
+        <f>'DNA sequencing'!C74</f>
+        <v>18.412046543463475</v>
+      </c>
+      <c r="H70" s="64">
+        <f>'DNA sequencing'!J74</f>
+        <v>4.6566339492538819E-4</v>
+      </c>
+    </row>
+    <row r="71" spans="7:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G71">
+        <f>'DNA sequencing'!C75</f>
+        <v>18.666666666666742</v>
+      </c>
+      <c r="H71" s="64">
+        <f>'DNA sequencing'!J75</f>
+        <v>5.0883900051850264E-4</v>
+      </c>
+    </row>
+    <row r="72" spans="7:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G72">
+        <f>'DNA sequencing'!C76</f>
+        <v>18.918548939082939</v>
+      </c>
+      <c r="H72" s="64">
+        <f>'DNA sequencing'!J76</f>
+        <v>4.9373666442219515E-4</v>
+      </c>
+    </row>
+    <row r="73" spans="7:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G73">
+        <f>'DNA sequencing'!C77</f>
+        <v>19.167693360711837</v>
+      </c>
+      <c r="H73" s="64">
+        <f>'DNA sequencing'!J77</f>
+        <v>3.6423861203251415E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="7:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G74">
+        <f>'DNA sequencing'!C78</f>
+        <v>19.414099931553892</v>
+      </c>
+      <c r="H74" s="64">
+        <f>'DNA sequencing'!J78</f>
+        <v>5.9866651559596358E-4</v>
+      </c>
+    </row>
+    <row r="75" spans="7:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G75">
+        <f>'DNA sequencing'!C79</f>
+        <v>19.665982203969861</v>
+      </c>
+      <c r="H75" s="64">
+        <f>'DNA sequencing'!J79</f>
+        <v>3.1275476067508102E-4</v>
+      </c>
+    </row>
+    <row r="76" spans="7:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G76">
+        <f>'DNA sequencing'!C80</f>
+        <v>19.917864476386058</v>
+      </c>
+      <c r="H76" s="64">
+        <f>'DNA sequencing'!J80</f>
+        <v>3.826328938425051E-4</v>
+      </c>
+    </row>
+    <row r="77" spans="7:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G77">
+        <f>'DNA sequencing'!C81</f>
+        <v>20.167008898015183</v>
+      </c>
+      <c r="H77" s="64">
+        <f>'DNA sequencing'!J81</f>
+        <v>3.6656030166835174E-4</v>
+      </c>
+    </row>
+    <row r="78" spans="7:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G78">
+        <f>'DNA sequencing'!C82</f>
+        <v>20.413415468857011</v>
+      </c>
+      <c r="H78" s="64">
+        <f>'DNA sequencing'!J82</f>
+        <v>3.3999026951282637E-4</v>
+      </c>
+    </row>
+    <row r="79" spans="7:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G79">
+        <f>'DNA sequencing'!C83</f>
+        <v>20.665297741273207</v>
+      </c>
+      <c r="H79" s="64">
+        <f>'DNA sequencing'!J83</f>
+        <v>3.3159531996810655E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65F39435-1293-4532-BF1C-F08882A43A51}">
   <dimension ref="A2:U84"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -12440,7 +12472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{094EF588-3858-4344-9891-009C77F9B845}">
   <dimension ref="A1:F727"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -23108,7 +23140,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A1E150-5D3C-4060-9D35-F316CF230083}">
   <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -23905,7 +23937,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AF663FF-764A-441E-A8E1-1D0B75A36E50}">
   <dimension ref="A2:Q132"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -29249,7 +29281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC457D79-CBEF-4BF3-AAFF-8C16C054ECB4}">
   <dimension ref="A1:L84"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -32374,7 +32406,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AF3011C-5D8B-464B-B249-C7FD9E34C16D}">
   <dimension ref="A1:F956"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -43326,7 +43358,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B271B3C2-352A-4524-A08F-EC611C28ACD6}">
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>

--- a/data/Cost declines by tech.xlsx
+++ b/data/Cost declines by tech.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9a072a59b81ab8f9/Documents/Work/Clients ^0 prospects/EpochAI/inference-cost/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1316" documentId="8_{237EF59B-240D-4B45-BBDB-12EDD86E70D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B7EC316-1CE7-456E-B72F-1EEA9688E45C}"/>
+  <xr:revisionPtr revIDLastSave="1324" documentId="8_{237EF59B-240D-4B45-BBDB-12EDD86E70D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA248723-2279-4597-8CC5-F6815764A7EE}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" xr2:uid="{55FDA7DF-2265-4D1B-B569-857BE3FE3144}"/>
   </bookViews>
@@ -4582,7 +4582,7 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1321391791"/>
-        <c:crossesAt val="1.0000000000000005E-9"/>
+        <c:crossesAt val="1.0000000000000006E-11"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="10"/>
       </c:valAx>
@@ -4591,7 +4591,7 @@
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
-          <c:max val="105"/>
+          <c:max val="1.05"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -12654,12 +12654,12 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.70486</cdr:x>
-      <cdr:y>0.82299</cdr:y>
+      <cdr:x>0.69525</cdr:x>
+      <cdr:y>0.81717</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.84653</cdr:x>
-      <cdr:y>0.93534</cdr:y>
+      <cdr:x>0.83692</cdr:x>
+      <cdr:y>0.92952</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -12674,7 +12674,7 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4750679" y="3230718"/>
+          <a:off x="4685909" y="3207858"/>
           <a:ext cx="954840" cy="441038"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">

--- a/data/Cost declines by tech.xlsx
+++ b/data/Cost declines by tech.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9a072a59b81ab8f9/Documents/Work/Clients ^0 prospects/EpochAI/inference-cost/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1324" documentId="8_{237EF59B-240D-4B45-BBDB-12EDD86E70D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA248723-2279-4597-8CC5-F6815764A7EE}"/>
+  <xr:revisionPtr revIDLastSave="1387" documentId="8_{237EF59B-240D-4B45-BBDB-12EDD86E70D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E87920B7-1C79-45A1-86CD-01868BF66B5F}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" xr2:uid="{55FDA7DF-2265-4D1B-B569-857BE3FE3144}"/>
+    <workbookView xWindow="3138" yWindow="240" windowWidth="17280" windowHeight="10524" activeTab="1" xr2:uid="{55FDA7DF-2265-4D1B-B569-857BE3FE3144}"/>
   </bookViews>
   <sheets>
-    <sheet name="Table" sheetId="4" r:id="rId1"/>
-    <sheet name="Figure data" sheetId="9" r:id="rId2"/>
-    <sheet name="Electricity" sheetId="8" r:id="rId3"/>
-    <sheet name="Illumination" sheetId="6" r:id="rId4"/>
-    <sheet name="Lithium batteries" sheetId="5" r:id="rId5"/>
-    <sheet name="Compute" sheetId="7" r:id="rId6"/>
-    <sheet name="DNA sequencing" sheetId="1" r:id="rId7"/>
-    <sheet name="CPI" sheetId="3" r:id="rId8"/>
-    <sheet name="Sources" sheetId="2" r:id="rId9"/>
+    <sheet name="Chart1" sheetId="10" r:id="rId1"/>
+    <sheet name="Table" sheetId="4" r:id="rId2"/>
+    <sheet name="Figure data" sheetId="9" r:id="rId3"/>
+    <sheet name="Electricity" sheetId="8" r:id="rId4"/>
+    <sheet name="Illumination" sheetId="6" r:id="rId5"/>
+    <sheet name="Lithium batteries" sheetId="5" r:id="rId6"/>
+    <sheet name="Compute" sheetId="7" r:id="rId7"/>
+    <sheet name="DNA sequencing" sheetId="1" r:id="rId8"/>
+    <sheet name="CPI" sheetId="3" r:id="rId9"/>
+    <sheet name="Sources" sheetId="2" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Electricity!$A$6:$B$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Electricity!$A$6:$B$140</definedName>
     <definedName name="fn">'DNA sequencing'!$J$20</definedName>
     <definedName name="Year_span">'DNA sequencing'!$I$1</definedName>
   </definedNames>
@@ -2858,6 +2859,1875 @@
           <c:x val="9.4016404945968773E-2"/>
           <c:y val="6.0274498584973017E-2"/>
           <c:w val="0.86806932836467099"/>
+          <c:h val="0.83039405742350791"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>AI</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Figure data'!$M$3:$M$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1.6163586584530094</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.7829586584530261</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Figure data'!$N$3:$N$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1.6493911422653169E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.307518695827581E-6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-28D7-4073-BEF6-C7AC152E9096}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Compute</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Figure data'!$G$2:$G$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="55"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>61</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Figure data'!$H$2:$H$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="55"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.35115476038867788</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.8033172753900662E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.8033172753900662E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.8033172753900662E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.6382056926548551E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.6382056926548551E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.6382056926548551E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.7840715825846489E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.7840715825846489E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.7840715825846489E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.7840715825846489E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.1894462989462484E-3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.1894462989462484E-3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.9869035438097036E-4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.9869035438097036E-4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.9869035438097036E-4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.4230696120937078E-4</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.3078890527653685E-4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.3078890527653685E-4</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.3078890527653685E-4</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.4641876916147174E-5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.4641876916147174E-5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.4641876916147174E-5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.4641876916147174E-5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.3236862295869747E-5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.3236862295869747E-5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.3236862295869747E-5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.3236862295869747E-5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.3236862295869747E-5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.3236862295869747E-5</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.1618192756799012E-6</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7.2772030948188204E-7</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7.2772030948188204E-7</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7.2772030948188204E-7</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1.2546901887618653E-7</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.2546901887618653E-7</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.2546901887618653E-7</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1.2546901887618653E-7</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2.5093803775237309E-8</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2.5093803775237309E-8</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>4.7678227172950891E-9</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>4.7678227172950891E-9</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.5056282265142386E-9</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1.5056282265142386E-9</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>5.0187607550474615E-10</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2.5093803775237307E-10</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2.5093803775237307E-10</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2.5093803775237307E-10</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2.5093803775237307E-10</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>5.9723252985064788E-11</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>3.7389767625103589E-11</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>3.7389767625103589E-11</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.026336574407206E-11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-28D7-4073-BEF6-C7AC152E9096}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Lithium batteries</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Figure data'!$D$2:$D$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="34"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>33</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Figure data'!$E$2:$E$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="34"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.80216650398524247</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.63861393255108734</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.72902084964219138</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.68422648511492123</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.57629766031901486</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.49350477675367499</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.39704364603272668</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.30073870033647371</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.29213463724575828</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.20390688397575304</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.14609075994844864</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.11295786315868334</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.10107282119990488</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.7135380983971084E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.462309193147186E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.1207342270497048E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.4662293992658169E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.6510416135101946E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.9794450301458274E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.6958182368952774E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.8597070865765571E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.3298723267497128E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.7150820337820011E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.6040658050884723E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.8120904689676589E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.0303510335789657E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.7046262688336773E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.4331889648792702E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.3354715354556837E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.2920415668229785E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.4331889648792702E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.2051816295575682E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>8.468843883377505E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-28D7-4073-BEF6-C7AC152E9096}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>DNA sequencing</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Figure data'!$J$2:$J$79</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="78"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.49828884325802392</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.99931553730334599</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.4976043805613699</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.0835044490077053</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.3353867214236743</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.5817932922657292</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.8336755646816982</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.0855578370978947</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.3374401095140911</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.5811088295688478</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.8329911019850442</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.0848733744012407</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.3367556468174371</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.5804243668721938</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.8323066392881628</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.0841889117043593</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.3360711841205557</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.5797399041753124</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.8316221765915088</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.0835044490077053</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.3353867214236743</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.5817932922657292</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.8336755646816982</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7.0855578370978947</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.3374401095140911</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.5811088295688478</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>7.8329911019850442</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8.0848733744012407</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8.3367556468174371</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>8.5804243668721938</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>8.8323066392881628</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>9.0841889117043593</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>9.3360711841205557</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>9.5797399041753124</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>9.8316221765915088</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>10.080766598220407</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>10.335386721423674</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>10.581793292265729</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>10.833675564681698</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>11.085557837097895</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>11.337440109514091</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>11.581108829568848</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>11.832991101985044</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>12.084873374401241</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>12.336755646817437</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>12.580424366872194</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>12.832306639288163</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>13.084188911704359</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>13.336071184120556</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>13.579739904175312</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>13.831622176591509</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>14.083504449007705</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>14.666666666666742</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>14.918548939082939</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>15.167693360711837</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>15.414099931553892</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>15.665982203969861</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>15.917864476386058</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>16.167008898015183</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>16.413415468857011</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>16.665297741273207</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>16.917180013689403</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>17.166324435318302</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>17.412731006160357</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>17.582477754962383</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>17.83436002737858</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>18.165639972621648</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>18.412046543463475</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>18.666666666666742</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>18.918548939082939</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>19.167693360711837</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>19.414099931553892</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>19.665982203969861</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>19.917864476386058</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>20.167008898015183</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>20.413415468857011</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>20.665297741273207</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Figure data'!$K$2:$K$79</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="78"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.72966450166975194</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.63222391132945199</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.54699705192006998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.40468201668292464</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.2873892560087431</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.20250436288913715</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.1964261179806801</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.18010307127461045</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.16990976065198432</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.1556131540651009</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.15382443136010684</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.12988182068984197</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.1176709291497095</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.10865918549877641</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.10479033872157595</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>9.6672432806743716E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.5889241079984052E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.157688002031134E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.0144379342313013E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.320278748727777E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.6855959871058328E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.1720659796107069E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.411408344161644E-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.9956434297798685E-3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.0398733178367294E-3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.3540116803166067E-3</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>9.3512050058278519E-4</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6.0360355326899353E-4</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4.0133189210794686E-4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.7036791526076814E-4</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.662711554270181E-4</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.4698775629687983E-4</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.7612212416533382E-4</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.3859234684711133E-4</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>8.6550335982576426E-5</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>6.3548184017738271E-5</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>6.2594839264667776E-5</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>4.8103278850098872E-5</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>4.8527658871325301E-5</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>5.3356606328380226E-5</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>4.5390613351393476E-5</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>4.4621528929781469E-5</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>4.4322785484690122E-5</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>4.0583822454023445E-5</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3.172342788152098E-5</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3.8719458844008944E-5</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>3.8508215680075617E-5</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4.5084089040370574E-5</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3.1447903655264528E-5</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3.3123140454630736E-5</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1.0677107071392571E-5</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>9.7541058846892562E-6</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>9.1246967031509706E-6</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.1655187674886646E-5</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0417268640705677E-5</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>7.761601513369908E-6</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0181197746957041E-5</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>8.5785382607503547E-6</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.3873546008372642E-5</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>9.2049523124533013E-6</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.0866685918468429E-5</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.0847204116506927E-5</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1.0264509761350724E-5</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>7.2814851439087127E-6</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>4.4276553363266953E-6</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>6.8601844627310086E-6</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>5.0125444788007422E-6</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>4.6566339492538819E-6</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5.0883900051850262E-6</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>4.9373666442219515E-6</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>3.6423861203251413E-6</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>5.9866651559596355E-6</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>3.1275476067508102E-6</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>3.8263289384250511E-6</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>3.6656030166835175E-6</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>3.3999026951282636E-6</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>3.3159531996810656E-6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-28D7-4073-BEF6-C7AC152E9096}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>AI</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Figure data'!$M$2:$M$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.6163586584530094</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Figure data'!$N$2:$N$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.6493911422653169E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-28D7-4073-BEF6-C7AC152E9096}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>Electricity</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Figure data'!$A$2:$A$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="55"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>81</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Figure data'!$B$2:$B$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="55"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98103137396321638</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.77924442228328306</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.46036688553442084</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.38533537553467684</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.24215681818181811</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.1810655844155844</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.16300975860297892</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.16155632183908042</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.15981084529505579</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.15257958532695373</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.14882972237343495</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.15673755980861243</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.1687839416058394</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.1750187412587412</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.16394993215739484</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.1507321831453218</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.13848122956180506</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.12279583333333331</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.12102359767891679</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.11861347285807716</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.11305558441558441</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.10458763141620282</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>9.3056999442275495E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>8.5771939043615339E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>8.2202169421487573E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.8085555555555533E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6.8062843822843819E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5.7113982878108427E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5.1479969822708395E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5.1089763177998473E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4.9256582421727632E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>4.4547342657342649E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4.3084665523156082E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4.2298808307797066E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4.1218181818181814E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>4.0602985074626868E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3.9399732620320857E-2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3.7551083791653179E-2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3.6083737024221442E-2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3.541080912214932E-2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3.4394901719901713E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3.3774095469747648E-2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3.2892655027092113E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3.1923885918003561E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3.0714193548387093E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2.9441558441558432E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2.798765432098765E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2.6779477408818718E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2.5109926854754439E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2.3473024523160756E-2</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2.2308809746954081E-2</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2.2288350168350166E-2</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2.2581252718573294E-2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2.209443079443079E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-28D7-4073-BEF6-C7AC152E9096}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1131568655"/>
+        <c:axId val="1321391791"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1131568655"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+                    <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+                  </a:rPr>
+                  <a:t>Years since start of price decline</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+                <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1321391791"/>
+        <c:crossesAt val="1.0000000000000006E-11"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="30"/>
+        <c:minorUnit val="10"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1321391791"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+          <c:max val="1.05"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:noFill/>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1131568655"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+          <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:userShapes r:id="rId3"/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.4016404945968773E-2"/>
+          <c:y val="6.0274498584973017E-2"/>
+          <c:w val="0.86806932836467099"/>
           <c:h val="0.84656994233186922"/>
         </c:manualLayout>
       </c:layout>
@@ -4690,7 +6560,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6546,7 +8416,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -8401,7 +10271,1881 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10759408638075027"/>
+          <c:y val="6.0274498584973017E-2"/>
+          <c:w val="0.80018068006264997"/>
+          <c:h val="0.80056544945304653"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>AI</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Figure data'!$M$3:$M$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1.6163586584530094</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.7829586584530261</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Figure data'!$N$3:$N$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1.6493911422653169E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.307518695827581E-6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-358F-4399-8A8E-7CCC366A89F2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Compute</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Figure data'!$G$2:$G$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="55"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>61</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Figure data'!$H$2:$H$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="55"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.35115476038867788</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.8033172753900662E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.8033172753900662E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.8033172753900662E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.6382056926548551E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.6382056926548551E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.6382056926548551E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.7840715825846489E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.7840715825846489E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.7840715825846489E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.7840715825846489E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.1894462989462484E-3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.1894462989462484E-3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.9869035438097036E-4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.9869035438097036E-4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.9869035438097036E-4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.4230696120937078E-4</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.3078890527653685E-4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.3078890527653685E-4</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.3078890527653685E-4</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.4641876916147174E-5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.4641876916147174E-5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.4641876916147174E-5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.4641876916147174E-5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.3236862295869747E-5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.3236862295869747E-5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.3236862295869747E-5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.3236862295869747E-5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.3236862295869747E-5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.3236862295869747E-5</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.1618192756799012E-6</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7.2772030948188204E-7</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7.2772030948188204E-7</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7.2772030948188204E-7</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1.2546901887618653E-7</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.2546901887618653E-7</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.2546901887618653E-7</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1.2546901887618653E-7</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2.5093803775237309E-8</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2.5093803775237309E-8</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>4.7678227172950891E-9</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>4.7678227172950891E-9</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.5056282265142386E-9</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1.5056282265142386E-9</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>5.0187607550474615E-10</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2.5093803775237307E-10</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2.5093803775237307E-10</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2.5093803775237307E-10</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2.5093803775237307E-10</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>5.9723252985064788E-11</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>3.7389767625103589E-11</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>3.7389767625103589E-11</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.026336574407206E-11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-358F-4399-8A8E-7CCC366A89F2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Lithium batteries</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Figure data'!$D$2:$D$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="34"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>33</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Figure data'!$E$2:$E$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="34"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.80216650398524247</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.63861393255108734</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.72902084964219138</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.68422648511492123</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.57629766031901486</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.49350477675367499</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.39704364603272668</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.30073870033647371</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.29213463724575828</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.20390688397575304</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.14609075994844864</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.11295786315868334</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.10107282119990488</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.7135380983971084E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.462309193147186E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.1207342270497048E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.4662293992658169E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.6510416135101946E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.9794450301458274E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.6958182368952774E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.8597070865765571E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.3298723267497128E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.7150820337820011E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.6040658050884723E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.8120904689676589E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.0303510335789657E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.7046262688336773E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.4331889648792702E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.3354715354556837E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.2920415668229785E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.4331889648792702E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.2051816295575682E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>8.468843883377505E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-358F-4399-8A8E-7CCC366A89F2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>DNA sequencing</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Figure data'!$J$2:$J$79</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="78"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.49828884325802392</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.99931553730334599</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.4976043805613699</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.0835044490077053</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.3353867214236743</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.5817932922657292</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.8336755646816982</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.0855578370978947</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.3374401095140911</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.5811088295688478</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.8329911019850442</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.0848733744012407</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.3367556468174371</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.5804243668721938</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.8323066392881628</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.0841889117043593</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.3360711841205557</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.5797399041753124</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.8316221765915088</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.0835044490077053</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.3353867214236743</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.5817932922657292</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.8336755646816982</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7.0855578370978947</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.3374401095140911</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.5811088295688478</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>7.8329911019850442</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8.0848733744012407</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8.3367556468174371</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>8.5804243668721938</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>8.8323066392881628</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>9.0841889117043593</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>9.3360711841205557</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>9.5797399041753124</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>9.8316221765915088</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>10.080766598220407</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>10.335386721423674</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>10.581793292265729</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>10.833675564681698</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>11.085557837097895</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>11.337440109514091</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>11.581108829568848</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>11.832991101985044</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>12.084873374401241</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>12.336755646817437</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>12.580424366872194</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>12.832306639288163</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>13.084188911704359</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>13.336071184120556</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>13.579739904175312</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>13.831622176591509</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>14.083504449007705</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>14.666666666666742</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>14.918548939082939</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>15.167693360711837</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>15.414099931553892</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>15.665982203969861</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>15.917864476386058</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>16.167008898015183</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>16.413415468857011</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>16.665297741273207</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>16.917180013689403</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>17.166324435318302</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>17.412731006160357</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>17.582477754962383</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>17.83436002737858</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>18.165639972621648</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>18.412046543463475</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>18.666666666666742</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>18.918548939082939</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>19.167693360711837</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>19.414099931553892</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>19.665982203969861</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>19.917864476386058</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>20.167008898015183</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>20.413415468857011</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>20.665297741273207</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Figure data'!$K$2:$K$79</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="78"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.72966450166975194</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.63222391132945199</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.54699705192006998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.40468201668292464</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.2873892560087431</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.20250436288913715</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.1964261179806801</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.18010307127461045</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.16990976065198432</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.1556131540651009</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.15382443136010684</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.12988182068984197</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.1176709291497095</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.10865918549877641</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.10479033872157595</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>9.6672432806743716E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.5889241079984052E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.157688002031134E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.0144379342313013E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.320278748727777E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.6855959871058328E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.1720659796107069E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.411408344161644E-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.9956434297798685E-3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.0398733178367294E-3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.3540116803166067E-3</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>9.3512050058278519E-4</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6.0360355326899353E-4</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4.0133189210794686E-4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.7036791526076814E-4</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.662711554270181E-4</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.4698775629687983E-4</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.7612212416533382E-4</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.3859234684711133E-4</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>8.6550335982576426E-5</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>6.3548184017738271E-5</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>6.2594839264667776E-5</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>4.8103278850098872E-5</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>4.8527658871325301E-5</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>5.3356606328380226E-5</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>4.5390613351393476E-5</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>4.4621528929781469E-5</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>4.4322785484690122E-5</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>4.0583822454023445E-5</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3.172342788152098E-5</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3.8719458844008944E-5</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>3.8508215680075617E-5</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4.5084089040370574E-5</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3.1447903655264528E-5</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3.3123140454630736E-5</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1.0677107071392571E-5</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>9.7541058846892562E-6</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>9.1246967031509706E-6</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.1655187674886646E-5</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0417268640705677E-5</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>7.761601513369908E-6</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0181197746957041E-5</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>8.5785382607503547E-6</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.3873546008372642E-5</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>9.2049523124533013E-6</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.0866685918468429E-5</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.0847204116506927E-5</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1.0264509761350724E-5</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>7.2814851439087127E-6</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>4.4276553363266953E-6</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>6.8601844627310086E-6</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>5.0125444788007422E-6</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>4.6566339492538819E-6</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5.0883900051850262E-6</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>4.9373666442219515E-6</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>3.6423861203251413E-6</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>5.9866651559596355E-6</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>3.1275476067508102E-6</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>3.8263289384250511E-6</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>3.6656030166835175E-6</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>3.3999026951282636E-6</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>3.3159531996810656E-6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-358F-4399-8A8E-7CCC366A89F2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>AI</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Figure data'!$M$2:$M$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.6163586584530094</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Figure data'!$N$2:$N$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.6493911422653169E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-358F-4399-8A8E-7CCC366A89F2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>Electricity</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Figure data'!$A$2:$A$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="55"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>81</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Figure data'!$B$2:$B$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="55"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98103137396321638</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.77924442228328306</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.46036688553442084</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.38533537553467684</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.24215681818181811</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.1810655844155844</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.16300975860297892</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.16155632183908042</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.15981084529505579</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.15257958532695373</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.14882972237343495</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.15673755980861243</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.1687839416058394</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.1750187412587412</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.16394993215739484</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.1507321831453218</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.13848122956180506</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.12279583333333331</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.12102359767891679</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.11861347285807716</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.11305558441558441</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.10458763141620282</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>9.3056999442275495E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>8.5771939043615339E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>8.2202169421487573E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.8085555555555533E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6.8062843822843819E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5.7113982878108427E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5.1479969822708395E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5.1089763177998473E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4.9256582421727632E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>4.4547342657342649E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4.3084665523156082E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4.2298808307797066E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4.1218181818181814E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>4.0602985074626868E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3.9399732620320857E-2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3.7551083791653179E-2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3.6083737024221442E-2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3.541080912214932E-2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3.4394901719901713E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3.3774095469747648E-2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3.2892655027092113E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3.1923885918003561E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3.0714193548387093E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2.9441558441558432E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2.798765432098765E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2.6779477408818718E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2.5109926854754439E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2.3473024523160756E-2</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2.2308809746954081E-2</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2.2288350168350166E-2</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2.2581252718573294E-2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2.209443079443079E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-358F-4399-8A8E-7CCC366A89F2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1131568655"/>
+        <c:axId val="1321391791"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1131568655"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+                    <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+                  </a:rPr>
+                  <a:t>Years since start of price decline</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+                <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1321391791"/>
+        <c:crossesAt val="1.0000000000000006E-11"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="30"/>
+        <c:minorUnit val="10"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1321391791"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+          <c:max val="1.05"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:noFill/>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1131568655"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+          <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId3"/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -9079,6 +12823,86 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -11182,8 +15006,2033 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{B2ECE642-63CB-49BA-A3A9-08DA64A8BA4C}">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="8666825" cy="6292049"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0900A08B-AAD3-0CDF-DA80-ACFD86DA6F79}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.67193</cdr:x>
+      <cdr:y>0.81426</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.8136</cdr:x>
+      <cdr:y>0.92661</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D886207-E4F1-F019-14A4-3966205D2678}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="4500571" y="3196437"/>
+          <a:ext cx="948902" cy="441038"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>Compute</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1940–2001</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
+            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.387</cdr:x>
+      <cdr:y>0.1999</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.52868</cdr:x>
+      <cdr:y>0.2709</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="3" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A081233B-3C5D-69F2-6F98-E93F2A94B7BA}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="2592123" y="784726"/>
+          <a:ext cx="948970" cy="278716"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>Lithium</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>batteries</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1991–2024</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
+            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.26343</cdr:x>
+      <cdr:y>0.42808</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.40511</cdr:x>
+      <cdr:y>0.59199</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9E084F5-0B96-630A-2881-BBE3FCD7E1A1}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="1764462" y="1680456"/>
+          <a:ext cx="948970" cy="643440"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>DNA</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>sequencing,</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2001–22</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
+            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.13456</cdr:x>
+      <cdr:y>0.42957</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.19182</cdr:x>
+      <cdr:y>0.55779</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AE0DB7A-E029-B57F-9D5A-278C5057FA5B}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="901258" y="1686307"/>
+          <a:ext cx="383526" cy="503337"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>AI</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2021–26</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
+            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.8706</cdr:x>
+      <cdr:y>0.12194</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.99374</cdr:x>
+      <cdr:y>0.2462</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="7" name="TextBox 6">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89558BC0-E47B-44E8-15AA-1CD6C980C277}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5831231" y="478680"/>
+          <a:ext cx="824839" cy="487791"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>Electricity,</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>1892–1973</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.00796</cdr:x>
+      <cdr:y>0</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.08745</cdr:x>
+      <cdr:y>0.099</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E6EFF4C-E325-4C3A-AC7D-7A0F249A747B}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="53340" y="0"/>
+          <a:ext cx="532378" cy="388620"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>Starting</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>price</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.04601</cdr:x>
+      <cdr:y>0.1028</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.09846</cdr:x>
+      <cdr:y>0.17358</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="8" name="TextBox 7">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8660BA5-7038-65A7-9FF1-0F500B788276}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="308164" y="403555"/>
+          <a:ext cx="351309" cy="277852"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>10x fall</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.02446</cdr:x>
+      <cdr:y>0.17746</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.09556</cdr:x>
+      <cdr:y>0.25212</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="9" name="TextBox 8">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B7D3985-CC17-2DF7-E36A-C5B4D9537AAC}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="163830" y="696634"/>
+          <a:ext cx="476227" cy="293083"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>100x</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.0599</cdr:x>
+      <cdr:y>0.40353</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.0937</cdr:x>
+      <cdr:y>0.48983</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="10" name="TextBox 9">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E65FA36-95D4-E093-4095-D9E3AA41C5E3}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="401211" y="1584086"/>
+          <a:ext cx="226391" cy="338777"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.06063</cdr:x>
+      <cdr:y>0.24666</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.09443</cdr:x>
+      <cdr:y>0.3056</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="11" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0F0CBBC-B2A7-7545-154C-45F157FD73F0}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="406077" y="968271"/>
+          <a:ext cx="226391" cy="231374"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.05951</cdr:x>
+      <cdr:y>0.32509</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.09331</cdr:x>
+      <cdr:y>0.38403</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="13" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DAA3E2A-F391-FAF9-BA1C-34832F8F390A}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="398598" y="1276147"/>
+          <a:ext cx="226392" cy="231373"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>11430</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>316676</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>126087</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{053037C8-4D63-4185-A8E2-D675969691CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect l="1169" t="22272" r="2308"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22495378" y="762792"/>
+          <a:ext cx="6049934" cy="4123321"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
@@ -11216,7 +17065,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11254,7 +17103,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11292,16 +17141,807 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="16123920" y="544830"/>
+    <xdr:ext cx="5612130" cy="3406140"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5B9A8FE-1FC6-4D17-94CC-4A28BB5F6FBF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>312420</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>165636</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5836856D-DB24-4B6E-A798-C0D0D5A15D56}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30811470" y="1752600"/>
+          <a:ext cx="975360" cy="241836"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0"/>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>Lithium</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1200" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>batteries</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1200">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1991–2024</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1200" kern="1200">
+            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>38645</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>152796</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>478823</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>99652</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A72F1717-FA6E-1677-354F-A1BB54931C7A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="26352385" y="3814354"/>
+          <a:ext cx="1078477" cy="496090"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0"/>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>Compute</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1200">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1940–2001</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1200" kern="1200">
+            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>626324</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>80010</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>378674</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>49475</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF6DC70B-A323-D8F5-0653-B3A7D9000D92}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27578363" y="1361555"/>
+          <a:ext cx="1028947" cy="518699"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0"/>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>Electricity,</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1200" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>1892–1973</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>205740</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>64770</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>39230</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EE64856-9CA0-C094-1257-63DE401607E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23966285" y="2627861"/>
+          <a:ext cx="1070858" cy="706772"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0"/>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>DNA</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1200" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>sequencing,</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1200" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2001–22</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1200" kern="1200">
+            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>548640</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>72390</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>64325</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>143365</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3253CCA4-3179-D685-0854-FF8F47EBB584}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23032588" y="2635481"/>
+          <a:ext cx="792282" cy="437131"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0"/>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>AI</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1200">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2021–26</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1200" kern="1200">
+            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>89065</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>123702</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>436015</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>40041</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F865A73-C3AA-C017-DA5C-F1351AF6A2DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect l="1362" r="1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="28956000" y="672936"/>
+          <a:ext cx="6091638" cy="4127131"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
@@ -12208,7 +18848,7 @@
 </c:userShapes>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
@@ -12650,7 +19290,7 @@
 </c:userShapes>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
@@ -13092,7 +19732,914 @@
 </c:userShapes>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.65224</cdr:x>
+      <cdr:y>0.74379</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.79391</cdr:x>
+      <cdr:y>0.88926</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D886207-E4F1-F019-14A4-3966205D2678}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="3660469" y="2533454"/>
+          <a:ext cx="795070" cy="495496"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>Compute</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1940–2001</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
+            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.387</cdr:x>
+      <cdr:y>0.1999</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.52868</cdr:x>
+      <cdr:y>0.2709</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="3" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A081233B-3C5D-69F2-6F98-E93F2A94B7BA}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="2592123" y="784726"/>
+          <a:ext cx="948970" cy="278716"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>Lithium</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>batteries</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1991–2024</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
+            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.26343</cdr:x>
+      <cdr:y>0.42808</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.40511</cdr:x>
+      <cdr:y>0.63535</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9E084F5-0B96-630A-2881-BBE3FCD7E1A1}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="1478403" y="1458100"/>
+          <a:ext cx="795127" cy="705980"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>DNA</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>sequencing,</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2001–22</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
+            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.13456</cdr:x>
+      <cdr:y>0.42957</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.19182</cdr:x>
+      <cdr:y>0.55779</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AE0DB7A-E029-B57F-9D5A-278C5057FA5B}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="901258" y="1686307"/>
+          <a:ext cx="383526" cy="503337"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>AI</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2021–26</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
+            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.82308</cdr:x>
+      <cdr:y>0.11523</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.94622</cdr:x>
+      <cdr:y>0.26734</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="7" name="TextBox 6">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89558BC0-E47B-44E8-15AA-1CD6C980C277}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="4619220" y="392485"/>
+          <a:ext cx="691078" cy="518105"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>Electricity,</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>1892–1973</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.00796</cdr:x>
+      <cdr:y>0</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.08745</cdr:x>
+      <cdr:y>0.12528</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E6EFF4C-E325-4C3A-AC7D-7A0F249A747B}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="44673" y="0"/>
+          <a:ext cx="446108" cy="426720"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>Starting</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>price</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.04601</cdr:x>
+      <cdr:y>0.1028</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.09846</cdr:x>
+      <cdr:y>0.17358</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="8" name="TextBox 7">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8660BA5-7038-65A7-9FF1-0F500B788276}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="308164" y="403555"/>
+          <a:ext cx="351309" cy="277852"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>10x fall</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.02446</cdr:x>
+      <cdr:y>0.17746</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.09556</cdr:x>
+      <cdr:y>0.25212</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="9" name="TextBox 8">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B7D3985-CC17-2DF7-E36A-C5B4D9537AAC}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="163830" y="696634"/>
+          <a:ext cx="476227" cy="293083"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>100x</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.0599</cdr:x>
+      <cdr:y>0.40353</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.0937</cdr:x>
+      <cdr:y>0.48983</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="10" name="TextBox 9">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E65FA36-95D4-E093-4095-D9E3AA41C5E3}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="401211" y="1584086"/>
+          <a:ext cx="226391" cy="338777"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.06063</cdr:x>
+      <cdr:y>0.24666</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.09443</cdr:x>
+      <cdr:y>0.3056</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="11" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0F0CBBC-B2A7-7545-154C-45F157FD73F0}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="406077" y="968271"/>
+          <a:ext cx="226391" cy="231374"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.05951</cdr:x>
+      <cdr:y>0.32509</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.09331</cdr:x>
+      <cdr:y>0.38403</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="13" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DAA3E2A-F391-FAF9-BA1C-34832F8F390A}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="398598" y="1276147"/>
+          <a:ext cx="226392" cy="231373"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -13194,10 +20741,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13603,7 +21146,7 @@
     <col min="7" max="7" width="14.26171875" customWidth="1"/>
     <col min="8" max="8" width="6" customWidth="1"/>
     <col min="9" max="9" width="10.9453125" customWidth="1"/>
-    <col min="22" max="31" width="10.89453125" customWidth="1"/>
+    <col min="22" max="29" width="10.89453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="28.8" x14ac:dyDescent="0.55000000000000004">

--- a/data/Cost declines by tech.xlsx
+++ b/data/Cost declines by tech.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9a072a59b81ab8f9/Documents/Work/Clients ^0 prospects/EpochAI/inference-cost/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1387" documentId="8_{237EF59B-240D-4B45-BBDB-12EDD86E70D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E87920B7-1C79-45A1-86CD-01868BF66B5F}"/>
+  <xr:revisionPtr revIDLastSave="1390" documentId="8_{237EF59B-240D-4B45-BBDB-12EDD86E70D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1BBF066-C0FE-4E31-A20B-81B5F83AE3B0}"/>
   <bookViews>
-    <workbookView xWindow="3138" yWindow="240" windowWidth="17280" windowHeight="10524" activeTab="1" xr2:uid="{55FDA7DF-2265-4D1B-B569-857BE3FE3144}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" activeTab="1" xr2:uid="{55FDA7DF-2265-4D1B-B569-857BE3FE3144}"/>
   </bookViews>
   <sheets>
     <sheet name="Chart1" sheetId="10" r:id="rId1"/>
@@ -6379,8 +6379,8 @@
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
-                    <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                    <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                    <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+                    <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
@@ -6408,8 +6408,8 @@
                   <a:solidFill>
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
-                  <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
@@ -6443,8 +6443,8 @@
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+                <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
@@ -6500,8 +6500,8 @@
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+                <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
@@ -6544,8 +6544,8 @@
           <a:solidFill>
             <a:schemeClr val="tx1"/>
           </a:solidFill>
-          <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-          <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+          <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
         </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
@@ -6561,1862 +6561,6 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="1"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="9.4016404945968773E-2"/>
-          <c:y val="6.0274498584973017E-2"/>
-          <c:w val="0.86806932836467099"/>
-          <c:h val="0.84656994233186922"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="7"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>AI</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$M$3:$M$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>1.6163586584530094</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.7829586584530261</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$N$3:$N$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>1.6493911422653169E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.307518695827581E-6</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0A62-4DCA-9593-B1B89F2142F3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>Compute</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$G$2:$G$56</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>42</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>47</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>48</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>51</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>52</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>53</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>55</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>56</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>57</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>58</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>61</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$H$2:$H$56</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.35115476038867788</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7.8033172753900662E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.8033172753900662E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7.8033172753900662E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4.6382056926548551E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4.6382056926548551E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.6382056926548551E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>5.7840715825846489E-3</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5.7840715825846489E-3</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5.7840715825846489E-3</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>5.7840715825846489E-3</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.1894462989462484E-3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1.1894462989462484E-3</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>3.9869035438097036E-4</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>3.9869035438097036E-4</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>3.9869035438097036E-4</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1.4230696120937078E-4</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1.3078890527653685E-4</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1.3078890527653685E-4</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1.3078890527653685E-4</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>4.4641876916147174E-5</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>4.4641876916147174E-5</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>4.4641876916147174E-5</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>4.4641876916147174E-5</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>3.1618192756799012E-6</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>7.2772030948188204E-7</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>7.2772030948188204E-7</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>7.2772030948188204E-7</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1.2546901887618653E-7</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1.2546901887618653E-7</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1.2546901887618653E-7</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1.2546901887618653E-7</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>2.5093803775237309E-8</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2.5093803775237309E-8</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>4.7678227172950891E-9</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>4.7678227172950891E-9</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1.5056282265142386E-9</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1.5056282265142386E-9</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>5.0187607550474615E-10</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>2.5093803775237307E-10</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>2.5093803775237307E-10</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>2.5093803775237307E-10</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>2.5093803775237307E-10</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>5.9723252985064788E-11</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>3.7389767625103589E-11</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>3.7389767625103589E-11</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1.026336574407206E-11</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0A62-4DCA-9593-B1B89F2142F3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:v>Lithium batteries</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$D$2:$D$35</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>33</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$E$2:$E$35</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.80216650398524247</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.63861393255108734</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.72902084964219138</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.68422648511492123</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.57629766031901486</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.49350477675367499</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.39704364603272668</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.30073870033647371</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.29213463724575828</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.20390688397575304</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.14609075994844864</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.11295786315868334</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.10107282119990488</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>8.7135380983971084E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>7.462309193147186E-2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>7.1207342270497048E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>7.4662293992658169E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>6.6510416135101946E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>5.9794450301458274E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>5.6958182368952774E-2</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>5.8597070865765571E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>5.3298723267497128E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>4.7150820337820011E-2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>3.6040658050884723E-2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>2.8120904689676589E-2</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2.0303510335789657E-2</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1.7046262688336773E-2</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1.4331889648792702E-2</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1.3354715354556837E-2</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>1.2920415668229785E-2</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1.4331889648792702E-2</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1.2051816295575682E-2</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>8.468843883377505E-3</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-0A62-4DCA-9593-B1B89F2142F3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:v>DNA sequencing</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$J$2:$J$79</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="78"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.49828884325802392</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.99931553730334599</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.4976043805613699</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.0835044490077053</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2.3353867214236743</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2.5817932922657292</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.8336755646816982</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3.0855578370978947</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.3374401095140911</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>3.5811088295688478</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>3.8329911019850442</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4.0848733744012407</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>4.3367556468174371</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4.5804243668721938</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>4.8323066392881628</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>5.0841889117043593</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>5.3360711841205557</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>5.5797399041753124</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>5.8316221765915088</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>6.0835044490077053</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>6.3353867214236743</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>6.5817932922657292</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>6.8336755646816982</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>7.0855578370978947</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>7.3374401095140911</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>7.5811088295688478</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>7.8329911019850442</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>8.0848733744012407</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>8.3367556468174371</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>8.5804243668721938</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>8.8323066392881628</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>9.0841889117043593</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>9.3360711841205557</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>9.5797399041753124</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>9.8316221765915088</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>10.080766598220407</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>10.335386721423674</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>10.581793292265729</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>10.833675564681698</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>11.085557837097895</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>11.337440109514091</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>11.581108829568848</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>11.832991101985044</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>12.084873374401241</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>12.336755646817437</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>12.580424366872194</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>12.832306639288163</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>13.084188911704359</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>13.336071184120556</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>13.579739904175312</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>13.831622176591509</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>14.083504449007705</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>14.666666666666742</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>14.918548939082939</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>15.167693360711837</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>15.414099931553892</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>15.665982203969861</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>15.917864476386058</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>16.167008898015183</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>16.413415468857011</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>16.665297741273207</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>16.917180013689403</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>17.166324435318302</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>17.412731006160357</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>17.582477754962383</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>17.83436002737858</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>18.165639972621648</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>18.412046543463475</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>18.666666666666742</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>18.918548939082939</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>19.167693360711837</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>19.414099931553892</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>19.665982203969861</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>19.917864476386058</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>20.167008898015183</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>20.413415468857011</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>20.665297741273207</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$K$2:$K$79</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="78"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.72966450166975194</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.63222391132945199</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.54699705192006998</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.40468201668292464</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.2873892560087431</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.20250436288913715</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.1964261179806801</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.18010307127461045</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.16990976065198432</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.1556131540651009</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.15382443136010684</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.12988182068984197</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.1176709291497095</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.10865918549877641</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.10479033872157595</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>9.6672432806743716E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>8.5889241079984052E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>8.157688002031134E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>8.0144379342313013E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>6.320278748727777E-2</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>2.6855959871058328E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1.1720659796107069E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>6.411408344161644E-3</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>2.9956434297798685E-3</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>2.0398733178367294E-3</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1.3540116803166067E-3</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>9.3512050058278519E-4</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>6.0360355326899353E-4</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>4.0133189210794686E-4</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>2.7036791526076814E-4</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>2.662711554270181E-4</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>2.4698775629687983E-4</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1.7612212416533382E-4</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1.3859234684711133E-4</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>8.6550335982576426E-5</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>6.3548184017738271E-5</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>6.2594839264667776E-5</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>4.8103278850098872E-5</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>4.8527658871325301E-5</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>5.3356606328380226E-5</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>4.5390613351393476E-5</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>4.4621528929781469E-5</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>4.4322785484690122E-5</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>4.0583822454023445E-5</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>3.172342788152098E-5</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>3.8719458844008944E-5</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>3.8508215680075617E-5</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>4.5084089040370574E-5</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>3.1447903655264528E-5</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>3.3123140454630736E-5</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>1.0677107071392571E-5</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>9.7541058846892562E-6</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>9.1246967031509706E-6</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1.1655187674886646E-5</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>1.0417268640705677E-5</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>7.761601513369908E-6</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>1.0181197746957041E-5</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>8.5785382607503547E-6</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>1.3873546008372642E-5</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>9.2049523124533013E-6</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>1.0866685918468429E-5</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>1.0847204116506927E-5</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>1.0264509761350724E-5</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>7.2814851439087127E-6</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>4.4276553363266953E-6</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>6.8601844627310086E-6</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>5.0125444788007422E-6</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>4.6566339492538819E-6</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>5.0883900051850262E-6</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>4.9373666442219515E-6</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>3.6423861203251413E-6</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>5.9866651559596355E-6</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>3.1275476067508102E-6</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>3.8263289384250511E-6</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>3.6656030166835175E-6</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>3.3999026951282636E-6</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>3.3159531996810656E-6</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-0A62-4DCA-9593-B1B89F2142F3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:v>AI</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$M$2:$M$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.6163586584530094</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$N$2:$N$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.6493911422653169E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-0A62-4DCA-9593-B1B89F2142F3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:v>Electricity</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$A$2:$A$56</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>34</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>39</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>41</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>42</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>47</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>48</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>49</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>51</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>52</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>53</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>55</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>56</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>57</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>58</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>61</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>62</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>63</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>66</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>67</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>68</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>71</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>72</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>73</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>74</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>76</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>77</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>79</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>81</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$B$2:$B$56</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.98103137396321638</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.77924442228328306</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.46036688553442084</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.38533537553467684</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.24215681818181811</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.1810655844155844</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.16300975860297892</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.16155632183908042</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.15981084529505579</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.15257958532695373</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.14882972237343495</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.15673755980861243</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.1687839416058394</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.1750187412587412</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.16394993215739484</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.1507321831453218</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.13848122956180506</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.12279583333333331</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.12102359767891679</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.11861347285807716</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.11305558441558441</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.10458763141620282</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>9.3056999442275495E-2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>8.5771939043615339E-2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>8.2202169421487573E-2</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>7.8085555555555533E-2</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>6.8062843822843819E-2</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>5.7113982878108427E-2</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>5.1479969822708395E-2</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>5.1089763177998473E-2</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>4.9256582421727632E-2</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>4.4547342657342649E-2</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>4.3084665523156082E-2</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>4.2298808307797066E-2</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>4.1218181818181814E-2</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>4.0602985074626868E-2</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>3.9399732620320857E-2</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>3.7551083791653179E-2</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>3.6083737024221442E-2</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>3.541080912214932E-2</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>3.4394901719901713E-2</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>3.3774095469747648E-2</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>3.2892655027092113E-2</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>3.1923885918003561E-2</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>3.0714193548387093E-2</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>2.9441558441558432E-2</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>2.798765432098765E-2</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>2.6779477408818718E-2</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>2.5109926854754439E-2</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>2.3473024523160756E-2</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>2.2308809746954081E-2</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>2.2288350168350166E-2</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>2.2581252718573294E-2</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>2.209443079443079E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-0A62-4DCA-9593-B1B89F2142F3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1131568655"/>
-        <c:axId val="1321391791"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1131568655"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                    <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Years</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1321391791"/>
-        <c:crossesAt val="1.0000000000000006E-11"/>
-        <c:crossBetween val="midCat"/>
-        <c:majorUnit val="10"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1321391791"/>
-        <c:scaling>
-          <c:logBase val="10"/>
-          <c:orientation val="minMax"/>
-          <c:max val="1.05"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.################" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:noFill/>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1131568655"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="25400">
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:noFill/>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr sz="1100">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-          <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-        </a:defRPr>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:userShapes r:id="rId3"/>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -10271,1881 +8415,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="1"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.10759408638075027"/>
-          <c:y val="6.0274498584973017E-2"/>
-          <c:w val="0.80018068006264997"/>
-          <c:h val="0.80056544945304653"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="7"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>AI</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$M$3:$M$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>1.6163586584530094</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.7829586584530261</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$N$3:$N$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>1.6493911422653169E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.307518695827581E-6</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-358F-4399-8A8E-7CCC366A89F2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>Compute</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$G$2:$G$56</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>42</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>47</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>48</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>51</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>52</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>53</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>55</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>56</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>57</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>58</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>61</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$H$2:$H$56</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.35115476038867788</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7.8033172753900662E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.8033172753900662E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7.8033172753900662E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4.6382056926548551E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4.6382056926548551E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.6382056926548551E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>5.7840715825846489E-3</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5.7840715825846489E-3</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5.7840715825846489E-3</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>5.7840715825846489E-3</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.1894462989462484E-3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1.1894462989462484E-3</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>3.9869035438097036E-4</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>3.9869035438097036E-4</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>3.9869035438097036E-4</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1.4230696120937078E-4</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1.3078890527653685E-4</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1.3078890527653685E-4</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1.3078890527653685E-4</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>4.4641876916147174E-5</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>4.4641876916147174E-5</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>4.4641876916147174E-5</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>4.4641876916147174E-5</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>3.1618192756799012E-6</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>7.2772030948188204E-7</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>7.2772030948188204E-7</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>7.2772030948188204E-7</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1.2546901887618653E-7</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1.2546901887618653E-7</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1.2546901887618653E-7</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1.2546901887618653E-7</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>2.5093803775237309E-8</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2.5093803775237309E-8</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>4.7678227172950891E-9</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>4.7678227172950891E-9</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1.5056282265142386E-9</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1.5056282265142386E-9</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>5.0187607550474615E-10</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>2.5093803775237307E-10</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>2.5093803775237307E-10</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>2.5093803775237307E-10</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>2.5093803775237307E-10</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>5.9723252985064788E-11</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>3.7389767625103589E-11</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>3.7389767625103589E-11</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1.026336574407206E-11</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-358F-4399-8A8E-7CCC366A89F2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:v>Lithium batteries</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$D$2:$D$35</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>33</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$E$2:$E$35</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.80216650398524247</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.63861393255108734</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.72902084964219138</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.68422648511492123</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.57629766031901486</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.49350477675367499</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.39704364603272668</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.30073870033647371</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.29213463724575828</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.20390688397575304</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.14609075994844864</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.11295786315868334</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.10107282119990488</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>8.7135380983971084E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>7.462309193147186E-2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>7.1207342270497048E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>7.4662293992658169E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>6.6510416135101946E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>5.9794450301458274E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>5.6958182368952774E-2</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>5.8597070865765571E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>5.3298723267497128E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>4.7150820337820011E-2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>3.6040658050884723E-2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>2.8120904689676589E-2</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2.0303510335789657E-2</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1.7046262688336773E-2</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1.4331889648792702E-2</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1.3354715354556837E-2</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>1.2920415668229785E-2</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1.4331889648792702E-2</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1.2051816295575682E-2</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>8.468843883377505E-3</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-358F-4399-8A8E-7CCC366A89F2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:v>DNA sequencing</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$J$2:$J$79</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="78"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.49828884325802392</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.99931553730334599</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.4976043805613699</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.0835044490077053</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2.3353867214236743</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2.5817932922657292</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.8336755646816982</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3.0855578370978947</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.3374401095140911</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>3.5811088295688478</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>3.8329911019850442</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4.0848733744012407</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>4.3367556468174371</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4.5804243668721938</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>4.8323066392881628</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>5.0841889117043593</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>5.3360711841205557</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>5.5797399041753124</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>5.8316221765915088</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>6.0835044490077053</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>6.3353867214236743</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>6.5817932922657292</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>6.8336755646816982</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>7.0855578370978947</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>7.3374401095140911</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>7.5811088295688478</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>7.8329911019850442</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>8.0848733744012407</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>8.3367556468174371</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>8.5804243668721938</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>8.8323066392881628</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>9.0841889117043593</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>9.3360711841205557</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>9.5797399041753124</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>9.8316221765915088</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>10.080766598220407</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>10.335386721423674</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>10.581793292265729</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>10.833675564681698</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>11.085557837097895</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>11.337440109514091</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>11.581108829568848</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>11.832991101985044</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>12.084873374401241</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>12.336755646817437</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>12.580424366872194</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>12.832306639288163</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>13.084188911704359</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>13.336071184120556</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>13.579739904175312</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>13.831622176591509</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>14.083504449007705</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>14.666666666666742</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>14.918548939082939</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>15.167693360711837</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>15.414099931553892</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>15.665982203969861</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>15.917864476386058</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>16.167008898015183</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>16.413415468857011</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>16.665297741273207</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>16.917180013689403</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>17.166324435318302</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>17.412731006160357</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>17.582477754962383</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>17.83436002737858</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>18.165639972621648</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>18.412046543463475</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>18.666666666666742</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>18.918548939082939</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>19.167693360711837</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>19.414099931553892</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>19.665982203969861</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>19.917864476386058</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>20.167008898015183</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>20.413415468857011</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>20.665297741273207</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$K$2:$K$79</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="78"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.72966450166975194</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.63222391132945199</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.54699705192006998</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.40468201668292464</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.2873892560087431</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.20250436288913715</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.1964261179806801</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.18010307127461045</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.16990976065198432</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.1556131540651009</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.15382443136010684</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.12988182068984197</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.1176709291497095</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.10865918549877641</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.10479033872157595</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>9.6672432806743716E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>8.5889241079984052E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>8.157688002031134E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>8.0144379342313013E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>6.320278748727777E-2</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>2.6855959871058328E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1.1720659796107069E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>6.411408344161644E-3</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>2.9956434297798685E-3</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>2.0398733178367294E-3</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1.3540116803166067E-3</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>9.3512050058278519E-4</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>6.0360355326899353E-4</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>4.0133189210794686E-4</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>2.7036791526076814E-4</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>2.662711554270181E-4</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>2.4698775629687983E-4</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1.7612212416533382E-4</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1.3859234684711133E-4</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>8.6550335982576426E-5</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>6.3548184017738271E-5</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>6.2594839264667776E-5</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>4.8103278850098872E-5</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>4.8527658871325301E-5</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>5.3356606328380226E-5</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>4.5390613351393476E-5</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>4.4621528929781469E-5</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>4.4322785484690122E-5</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>4.0583822454023445E-5</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>3.172342788152098E-5</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>3.8719458844008944E-5</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>3.8508215680075617E-5</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>4.5084089040370574E-5</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>3.1447903655264528E-5</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>3.3123140454630736E-5</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>1.0677107071392571E-5</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>9.7541058846892562E-6</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>9.1246967031509706E-6</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1.1655187674886646E-5</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>1.0417268640705677E-5</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>7.761601513369908E-6</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>1.0181197746957041E-5</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>8.5785382607503547E-6</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>1.3873546008372642E-5</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>9.2049523124533013E-6</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>1.0866685918468429E-5</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>1.0847204116506927E-5</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>1.0264509761350724E-5</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>7.2814851439087127E-6</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>4.4276553363266953E-6</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>6.8601844627310086E-6</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>5.0125444788007422E-6</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>4.6566339492538819E-6</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>5.0883900051850262E-6</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>4.9373666442219515E-6</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>3.6423861203251413E-6</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>5.9866651559596355E-6</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>3.1275476067508102E-6</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>3.8263289384250511E-6</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>3.6656030166835175E-6</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>3.3999026951282636E-6</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>3.3159531996810656E-6</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-358F-4399-8A8E-7CCC366A89F2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:v>AI</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$M$2:$M$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.6163586584530094</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$N$2:$N$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.6493911422653169E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-358F-4399-8A8E-7CCC366A89F2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:v>Electricity</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$A$2:$A$56</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>34</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>39</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>41</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>42</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>47</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>48</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>49</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>51</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>52</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>53</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>55</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>56</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>57</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>58</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>61</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>62</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>63</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>66</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>67</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>68</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>71</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>72</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>73</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>74</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>76</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>77</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>79</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>81</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$B$2:$B$56</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.98103137396321638</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.77924442228328306</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.46036688553442084</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.38533537553467684</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.24215681818181811</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.1810655844155844</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.16300975860297892</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.16155632183908042</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.15981084529505579</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.15257958532695373</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.14882972237343495</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.15673755980861243</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.1687839416058394</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.1750187412587412</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.16394993215739484</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.1507321831453218</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.13848122956180506</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.12279583333333331</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.12102359767891679</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.11861347285807716</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.11305558441558441</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.10458763141620282</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>9.3056999442275495E-2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>8.5771939043615339E-2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>8.2202169421487573E-2</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>7.8085555555555533E-2</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>6.8062843822843819E-2</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>5.7113982878108427E-2</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>5.1479969822708395E-2</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>5.1089763177998473E-2</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>4.9256582421727632E-2</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>4.4547342657342649E-2</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>4.3084665523156082E-2</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>4.2298808307797066E-2</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>4.1218181818181814E-2</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>4.0602985074626868E-2</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>3.9399732620320857E-2</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>3.7551083791653179E-2</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>3.6083737024221442E-2</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>3.541080912214932E-2</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>3.4394901719901713E-2</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>3.3774095469747648E-2</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>3.2892655027092113E-2</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>3.1923885918003561E-2</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>3.0714193548387093E-2</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>2.9441558441558432E-2</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>2.798765432098765E-2</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>2.6779477408818718E-2</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>2.5109926854754439E-2</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>2.3473024523160756E-2</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>2.2308809746954081E-2</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>2.2288350168350166E-2</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>2.2581252718573294E-2</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>2.209443079443079E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-358F-4399-8A8E-7CCC366A89F2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1131568655"/>
-        <c:axId val="1321391791"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1131568655"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                    <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US">
-                    <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-                    <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-                  </a:rPr>
-                  <a:t>Years since start of price decline</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-                <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1321391791"/>
-        <c:crossesAt val="1.0000000000000006E-11"/>
-        <c:crossBetween val="midCat"/>
-        <c:majorUnit val="30"/>
-        <c:minorUnit val="10"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1321391791"/>
-        <c:scaling>
-          <c:logBase val="10"/>
-          <c:orientation val="minMax"/>
-          <c:max val="1.05"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:noFill/>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1131568655"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="25400">
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:noFill/>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr sz="1100">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-          <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-        </a:defRPr>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:userShapes r:id="rId3"/>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -12823,86 +9093,6 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -15006,1038 +11196,6 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{B2ECE642-63CB-49BA-A3A9-08DA64A8BA4C}">
   <sheetPr/>
@@ -17074,44 +12232,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>87630</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>172720</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78FCC3B4-B8EF-43C4-B472-E2F6B8CF2CA3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>47</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -17141,40 +12261,12 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="16123920" y="544830"/>
-    <xdr:ext cx="5612130" cy="3406140"/>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5B9A8FE-1FC6-4D17-94CC-4A28BB5F6FBF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks noGrp="1"/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>33</xdr:col>
@@ -18872,448 +13964,6 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4656784" y="3207865"/>
-          <a:ext cx="948903" cy="441037"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>Compute</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>,</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>1940–2001</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
-            <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.42625</cdr:x>
-      <cdr:y>0.20378</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.56793</cdr:x>
-      <cdr:y>0.27478</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="3" name="TextBox 1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A081233B-3C5D-69F2-6F98-E93F2A94B7BA}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="2855008" y="799961"/>
-          <a:ext cx="948970" cy="278716"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:lvl1pPr marL="0" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>Lithium</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>batteries</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>,</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>1991–2024</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
-            <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.30495</cdr:x>
-      <cdr:y>0.43002</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.44663</cdr:x>
-      <cdr:y>0.59393</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="5" name="TextBox 4">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9E084F5-0B96-630A-2881-BBE3FCD7E1A1}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="2042579" y="1688078"/>
-          <a:ext cx="948970" cy="643440"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>DNA</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>sequencing,</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>2001–22</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
-            <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.18746</cdr:x>
-      <cdr:y>0.43151</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.24472</cdr:x>
-      <cdr:y>0.55973</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="6" name="TextBox 5">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AE0DB7A-E029-B57F-9D5A-278C5057FA5B}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1255610" y="1693927"/>
-          <a:ext cx="383527" cy="503337"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>AI</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>,</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>2021–26</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
-            <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.87827</cdr:x>
-      <cdr:y>0.12194</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.99374</cdr:x>
-      <cdr:y>0.2462</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="7" name="TextBox 6">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89558BC0-E47B-44E8-15AA-1CD6C980C277}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5882639" y="478684"/>
-          <a:ext cx="773411" cy="487791"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>Electricity,</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>1892–1973</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-</c:userShapes>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.69525</cdr:x>
-      <cdr:y>0.81717</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.83692</cdr:x>
-      <cdr:y>0.92952</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="2" name="TextBox 1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D886207-E4F1-F019-14A4-3966205D2678}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4685909" y="3207858"/>
           <a:ext cx="954840" cy="441038"/>
         </a:xfrm>
@@ -19732,914 +14382,7 @@
 </c:userShapes>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.65224</cdr:x>
-      <cdr:y>0.74379</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.79391</cdr:x>
-      <cdr:y>0.88926</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="2" name="TextBox 1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D886207-E4F1-F019-14A4-3966205D2678}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3660469" y="2533454"/>
-          <a:ext cx="795070" cy="495496"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>Compute</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>,</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>1940–2001</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
-            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.387</cdr:x>
-      <cdr:y>0.1999</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.52868</cdr:x>
-      <cdr:y>0.2709</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="3" name="TextBox 1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A081233B-3C5D-69F2-6F98-E93F2A94B7BA}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="2592123" y="784726"/>
-          <a:ext cx="948970" cy="278716"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:lvl1pPr marL="0" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>Lithium</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>batteries</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>,</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>1991–2024</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
-            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.26343</cdr:x>
-      <cdr:y>0.42808</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.40511</cdr:x>
-      <cdr:y>0.63535</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="5" name="TextBox 4">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9E084F5-0B96-630A-2881-BBE3FCD7E1A1}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1478403" y="1458100"/>
-          <a:ext cx="795127" cy="705980"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>DNA</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>sequencing,</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>2001–22</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
-            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.13456</cdr:x>
-      <cdr:y>0.42957</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.19182</cdr:x>
-      <cdr:y>0.55779</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="6" name="TextBox 5">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AE0DB7A-E029-B57F-9D5A-278C5057FA5B}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="901258" y="1686307"/>
-          <a:ext cx="383526" cy="503337"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>AI</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>,</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>2021–26</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
-            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.82308</cdr:x>
-      <cdr:y>0.11523</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.94622</cdr:x>
-      <cdr:y>0.26734</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="7" name="TextBox 6">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89558BC0-E47B-44E8-15AA-1CD6C980C277}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4619220" y="392485"/>
-          <a:ext cx="691078" cy="518105"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>Electricity,</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>1892–1973</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.00796</cdr:x>
-      <cdr:y>0</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.08745</cdr:x>
-      <cdr:y>0.12528</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="4" name="TextBox 3">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E6EFF4C-E325-4C3A-AC7D-7A0F249A747B}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="44673" y="0"/>
-          <a:ext cx="446108" cy="426720"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>Starting</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>price</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.04601</cdr:x>
-      <cdr:y>0.1028</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.09846</cdr:x>
-      <cdr:y>0.17358</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="8" name="TextBox 7">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8660BA5-7038-65A7-9FF1-0F500B788276}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="308164" y="403555"/>
-          <a:ext cx="351309" cy="277852"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>10x fall</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.02446</cdr:x>
-      <cdr:y>0.17746</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.09556</cdr:x>
-      <cdr:y>0.25212</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="9" name="TextBox 8">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B7D3985-CC17-2DF7-E36A-C5B4D9537AAC}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="163830" y="696634"/>
-          <a:ext cx="476227" cy="293083"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>100x</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.0599</cdr:x>
-      <cdr:y>0.40353</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.0937</cdr:x>
-      <cdr:y>0.48983</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="10" name="TextBox 9">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E65FA36-95D4-E093-4095-D9E3AA41C5E3}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="401211" y="1584086"/>
-          <a:ext cx="226391" cy="338777"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.06063</cdr:x>
-      <cdr:y>0.24666</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.09443</cdr:x>
-      <cdr:y>0.3056</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="11" name="TextBox 1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0F0CBBC-B2A7-7545-154C-45F157FD73F0}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="406077" y="968271"/>
-          <a:ext cx="226391" cy="231374"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:lvl1pPr marL="0" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.05951</cdr:x>
-      <cdr:y>0.32509</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.09331</cdr:x>
-      <cdr:y>0.38403</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="13" name="TextBox 1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DAA3E2A-F391-FAF9-BA1C-34832F8F390A}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="398598" y="1276147"/>
-          <a:ext cx="226392" cy="231373"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:lvl1pPr marL="0" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-</c:userShapes>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>

--- a/data/Cost declines by tech.xlsx
+++ b/data/Cost declines by tech.xlsx
@@ -8,24 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9a072a59b81ab8f9/Documents/Work/Clients ^0 prospects/EpochAI/inference-cost/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1390" documentId="8_{237EF59B-240D-4B45-BBDB-12EDD86E70D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1BBF066-C0FE-4E31-A20B-81B5F83AE3B0}"/>
+  <xr:revisionPtr revIDLastSave="1440" documentId="8_{237EF59B-240D-4B45-BBDB-12EDD86E70D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D9B9F86-9EF2-40D1-AB39-4F0EB1DD6042}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" activeTab="1" xr2:uid="{55FDA7DF-2265-4D1B-B569-857BE3FE3144}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" xr2:uid="{55FDA7DF-2265-4D1B-B569-857BE3FE3144}"/>
   </bookViews>
   <sheets>
-    <sheet name="Chart1" sheetId="10" r:id="rId1"/>
-    <sheet name="Table" sheetId="4" r:id="rId2"/>
-    <sheet name="Figure data" sheetId="9" r:id="rId3"/>
-    <sheet name="Electricity" sheetId="8" r:id="rId4"/>
-    <sheet name="Illumination" sheetId="6" r:id="rId5"/>
-    <sheet name="Lithium batteries" sheetId="5" r:id="rId6"/>
-    <sheet name="Compute" sheetId="7" r:id="rId7"/>
-    <sheet name="DNA sequencing" sheetId="1" r:id="rId8"/>
-    <sheet name="CPI" sheetId="3" r:id="rId9"/>
-    <sheet name="Sources" sheetId="2" r:id="rId10"/>
+    <sheet name="Figure" sheetId="4" r:id="rId1"/>
+    <sheet name="Figure data" sheetId="9" r:id="rId2"/>
+    <sheet name="Electricity" sheetId="8" r:id="rId3"/>
+    <sheet name="Illumination" sheetId="6" r:id="rId4"/>
+    <sheet name="Lithium batteries" sheetId="5" r:id="rId5"/>
+    <sheet name="Compute" sheetId="7" r:id="rId6"/>
+    <sheet name="DNA sequencing" sheetId="1" r:id="rId7"/>
+    <sheet name="CPI" sheetId="3" r:id="rId8"/>
+    <sheet name="Sources" sheetId="2" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Electricity!$A$6:$B$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Electricity!$A$6:$B$140</definedName>
     <definedName name="fn">'DNA sequencing'!$J$20</definedName>
     <definedName name="Year_span">'DNA sequencing'!$I$1</definedName>
   </definedNames>
@@ -75,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="238">
   <si>
     <t>World</t>
   </si>
@@ -2308,6 +2307,12 @@
   <si>
     <t>LLM t</t>
   </si>
+  <si>
+    <t>Relative to AI</t>
+  </si>
+  <si>
+    <t>x/year</t>
+  </si>
 </sst>
 </file>
 
@@ -2521,7 +2526,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2680,6 +2685,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2856,1878 +2873,9 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="9.4016404945968773E-2"/>
+          <c:x val="0.15474459887663092"/>
           <c:y val="6.0274498584973017E-2"/>
-          <c:w val="0.86806932836467099"/>
-          <c:h val="0.83039405742350791"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="7"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>AI</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$M$3:$M$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>1.6163586584530094</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.7829586584530261</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$N$3:$N$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>1.6493911422653169E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.307518695827581E-6</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-28D7-4073-BEF6-C7AC152E9096}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>Compute</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$G$2:$G$56</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>42</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>47</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>48</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>51</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>52</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>53</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>55</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>56</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>57</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>58</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>61</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$H$2:$H$56</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.35115476038867788</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7.8033172753900662E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.8033172753900662E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7.8033172753900662E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4.6382056926548551E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4.6382056926548551E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.6382056926548551E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>5.7840715825846489E-3</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5.7840715825846489E-3</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5.7840715825846489E-3</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>5.7840715825846489E-3</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.1894462989462484E-3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1.1894462989462484E-3</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>3.9869035438097036E-4</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>3.9869035438097036E-4</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>3.9869035438097036E-4</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1.4230696120937078E-4</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1.3078890527653685E-4</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1.3078890527653685E-4</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1.3078890527653685E-4</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>4.4641876916147174E-5</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>4.4641876916147174E-5</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>4.4641876916147174E-5</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>4.4641876916147174E-5</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>2.3236862295869747E-5</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>3.1618192756799012E-6</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>7.2772030948188204E-7</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>7.2772030948188204E-7</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>7.2772030948188204E-7</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1.2546901887618653E-7</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1.2546901887618653E-7</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1.2546901887618653E-7</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1.2546901887618653E-7</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>2.5093803775237309E-8</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2.5093803775237309E-8</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>4.7678227172950891E-9</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>4.7678227172950891E-9</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1.5056282265142386E-9</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1.5056282265142386E-9</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>5.0187607550474615E-10</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>2.5093803775237307E-10</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>2.5093803775237307E-10</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>2.5093803775237307E-10</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>2.5093803775237307E-10</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>5.9723252985064788E-11</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>3.7389767625103589E-11</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>3.7389767625103589E-11</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1.026336574407206E-11</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-28D7-4073-BEF6-C7AC152E9096}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:v>Lithium batteries</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$D$2:$D$35</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>33</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$E$2:$E$35</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.80216650398524247</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.63861393255108734</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.72902084964219138</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.68422648511492123</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.57629766031901486</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.49350477675367499</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.39704364603272668</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.30073870033647371</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.29213463724575828</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.20390688397575304</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.14609075994844864</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.11295786315868334</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.10107282119990488</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>8.7135380983971084E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>7.462309193147186E-2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>7.1207342270497048E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>7.4662293992658169E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>6.6510416135101946E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>5.9794450301458274E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>5.6958182368952774E-2</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>5.8597070865765571E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>5.3298723267497128E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>4.7150820337820011E-2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>3.6040658050884723E-2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>2.8120904689676589E-2</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2.0303510335789657E-2</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1.7046262688336773E-2</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1.4331889648792702E-2</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1.3354715354556837E-2</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>1.2920415668229785E-2</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1.4331889648792702E-2</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1.2051816295575682E-2</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>8.468843883377505E-3</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-28D7-4073-BEF6-C7AC152E9096}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:v>DNA sequencing</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$J$2:$J$79</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="78"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.49828884325802392</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.99931553730334599</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.4976043805613699</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.0835044490077053</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2.3353867214236743</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2.5817932922657292</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.8336755646816982</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3.0855578370978947</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.3374401095140911</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>3.5811088295688478</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>3.8329911019850442</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4.0848733744012407</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>4.3367556468174371</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4.5804243668721938</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>4.8323066392881628</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>5.0841889117043593</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>5.3360711841205557</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>5.5797399041753124</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>5.8316221765915088</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>6.0835044490077053</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>6.3353867214236743</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>6.5817932922657292</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>6.8336755646816982</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>7.0855578370978947</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>7.3374401095140911</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>7.5811088295688478</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>7.8329911019850442</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>8.0848733744012407</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>8.3367556468174371</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>8.5804243668721938</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>8.8323066392881628</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>9.0841889117043593</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>9.3360711841205557</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>9.5797399041753124</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>9.8316221765915088</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>10.080766598220407</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>10.335386721423674</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>10.581793292265729</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>10.833675564681698</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>11.085557837097895</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>11.337440109514091</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>11.581108829568848</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>11.832991101985044</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>12.084873374401241</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>12.336755646817437</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>12.580424366872194</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>12.832306639288163</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>13.084188911704359</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>13.336071184120556</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>13.579739904175312</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>13.831622176591509</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>14.083504449007705</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>14.666666666666742</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>14.918548939082939</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>15.167693360711837</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>15.414099931553892</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>15.665982203969861</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>15.917864476386058</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>16.167008898015183</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>16.413415468857011</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>16.665297741273207</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>16.917180013689403</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>17.166324435318302</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>17.412731006160357</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>17.582477754962383</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>17.83436002737858</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>18.165639972621648</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>18.412046543463475</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>18.666666666666742</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>18.918548939082939</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>19.167693360711837</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>19.414099931553892</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>19.665982203969861</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>19.917864476386058</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>20.167008898015183</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>20.413415468857011</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>20.665297741273207</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$K$2:$K$79</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="78"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.72966450166975194</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.63222391132945199</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.54699705192006998</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.40468201668292464</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.2873892560087431</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.20250436288913715</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.1964261179806801</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.18010307127461045</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.16990976065198432</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.1556131540651009</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.15382443136010684</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.12988182068984197</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.1176709291497095</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.10865918549877641</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.10479033872157595</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>9.6672432806743716E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>8.5889241079984052E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>8.157688002031134E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>8.0144379342313013E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>6.320278748727777E-2</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>2.6855959871058328E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1.1720659796107069E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>6.411408344161644E-3</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>2.9956434297798685E-3</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>2.0398733178367294E-3</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1.3540116803166067E-3</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>9.3512050058278519E-4</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>6.0360355326899353E-4</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>4.0133189210794686E-4</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>2.7036791526076814E-4</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>2.662711554270181E-4</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>2.4698775629687983E-4</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1.7612212416533382E-4</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1.3859234684711133E-4</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>8.6550335982576426E-5</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>6.3548184017738271E-5</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>6.2594839264667776E-5</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>4.8103278850098872E-5</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>4.8527658871325301E-5</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>5.3356606328380226E-5</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>4.5390613351393476E-5</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>4.4621528929781469E-5</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>4.4322785484690122E-5</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>4.0583822454023445E-5</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>3.172342788152098E-5</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>3.8719458844008944E-5</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>3.8508215680075617E-5</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>4.5084089040370574E-5</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>3.1447903655264528E-5</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>3.3123140454630736E-5</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>1.0677107071392571E-5</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>9.7541058846892562E-6</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>9.1246967031509706E-6</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1.1655187674886646E-5</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>1.0417268640705677E-5</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>7.761601513369908E-6</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>1.0181197746957041E-5</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>8.5785382607503547E-6</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>1.3873546008372642E-5</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>9.2049523124533013E-6</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>1.0866685918468429E-5</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>1.0847204116506927E-5</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>1.0264509761350724E-5</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>7.2814851439087127E-6</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>4.4276553363266953E-6</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>6.8601844627310086E-6</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>5.0125444788007422E-6</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>4.6566339492538819E-6</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>5.0883900051850262E-6</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>4.9373666442219515E-6</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>3.6423861203251413E-6</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>5.9866651559596355E-6</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>3.1275476067508102E-6</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>3.8263289384250511E-6</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>3.6656030166835175E-6</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>3.3999026951282636E-6</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>3.3159531996810656E-6</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-28D7-4073-BEF6-C7AC152E9096}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:v>AI</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$M$2:$M$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.6163586584530094</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$N$2:$N$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.6493911422653169E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-28D7-4073-BEF6-C7AC152E9096}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:v>Electricity</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Figure data'!$A$2:$A$56</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>34</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>39</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>41</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>42</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>47</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>48</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>49</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>51</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>52</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>53</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>55</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>56</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>57</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>58</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>61</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>62</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>63</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>66</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>67</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>68</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>71</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>72</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>73</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>74</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>76</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>77</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>79</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>81</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Figure data'!$B$2:$B$56</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.98103137396321638</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.77924442228328306</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.46036688553442084</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.38533537553467684</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.24215681818181811</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.1810655844155844</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.16300975860297892</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.16155632183908042</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.15981084529505579</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.15257958532695373</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.14882972237343495</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.15673755980861243</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.1687839416058394</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.1750187412587412</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.16394993215739484</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.1507321831453218</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.13848122956180506</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.12279583333333331</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.12102359767891679</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.11861347285807716</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.11305558441558441</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.10458763141620282</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>9.3056999442275495E-2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>8.5771939043615339E-2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>8.2202169421487573E-2</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>7.8085555555555533E-2</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>6.8062843822843819E-2</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>5.7113982878108427E-2</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>5.1479969822708395E-2</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>5.1089763177998473E-2</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>4.9256582421727632E-2</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>4.4547342657342649E-2</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>4.3084665523156082E-2</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>4.2298808307797066E-2</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>4.1218181818181814E-2</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>4.0602985074626868E-2</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>3.9399732620320857E-2</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>3.7551083791653179E-2</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>3.6083737024221442E-2</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>3.541080912214932E-2</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>3.4394901719901713E-2</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>3.3774095469747648E-2</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>3.2892655027092113E-2</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>3.1923885918003561E-2</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>3.0714193548387093E-2</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>2.9441558441558432E-2</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>2.798765432098765E-2</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>2.6779477408818718E-2</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>2.5109926854754439E-2</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>2.3473024523160756E-2</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>2.2308809746954081E-2</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>2.2288350168350166E-2</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>2.2581252718573294E-2</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>2.209443079443079E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-28D7-4073-BEF6-C7AC152E9096}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1131568655"/>
-        <c:axId val="1321391791"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1131568655"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                    <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US">
-                    <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-                    <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-                  </a:rPr>
-                  <a:t>Years since start of price decline</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-                <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1321391791"/>
-        <c:crossesAt val="1.0000000000000006E-11"/>
-        <c:crossBetween val="midCat"/>
-        <c:majorUnit val="30"/>
-        <c:minorUnit val="10"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1321391791"/>
-        <c:scaling>
-          <c:logBase val="10"/>
-          <c:orientation val="minMax"/>
-          <c:max val="1.05"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:noFill/>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1131568655"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="25400">
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:noFill/>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr sz="1100">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-          <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-        </a:defRPr>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:userShapes r:id="rId3"/>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="1"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="9.4016404945968773E-2"/>
-          <c:y val="6.0274498584973017E-2"/>
-          <c:w val="0.86806932836467099"/>
+          <c:w val="0.80734109673495824"/>
           <c:h val="0.84656994233186922"/>
         </c:manualLayout>
       </c:layout>
@@ -6368,6 +4516,20 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -6560,7 +4722,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -8415,7 +6577,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -9053,46 +7215,6 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -10680,1471 +8802,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{B2ECE642-63CB-49BA-A3A9-08DA64A8BA4C}">
-  <sheetPr/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</chartsheet>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="8666825" cy="6292049"/>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0900A08B-AAD3-0CDF-DA80-ACFD86DA6F79}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks noGrp="1"/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.67193</cdr:x>
-      <cdr:y>0.81426</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.8136</cdr:x>
-      <cdr:y>0.92661</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="2" name="TextBox 1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D886207-E4F1-F019-14A4-3966205D2678}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4500571" y="3196437"/>
-          <a:ext cx="948902" cy="441038"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>Compute</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>,</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>1940–2001</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
-            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.387</cdr:x>
-      <cdr:y>0.1999</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.52868</cdr:x>
-      <cdr:y>0.2709</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="3" name="TextBox 1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A081233B-3C5D-69F2-6F98-E93F2A94B7BA}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="2592123" y="784726"/>
-          <a:ext cx="948970" cy="278716"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:lvl1pPr marL="0" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>Lithium</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>batteries</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>,</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>1991–2024</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
-            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.26343</cdr:x>
-      <cdr:y>0.42808</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.40511</cdr:x>
-      <cdr:y>0.59199</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="5" name="TextBox 4">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9E084F5-0B96-630A-2881-BBE3FCD7E1A1}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1764462" y="1680456"/>
-          <a:ext cx="948970" cy="643440"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>DNA</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>sequencing,</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>2001–22</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
-            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.13456</cdr:x>
-      <cdr:y>0.42957</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.19182</cdr:x>
-      <cdr:y>0.55779</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="6" name="TextBox 5">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AE0DB7A-E029-B57F-9D5A-278C5057FA5B}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="901258" y="1686307"/>
-          <a:ext cx="383526" cy="503337"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>AI</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>,</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>2021–26</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
-            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.8706</cdr:x>
-      <cdr:y>0.12194</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.99374</cdr:x>
-      <cdr:y>0.2462</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="7" name="TextBox 6">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89558BC0-E47B-44E8-15AA-1CD6C980C277}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5831231" y="478680"/>
-          <a:ext cx="824839" cy="487791"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>Electricity,</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>1892–1973</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.00796</cdr:x>
-      <cdr:y>0</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.08745</cdr:x>
-      <cdr:y>0.099</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="4" name="TextBox 3">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E6EFF4C-E325-4C3A-AC7D-7A0F249A747B}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="53340" y="0"/>
-          <a:ext cx="532378" cy="388620"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>Starting</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>price</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.04601</cdr:x>
-      <cdr:y>0.1028</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.09846</cdr:x>
-      <cdr:y>0.17358</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="8" name="TextBox 7">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8660BA5-7038-65A7-9FF1-0F500B788276}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="308164" y="403555"/>
-          <a:ext cx="351309" cy="277852"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>10x fall</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.02446</cdr:x>
-      <cdr:y>0.17746</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.09556</cdr:x>
-      <cdr:y>0.25212</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="9" name="TextBox 8">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B7D3985-CC17-2DF7-E36A-C5B4D9537AAC}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="163830" y="696634"/>
-          <a:ext cx="476227" cy="293083"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>100x</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.0599</cdr:x>
-      <cdr:y>0.40353</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.0937</cdr:x>
-      <cdr:y>0.48983</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="10" name="TextBox 9">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E65FA36-95D4-E093-4095-D9E3AA41C5E3}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="401211" y="1584086"/>
-          <a:ext cx="226391" cy="338777"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.06063</cdr:x>
-      <cdr:y>0.24666</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.09443</cdr:x>
-      <cdr:y>0.3056</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="11" name="TextBox 1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0F0CBBC-B2A7-7545-154C-45F157FD73F0}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="406077" y="968271"/>
-          <a:ext cx="226391" cy="231374"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:lvl1pPr marL="0" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.05951</cdr:x>
-      <cdr:y>0.32509</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.09331</cdr:x>
-      <cdr:y>0.38403</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="13" name="TextBox 1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DAA3E2A-F391-FAF9-BA1C-34832F8F390A}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="398598" y="1276147"/>
-          <a:ext cx="226392" cy="231373"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:lvl1pPr marL="0" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-</c:userShapes>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -12194,15 +8852,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>354330</xdr:rowOff>
+      <xdr:colOff>325898</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>36304</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>487680</xdr:colOff>
+      <xdr:colOff>623078</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>73660</xdr:rowOff>
+      <xdr:rowOff>120890</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12237,8 +8895,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>573075</xdr:colOff>
       <xdr:row>68</xdr:row>
       <xdr:rowOff>85090</xdr:rowOff>
     </xdr:to>
@@ -13033,7 +9691,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
@@ -13112,11 +9770,11 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.387</cdr:x>
+      <cdr:x>0.42123</cdr:x>
       <cdr:y>0.1999</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.52868</cdr:x>
+      <cdr:x>0.56291</cdr:x>
       <cdr:y>0.2709</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
@@ -13132,8 +9790,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="2592123" y="784726"/>
-          <a:ext cx="948970" cy="278716"/>
+          <a:off x="2819065" y="788022"/>
+          <a:ext cx="948198" cy="279887"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -13264,12 +9922,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.26343</cdr:x>
-      <cdr:y>0.42808</cdr:y>
+      <cdr:x>0.30138</cdr:x>
+      <cdr:y>0.42981</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.40511</cdr:x>
-      <cdr:y>0.59199</cdr:y>
+      <cdr:x>0.44306</cdr:x>
+      <cdr:y>0.59372</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -13284,8 +9942,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1764462" y="1680456"/>
-          <a:ext cx="948970" cy="643440"/>
+          <a:off x="2017015" y="1694329"/>
+          <a:ext cx="948199" cy="646146"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -13341,12 +9999,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.13456</cdr:x>
-      <cdr:y>0.42957</cdr:y>
+      <cdr:x>0.18132</cdr:x>
+      <cdr:y>0.4313</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.19182</cdr:x>
-      <cdr:y>0.55779</cdr:y>
+      <cdr:x>0.23858</cdr:x>
+      <cdr:y>0.55952</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -13361,8 +10019,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="901258" y="1686307"/>
-          <a:ext cx="383526" cy="503337"/>
+          <a:off x="1213512" y="1700202"/>
+          <a:ext cx="383214" cy="505454"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -13474,12 +10132,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.00796</cdr:x>
-      <cdr:y>0</cdr:y>
+      <cdr:x>0.01177</cdr:x>
+      <cdr:y>0.03968</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.08745</cdr:x>
-      <cdr:y>0.099</cdr:y>
+      <cdr:x>0.1507</cdr:x>
+      <cdr:y>0.09739</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -13494,8 +10152,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="53340" y="0"/>
-          <a:ext cx="532378" cy="388620"/>
+          <a:off x="78719" y="155521"/>
+          <a:ext cx="929351" cy="226238"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -13508,21 +10166,22 @@
           <a:pPr algn="r"/>
           <a:r>
             <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
             </a:rPr>
             <a:t>Starting</a:t>
           </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200" baseline="0">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
             </a:rPr>
-          </a:br>
+            <a:t> </a:t>
+          </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
             </a:rPr>
             <a:t>price</a:t>
           </a:r>
@@ -13532,12 +10191,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.04601</cdr:x>
-      <cdr:y>0.1028</cdr:y>
+      <cdr:x>0.06013</cdr:x>
+      <cdr:y>0.10039</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.09846</cdr:x>
-      <cdr:y>0.17358</cdr:y>
+      <cdr:x>0.16559</cdr:x>
+      <cdr:y>0.17117</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -13552,8 +10211,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="308164" y="403555"/>
-          <a:ext cx="351309" cy="277852"/>
+          <a:off x="402231" y="393507"/>
+          <a:ext cx="705452" cy="277441"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -13566,10 +10225,10 @@
           <a:pPr algn="r"/>
           <a:r>
             <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
             </a:rPr>
-            <a:t>10x fall</a:t>
+            <a:t>10× cheaper</a:t>
           </a:r>
         </a:p>
       </cdr:txBody>
@@ -13577,11 +10236,11 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.02446</cdr:x>
+      <cdr:x>0.03105</cdr:x>
       <cdr:y>0.17746</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.09556</cdr:x>
+      <cdr:x>0.13773</cdr:x>
       <cdr:y>0.25212</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
@@ -13597,8 +10256,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="163830" y="696634"/>
-          <a:ext cx="476227" cy="293083"/>
+          <a:off x="207697" y="695604"/>
+          <a:ext cx="713604" cy="292650"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -13611,112 +10270,43 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
             </a:rPr>
-            <a:t>100x</a:t>
+            <a:t>100</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>×</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t> cheaper</a:t>
           </a:r>
           <a:br>
             <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
             </a:rPr>
           </a:br>
           <a:br>
             <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
             </a:rPr>
           </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0.0599</cdr:x>
-      <cdr:y>0.40353</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.0937</cdr:x>
-      <cdr:y>0.48983</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="10" name="TextBox 9">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E65FA36-95D4-E093-4095-D9E3AA41C5E3}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr txBox="1"/>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="401211" y="1584086"/>
-          <a:ext cx="226391" cy="338777"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
+            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
         </a:p>
       </cdr:txBody>
     </cdr:sp>
@@ -13818,32 +10408,29 @@
           </a:lvl9pPr>
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
+            <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+            <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
         </a:p>
       </cdr:txBody>
     </cdr:sp>
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.05951</cdr:x>
-      <cdr:y>0.32509</cdr:y>
+      <cdr:x>0.02352</cdr:x>
+      <cdr:y>0.25509</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.09331</cdr:x>
-      <cdr:y>0.38403</cdr:y>
+      <cdr:x>0.1302</cdr:x>
+      <cdr:y>0.32975</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
-        <cdr:cNvPr id="13" name="TextBox 1">
+        <cdr:cNvPr id="12" name="TextBox 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DAA3E2A-F391-FAF9-BA1C-34832F8F390A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C966B766-BB22-958D-04DF-C52D4AB984D1}"/>
             </a:ext>
           </a:extLst>
         </cdr:cNvPr>
@@ -13851,8 +10438,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="398598" y="1276147"/>
-          <a:ext cx="226392" cy="231373"/>
+          <a:off x="157389" y="1005568"/>
+          <a:ext cx="713963" cy="294315"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -13926,13 +10513,426 @@
           </a:lvl9pPr>
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-US" sz="1100" kern="1200">
-              <a:latin typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Cambria" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
             </a:rPr>
-            <a:t>.</a:t>
+            <a:t>1000</a:t>
           </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>×</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t> cheaper</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
+            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.03193</cdr:x>
+      <cdr:y>0.48371</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.17751</cdr:x>
+      <cdr:y>0.55837</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="14" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C966B766-BB22-958D-04DF-C52D4AB984D1}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="213609" y="1896016"/>
+          <a:ext cx="973780" cy="292650"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>1 million</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>×</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
+            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.0321</cdr:x>
+      <cdr:y>0.71648</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.17768</cdr:x>
+      <cdr:y>0.79114</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="15" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{053B2150-99B6-1CF4-6E55-FBAA25B5F73B}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="214748" y="2808451"/>
+          <a:ext cx="973780" cy="292650"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>1 billion</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>×</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
+            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.00847</cdr:x>
+      <cdr:y>0.86882</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.17553</cdr:x>
+      <cdr:y>0.94348</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="16" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{053B2150-99B6-1CF4-6E55-FBAA25B5F73B}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="56678" y="3405565"/>
+          <a:ext cx="1117490" cy="292650"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>100</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200" baseline="0">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t> b</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200">
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            </a:rPr>
+            <a:t>illion</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:effectLst/>
+              <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>×</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200">
+            <a:latin typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+            <a:ea typeface="Inter" panose="02000503000000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
         </a:p>
       </cdr:txBody>
     </cdr:sp>
@@ -13940,7 +10940,7 @@
 </c:userShapes>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
@@ -14382,7 +11382,7 @@
 </c:userShapes>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -14887,7 +11887,7 @@
     <col min="5" max="5" width="14.26171875" customWidth="1"/>
     <col min="6" max="6" width="1.41796875" customWidth="1"/>
     <col min="7" max="7" width="14.26171875" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
+    <col min="8" max="8" width="6.89453125" customWidth="1"/>
     <col min="9" max="9" width="10.9453125" customWidth="1"/>
     <col min="22" max="29" width="10.89453125" customWidth="1"/>
   </cols>
@@ -14908,12 +11908,16 @@
       <c r="E1" s="50" t="s">
         <v>201</v>
       </c>
-      <c r="F1" s="51"/>
-      <c r="G1" s="58" t="s">
+      <c r="F1" s="50"/>
+      <c r="G1" s="68" t="s">
         <v>220</v>
       </c>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
+      <c r="H1" s="68" t="s">
+        <v>236</v>
+      </c>
+      <c r="I1" s="58" t="s">
+        <v>237</v>
+      </c>
       <c r="V1" s="11"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -15089,15 +12093,15 @@
         <v>0.47</v>
       </c>
       <c r="F7" s="52"/>
-      <c r="G7" s="57">
+      <c r="G7" s="65">
         <f t="shared" si="2"/>
         <v>0.6348782724359695</v>
       </c>
-      <c r="H7" s="59">
+      <c r="H7" s="66">
         <f>$G$7/G7</f>
         <v>1</v>
       </c>
-      <c r="I7" s="61">
+      <c r="I7" s="67">
         <f>(1-D7)^-4</f>
         <v>12.673498611808327</v>
       </c>
@@ -15266,11 +12270,11 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <f>Table!$B11</f>
+        <f>Figure!$B11</f>
         <v>0</v>
       </c>
       <c r="N2">
-        <f>Table!$C11/100</f>
+        <f>Figure!$C11/100</f>
         <v>1</v>
       </c>
       <c r="O2">
@@ -15328,11 +12332,11 @@
         <v>1.3704928740696811</v>
       </c>
       <c r="M3">
-        <f>Table!$B12</f>
+        <f>Figure!$B12</f>
         <v>1.6163586584530094</v>
       </c>
       <c r="N3">
-        <f>Table!$C12/100</f>
+        <f>Figure!$C12/100</f>
         <v>1.6493911422653169E-2</v>
       </c>
       <c r="O3">
@@ -15390,11 +12394,11 @@
         <v>1.5817180939853757</v>
       </c>
       <c r="M4">
-        <f>Table!$B13</f>
+        <f>Figure!$B13</f>
         <v>4.7829586584530261</v>
       </c>
       <c r="N4">
-        <f>Table!$C13/100</f>
+        <f>Figure!$C13/100</f>
         <v>5.307518695827581E-6</v>
       </c>
       <c r="O4">
